--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,399 +656,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>31039000</v>
+        <v>36193600</v>
       </c>
       <c r="E8" s="3">
-        <v>32332300</v>
+        <v>31250300</v>
       </c>
       <c r="F8" s="3">
-        <v>28748300</v>
+        <v>32552400</v>
       </c>
       <c r="G8" s="3">
-        <v>34210100</v>
+        <v>28944000</v>
       </c>
       <c r="H8" s="3">
-        <v>28606900</v>
+        <v>34443000</v>
       </c>
       <c r="I8" s="3">
-        <v>28383000</v>
+        <v>28801600</v>
       </c>
       <c r="J8" s="3">
+        <v>28576300</v>
+      </c>
+      <c r="K8" s="3">
         <v>28175500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33422700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28528100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29548400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26085400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30774900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22849500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22656700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17897000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24861000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18567800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17558100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14222900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17032300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11917300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11610400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19284800</v>
+        <v>21716900</v>
       </c>
       <c r="E9" s="3">
-        <v>19655300</v>
+        <v>19416100</v>
       </c>
       <c r="F9" s="3">
-        <v>19168700</v>
+        <v>19789100</v>
       </c>
       <c r="G9" s="3">
-        <v>20712700</v>
+        <v>19299200</v>
       </c>
       <c r="H9" s="3">
-        <v>18117500</v>
+        <v>20853700</v>
       </c>
       <c r="I9" s="3">
-        <v>17903000</v>
+        <v>18240800</v>
       </c>
       <c r="J9" s="3">
+        <v>18024900</v>
+      </c>
+      <c r="K9" s="3">
         <v>19185500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20206500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18444000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17822800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17463200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16880500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13256500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12455300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11350900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12985400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10225800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9164800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8459400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8831900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6548200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6272900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>11754200</v>
+        <v>14476700</v>
       </c>
       <c r="E10" s="3">
-        <v>12677000</v>
+        <v>11834200</v>
       </c>
       <c r="F10" s="3">
-        <v>9579600</v>
+        <v>12763300</v>
       </c>
       <c r="G10" s="3">
-        <v>13497500</v>
+        <v>9644800</v>
       </c>
       <c r="H10" s="3">
-        <v>10489400</v>
+        <v>13589300</v>
       </c>
       <c r="I10" s="3">
-        <v>10480000</v>
+        <v>10560800</v>
       </c>
       <c r="J10" s="3">
+        <v>10551300</v>
+      </c>
+      <c r="K10" s="3">
         <v>8990000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13216100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10084100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11725600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8622200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13894400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9593000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10201400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6546100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11875600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8342000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8393300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5763500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8200400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5369100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5337500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1081,100 +1093,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1963200</v>
+        <v>1875100</v>
       </c>
       <c r="E12" s="3">
-        <v>1445000</v>
+        <v>1976600</v>
       </c>
       <c r="F12" s="3">
-        <v>1916600</v>
+        <v>1454800</v>
       </c>
       <c r="G12" s="3">
-        <v>1867000</v>
+        <v>1929600</v>
       </c>
       <c r="H12" s="3">
-        <v>2091900</v>
+        <v>1879700</v>
       </c>
       <c r="I12" s="3">
-        <v>1959800</v>
+        <v>2106200</v>
       </c>
       <c r="J12" s="3">
+        <v>1973100</v>
+      </c>
+      <c r="K12" s="3">
         <v>1511100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2163800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2174500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1941600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1851600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1894100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2835900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1633000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1657500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1705600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1706400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1600800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1317200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1292700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1170800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1651500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>959300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>933400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>754400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>696900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>657100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>642800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,192 +1281,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1180300</v>
       </c>
       <c r="E14" s="3">
-        <v>280400</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>282300</v>
       </c>
       <c r="G14" s="3">
-        <v>374700</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>377300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>89900</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
         <v>309000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>335700</v>
+        <v>2029800</v>
       </c>
       <c r="E15" s="3">
-        <v>342300</v>
+        <v>338000</v>
       </c>
       <c r="F15" s="3">
-        <v>344400</v>
+        <v>344600</v>
       </c>
       <c r="G15" s="3">
-        <v>763600</v>
+        <v>346700</v>
       </c>
       <c r="H15" s="3">
-        <v>376800</v>
+        <v>768800</v>
       </c>
       <c r="I15" s="3">
-        <v>379900</v>
+        <v>379400</v>
       </c>
       <c r="J15" s="3">
-        <v>390900</v>
+        <v>382400</v>
       </c>
       <c r="K15" s="3">
         <v>390900</v>
       </c>
       <c r="L15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="M15" s="3">
         <v>413100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>441300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>475400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>441500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>425600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>435000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>633100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>503800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>469000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>468400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>487200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>408000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>365400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>301900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>190700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>305300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>259400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>294700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>190900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>183400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1480,192 +1505,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26401700</v>
+        <v>33064100</v>
       </c>
       <c r="E17" s="3">
-        <v>26465200</v>
+        <v>26581500</v>
       </c>
       <c r="F17" s="3">
-        <v>26643900</v>
+        <v>26645400</v>
       </c>
       <c r="G17" s="3">
-        <v>29373100</v>
+        <v>26825300</v>
       </c>
       <c r="H17" s="3">
-        <v>25135900</v>
+        <v>29573000</v>
       </c>
       <c r="I17" s="3">
-        <v>24938900</v>
+        <v>25307100</v>
       </c>
       <c r="J17" s="3">
+        <v>25108700</v>
+      </c>
+      <c r="K17" s="3">
         <v>25867200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32448800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26395000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25118100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27152100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23953800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20840400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17542600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16780600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18769500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15390900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13834100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12889600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13140400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10027700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10459700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4637300</v>
+        <v>3129500</v>
       </c>
       <c r="E18" s="3">
-        <v>5867000</v>
+        <v>4668800</v>
       </c>
       <c r="F18" s="3">
-        <v>2104300</v>
+        <v>5907000</v>
       </c>
       <c r="G18" s="3">
-        <v>4837100</v>
+        <v>2118700</v>
       </c>
       <c r="H18" s="3">
-        <v>3470900</v>
+        <v>4870000</v>
       </c>
       <c r="I18" s="3">
-        <v>3444100</v>
+        <v>3494500</v>
       </c>
       <c r="J18" s="3">
+        <v>3467600</v>
+      </c>
+      <c r="K18" s="3">
         <v>2308300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>973800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2133100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4430200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6821100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2009100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5114100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1116400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6091400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3177000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3724000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1333300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3891900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1889600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1150700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1698,171 +1730,175 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>901200</v>
+        <v>-425500</v>
       </c>
       <c r="E20" s="3">
-        <v>-626100</v>
+        <v>907400</v>
       </c>
       <c r="F20" s="3">
-        <v>1629900</v>
+        <v>-630300</v>
       </c>
       <c r="G20" s="3">
-        <v>2344300</v>
+        <v>1641000</v>
       </c>
       <c r="H20" s="3">
-        <v>-5455300</v>
+        <v>2360300</v>
       </c>
       <c r="I20" s="3">
-        <v>756400</v>
+        <v>-5492400</v>
       </c>
       <c r="J20" s="3">
+        <v>761600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3230100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2335000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>309900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5966400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1717900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3482100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2790600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10377600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>349600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3059700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1735100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>714200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1027700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>405900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>767600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>498500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>560200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5492000</v>
+        <v>4442700</v>
       </c>
       <c r="E21" s="3">
-        <v>6505800</v>
+        <v>5529400</v>
       </c>
       <c r="F21" s="3">
-        <v>3277600</v>
+        <v>6550100</v>
       </c>
       <c r="G21" s="3">
-        <v>7563600</v>
+        <v>3299900</v>
       </c>
       <c r="H21" s="3">
-        <v>-1925000</v>
+        <v>7615100</v>
       </c>
       <c r="I21" s="3">
-        <v>5504800</v>
+        <v>-1938100</v>
       </c>
       <c r="J21" s="3">
+        <v>5542300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4157900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>704500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8197100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>564900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12940900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3812200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9866300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1609300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8955000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13596400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5257300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4411900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5740800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2772500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>10</v>
@@ -1873,293 +1909,305 @@
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>256000</v>
+        <v>296400</v>
       </c>
       <c r="E22" s="3">
-        <v>246300</v>
+        <v>257700</v>
       </c>
       <c r="F22" s="3">
-        <v>239700</v>
+        <v>248000</v>
       </c>
       <c r="G22" s="3">
-        <v>214000</v>
+        <v>241300</v>
       </c>
       <c r="H22" s="3">
-        <v>191700</v>
+        <v>215500</v>
       </c>
       <c r="I22" s="3">
-        <v>171800</v>
+        <v>193000</v>
       </c>
       <c r="J22" s="3">
+        <v>172900</v>
+      </c>
+      <c r="K22" s="3">
         <v>164200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>163400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>180100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>182000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>161500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>152000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>162200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>165500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>182400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>201600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>212200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>205600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>198200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>193700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>187500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>174000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>168600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>125300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>110900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>118700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>98300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>101900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5282500</v>
+        <v>2407500</v>
       </c>
       <c r="E23" s="3">
-        <v>4994600</v>
+        <v>5318500</v>
       </c>
       <c r="F23" s="3">
-        <v>3494500</v>
+        <v>5028600</v>
       </c>
       <c r="G23" s="3">
-        <v>6967400</v>
+        <v>3518300</v>
       </c>
       <c r="H23" s="3">
-        <v>-2176000</v>
+        <v>7014800</v>
       </c>
       <c r="I23" s="3">
-        <v>4028800</v>
+        <v>-2190800</v>
       </c>
       <c r="J23" s="3">
+        <v>4056200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4040500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>560900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6583300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-918300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12635500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3564800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8430800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-89100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8680500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13342400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3867900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4194900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5433200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2416300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2004400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>800400</v>
+        <v>693400</v>
       </c>
       <c r="E24" s="3">
-        <v>831500</v>
+        <v>805900</v>
       </c>
       <c r="F24" s="3">
-        <v>518900</v>
+        <v>837200</v>
       </c>
       <c r="G24" s="3">
-        <v>527500</v>
+        <v>522400</v>
       </c>
       <c r="H24" s="3">
-        <v>355100</v>
+        <v>531100</v>
       </c>
       <c r="I24" s="3">
-        <v>745500</v>
+        <v>357600</v>
       </c>
       <c r="J24" s="3">
+        <v>750600</v>
+      </c>
+      <c r="K24" s="3">
         <v>287100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1316200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>865300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1306400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>981200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1279800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>281600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1639200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>411400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1294500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>439200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1025500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>764400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>811300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>38800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>812800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>597500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>988900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>403500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>690600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>662100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>743100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2250,192 +2298,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4482100</v>
+        <v>1714100</v>
       </c>
       <c r="E26" s="3">
-        <v>4163100</v>
+        <v>4512600</v>
       </c>
       <c r="F26" s="3">
-        <v>2975600</v>
+        <v>4191500</v>
       </c>
       <c r="G26" s="3">
-        <v>6439900</v>
+        <v>2995900</v>
       </c>
       <c r="H26" s="3">
-        <v>-2531100</v>
+        <v>6483800</v>
       </c>
       <c r="I26" s="3">
-        <v>3283300</v>
+        <v>-2548400</v>
       </c>
       <c r="J26" s="3">
+        <v>3305600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2724300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-304300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5276900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11355700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3283200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6791500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7386000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12903300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2842500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3430500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4621900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2377500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1191600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>962900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3825600</v>
+        <v>2006500</v>
       </c>
       <c r="E27" s="3">
-        <v>4740600</v>
+        <v>3851700</v>
       </c>
       <c r="F27" s="3">
-        <v>3247100</v>
+        <v>4772800</v>
       </c>
       <c r="G27" s="3">
-        <v>6464200</v>
+        <v>3269200</v>
       </c>
       <c r="H27" s="3">
-        <v>-2839100</v>
+        <v>6508200</v>
       </c>
       <c r="I27" s="3">
-        <v>3139800</v>
+        <v>-2858400</v>
       </c>
       <c r="J27" s="3">
+        <v>3161200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2814700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>762900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6483200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-762700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11056200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7013000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>495000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8054500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11317000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3246900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3929300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2803800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1246100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2526,8 +2583,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2618,8 +2678,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2710,8 +2773,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2802,192 +2868,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-901200</v>
+        <v>425500</v>
       </c>
       <c r="E32" s="3">
-        <v>626100</v>
+        <v>-907400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1629900</v>
+        <v>630300</v>
       </c>
       <c r="G32" s="3">
-        <v>-2344300</v>
+        <v>-1641000</v>
       </c>
       <c r="H32" s="3">
-        <v>5455300</v>
+        <v>-2360300</v>
       </c>
       <c r="I32" s="3">
-        <v>-756400</v>
+        <v>5492400</v>
       </c>
       <c r="J32" s="3">
+        <v>-761600</v>
+      </c>
+      <c r="K32" s="3">
         <v>4845000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1392100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-309900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1023100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-349600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-714200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3825600</v>
+        <v>2006500</v>
       </c>
       <c r="E33" s="3">
-        <v>4740600</v>
+        <v>3851700</v>
       </c>
       <c r="F33" s="3">
-        <v>3247100</v>
+        <v>4772800</v>
       </c>
       <c r="G33" s="3">
-        <v>6464200</v>
+        <v>3269200</v>
       </c>
       <c r="H33" s="3">
-        <v>-2839100</v>
+        <v>6508200</v>
       </c>
       <c r="I33" s="3">
-        <v>3139800</v>
+        <v>-2858400</v>
       </c>
       <c r="J33" s="3">
+        <v>3161200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2814700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>762900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6483200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-762700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11056200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7013000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>495000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8054500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11317000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3246900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3929300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4800100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2803800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1246100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3078,197 +3153,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3825600</v>
+        <v>2006500</v>
       </c>
       <c r="E35" s="3">
-        <v>4740600</v>
+        <v>3851700</v>
       </c>
       <c r="F35" s="3">
-        <v>3247100</v>
+        <v>4772800</v>
       </c>
       <c r="G35" s="3">
-        <v>6464200</v>
+        <v>3269200</v>
       </c>
       <c r="H35" s="3">
-        <v>-2839100</v>
+        <v>6508200</v>
       </c>
       <c r="I35" s="3">
-        <v>3139800</v>
+        <v>-2858400</v>
       </c>
       <c r="J35" s="3">
+        <v>3161200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2814700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>762900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6483200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-762700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11056200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7013000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>495000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8054500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11317000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3246900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3929300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4800100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2803800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1246100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3301,8 +3385,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3335,192 +3420,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>33652300</v>
+        <v>35422900</v>
       </c>
       <c r="E41" s="3">
-        <v>31262000</v>
+        <v>33881400</v>
       </c>
       <c r="F41" s="3">
-        <v>26661300</v>
+        <v>31474800</v>
       </c>
       <c r="G41" s="3">
-        <v>26960000</v>
+        <v>26842800</v>
       </c>
       <c r="H41" s="3">
-        <v>28542700</v>
+        <v>27143500</v>
       </c>
       <c r="I41" s="3">
-        <v>24403200</v>
+        <v>28737000</v>
       </c>
       <c r="J41" s="3">
+        <v>24569300</v>
+      </c>
+      <c r="K41" s="3">
         <v>26221100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40385100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38694100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41909600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44719700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43449500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44430400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45573600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51743500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53981500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36534000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>32166100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28899100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27478100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>23005900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24089600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>45655300</v>
+        <v>49990900</v>
       </c>
       <c r="E42" s="3">
-        <v>43912800</v>
+        <v>45966100</v>
       </c>
       <c r="F42" s="3">
-        <v>45757500</v>
+        <v>44211700</v>
       </c>
       <c r="G42" s="3">
-        <v>44732900</v>
+        <v>46069000</v>
       </c>
       <c r="H42" s="3">
-        <v>38717500</v>
+        <v>45037500</v>
       </c>
       <c r="I42" s="3">
-        <v>39567000</v>
+        <v>38981100</v>
       </c>
       <c r="J42" s="3">
+        <v>39836300</v>
+      </c>
+      <c r="K42" s="3">
         <v>36617000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27806800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26581900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27509400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22575900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20883300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>16090800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11389600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5121400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1021700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1066000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1540200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2006300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1653700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2402000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2475900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3611,8 +3703,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3703,468 +3798,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25350900</v>
+        <v>26809000</v>
       </c>
       <c r="E45" s="3">
-        <v>25683700</v>
+        <v>25523500</v>
       </c>
       <c r="F45" s="3">
-        <v>23956300</v>
+        <v>25858600</v>
       </c>
       <c r="G45" s="3">
-        <v>28881200</v>
+        <v>24119400</v>
       </c>
       <c r="H45" s="3">
-        <v>26317900</v>
+        <v>29077800</v>
       </c>
       <c r="I45" s="3">
-        <v>25086500</v>
+        <v>26497100</v>
       </c>
       <c r="J45" s="3">
+        <v>25257300</v>
+      </c>
+      <c r="K45" s="3">
         <v>25330800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24828600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25422400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23522800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22260200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18870600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16538500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15436500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15610300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15742300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14770600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10696400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10208500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8872000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7886200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7438400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>104658600</v>
+        <v>112222800</v>
       </c>
       <c r="E46" s="3">
-        <v>100858500</v>
+        <v>105371000</v>
       </c>
       <c r="F46" s="3">
-        <v>96375100</v>
+        <v>101545100</v>
       </c>
       <c r="G46" s="3">
-        <v>100574200</v>
+        <v>97031200</v>
       </c>
       <c r="H46" s="3">
-        <v>93578100</v>
+        <v>101258800</v>
       </c>
       <c r="I46" s="3">
-        <v>89056600</v>
+        <v>94215100</v>
       </c>
       <c r="J46" s="3">
+        <v>89662900</v>
+      </c>
+      <c r="K46" s="3">
         <v>88168900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>93020500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>90698400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>92941800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>89555700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>83203500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>77059700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>72399700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>72475200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>70745500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>52370500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>44402800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>41113900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>38003800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33294100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34003900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>62979500</v>
+        <v>59667900</v>
       </c>
       <c r="E47" s="3">
-        <v>62365200</v>
+        <v>63408300</v>
       </c>
       <c r="F47" s="3">
-        <v>62566400</v>
+        <v>62789800</v>
       </c>
       <c r="G47" s="3">
-        <v>60218500</v>
+        <v>62992300</v>
       </c>
       <c r="H47" s="3">
-        <v>57739700</v>
+        <v>60628400</v>
       </c>
       <c r="I47" s="3">
-        <v>61691700</v>
+        <v>58132700</v>
       </c>
       <c r="J47" s="3">
+        <v>62111600</v>
+      </c>
+      <c r="K47" s="3">
         <v>61204400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>65630300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65584300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65281500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>60887500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>59266900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>58735200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>55079600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>54946500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>55746500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>51631700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>38852700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>36743700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>33087900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>30691800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>28385900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>24776500</v>
+        <v>25247100</v>
       </c>
       <c r="E48" s="3">
-        <v>24282600</v>
+        <v>24945200</v>
       </c>
       <c r="F48" s="3">
-        <v>24306400</v>
+        <v>24447900</v>
       </c>
       <c r="G48" s="3">
-        <v>24550100</v>
+        <v>24471800</v>
       </c>
       <c r="H48" s="3">
-        <v>24794600</v>
+        <v>24717200</v>
       </c>
       <c r="I48" s="3">
-        <v>24552300</v>
+        <v>24963400</v>
       </c>
       <c r="J48" s="3">
+        <v>24719400</v>
+      </c>
+      <c r="K48" s="3">
         <v>34500500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22741400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22326900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21917300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20519800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20473800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17393900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16424900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21612600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19466200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19627200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18193700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13999600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13188900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12180000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11286000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>42570800</v>
+        <v>40020700</v>
       </c>
       <c r="E49" s="3">
-        <v>42962800</v>
+        <v>42860600</v>
       </c>
       <c r="F49" s="3">
-        <v>43495800</v>
+        <v>43255200</v>
       </c>
       <c r="G49" s="3">
-        <v>43781400</v>
+        <v>43791900</v>
       </c>
       <c r="H49" s="3">
-        <v>44938000</v>
+        <v>44079500</v>
       </c>
       <c r="I49" s="3">
-        <v>45188600</v>
+        <v>45243900</v>
       </c>
       <c r="J49" s="3">
+        <v>45496200</v>
+      </c>
+      <c r="K49" s="3">
         <v>45402400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45628900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>51142200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>51691900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>50613700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>51132800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>49004600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>49288400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>52874900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>52626800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>53469800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>50862400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>50688100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>45348800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>35607600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>37195600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4255,8 +4368,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4347,100 +4463,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15159000</v>
+        <v>15992200</v>
       </c>
       <c r="E52" s="3">
-        <v>14872000</v>
+        <v>15262200</v>
       </c>
       <c r="F52" s="3">
-        <v>15316700</v>
+        <v>14973300</v>
       </c>
       <c r="G52" s="3">
-        <v>15570700</v>
+        <v>15420900</v>
       </c>
       <c r="H52" s="3">
-        <v>15417700</v>
+        <v>15676700</v>
       </c>
       <c r="I52" s="3">
-        <v>15402300</v>
+        <v>15522700</v>
       </c>
       <c r="J52" s="3">
+        <v>15507100</v>
+      </c>
+      <c r="K52" s="3">
         <v>4845800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15549900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15552800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14506300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13701700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13552100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9065700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8569300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3651800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4590900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3806500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3348900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4262100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3683500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3660800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3433600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4531,100 +4653,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>250144300</v>
+        <v>253150700</v>
       </c>
       <c r="E54" s="3">
-        <v>245341100</v>
+        <v>251847200</v>
       </c>
       <c r="F54" s="3">
-        <v>242060300</v>
+        <v>247011300</v>
       </c>
       <c r="G54" s="3">
-        <v>244694900</v>
+        <v>243708200</v>
       </c>
       <c r="H54" s="3">
-        <v>236468100</v>
+        <v>246360700</v>
       </c>
       <c r="I54" s="3">
-        <v>235891500</v>
+        <v>238077900</v>
       </c>
       <c r="J54" s="3">
+        <v>237497300</v>
+      </c>
+      <c r="K54" s="3">
         <v>234122000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>242570900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>245304600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>246338700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>235278300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>227629000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>211259100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>201761900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>205560900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>203175800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>180905600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>155660500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>146807400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>133312900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>115434400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114305100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4657,8 +4785,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4691,59 +4820,60 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>39574300</v>
+        <v>43824900</v>
       </c>
       <c r="E57" s="3">
-        <v>38572800</v>
+        <v>39843700</v>
       </c>
       <c r="F57" s="3">
-        <v>38103200</v>
+        <v>38835400</v>
       </c>
       <c r="G57" s="3">
-        <v>40549400</v>
+        <v>38362600</v>
       </c>
       <c r="H57" s="3">
-        <v>37538800</v>
+        <v>40825400</v>
       </c>
       <c r="I57" s="3">
-        <v>36668900</v>
-      </c>
-      <c r="J57" s="3" t="s">
+        <v>37794400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>36918600</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>38835600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37802900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35961600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36321300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>31307500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26279700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24271800</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="S57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
@@ -4783,468 +4913,486 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1130500</v>
+        <v>3663700</v>
       </c>
       <c r="E58" s="3">
-        <v>1137200</v>
+        <v>1138200</v>
       </c>
       <c r="F58" s="3">
-        <v>1693700</v>
+        <v>1145000</v>
       </c>
       <c r="G58" s="3">
-        <v>1596900</v>
+        <v>1705200</v>
       </c>
       <c r="H58" s="3">
-        <v>1602000</v>
+        <v>1607800</v>
       </c>
       <c r="I58" s="3">
-        <v>1870800</v>
+        <v>1612900</v>
       </c>
       <c r="J58" s="3">
+        <v>1883600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1220800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1089300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2679000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2443400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1870400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2094500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>722500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>669500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>806900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>649000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3768400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3516800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3417500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3313000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1262700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1964700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>864900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>956800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13120200</v>
+        <v>14897100</v>
       </c>
       <c r="E59" s="3">
-        <v>12793400</v>
+        <v>13209500</v>
       </c>
       <c r="F59" s="3">
-        <v>13412400</v>
+        <v>12880500</v>
       </c>
       <c r="G59" s="3">
-        <v>15548400</v>
+        <v>13503700</v>
       </c>
       <c r="H59" s="3">
-        <v>13724600</v>
+        <v>15654200</v>
       </c>
       <c r="I59" s="3">
-        <v>13320900</v>
+        <v>13818000</v>
       </c>
       <c r="J59" s="3">
+        <v>13411500</v>
+      </c>
+      <c r="K59" s="3">
         <v>51772100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16634700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14652800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14475700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14336500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16453900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11744900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11617700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>37060600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39764300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34290100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>28673900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>28173100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27007000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22264000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21594200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53825000</v>
+        <v>62385800</v>
       </c>
       <c r="E60" s="3">
-        <v>52503400</v>
+        <v>54191400</v>
       </c>
       <c r="F60" s="3">
-        <v>53209300</v>
+        <v>52860800</v>
       </c>
       <c r="G60" s="3">
-        <v>57694700</v>
+        <v>53571500</v>
       </c>
       <c r="H60" s="3">
-        <v>52865400</v>
+        <v>58087400</v>
       </c>
       <c r="I60" s="3">
-        <v>51860600</v>
+        <v>53225300</v>
       </c>
       <c r="J60" s="3">
+        <v>52213700</v>
+      </c>
+      <c r="K60" s="3">
         <v>52992900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56559700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55134700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52880700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52528200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>49855900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38747100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36559000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>37867500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40413300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38058500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32190700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31590600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30320000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23526700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23558800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21893600</v>
+        <v>19403300</v>
       </c>
       <c r="E61" s="3">
-        <v>21721000</v>
+        <v>22042600</v>
       </c>
       <c r="F61" s="3">
-        <v>20586100</v>
+        <v>21868800</v>
       </c>
       <c r="G61" s="3">
-        <v>20471700</v>
+        <v>20726200</v>
       </c>
       <c r="H61" s="3">
-        <v>20689600</v>
+        <v>20611100</v>
       </c>
       <c r="I61" s="3">
-        <v>19118800</v>
+        <v>20830500</v>
       </c>
       <c r="J61" s="3">
+        <v>19249000</v>
+      </c>
+      <c r="K61" s="3">
         <v>18296000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18149900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18892700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19187500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18891700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14289200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>17224200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17814900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18830400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18196100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18958600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17779000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17012200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16446000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18082000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17848900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12865900</v>
+        <v>12541000</v>
       </c>
       <c r="E62" s="3">
-        <v>12733300</v>
+        <v>12953500</v>
       </c>
       <c r="F62" s="3">
-        <v>13212000</v>
+        <v>12820000</v>
       </c>
       <c r="G62" s="3">
-        <v>13289600</v>
+        <v>13302000</v>
       </c>
       <c r="H62" s="3">
-        <v>13445300</v>
+        <v>13380100</v>
       </c>
       <c r="I62" s="3">
-        <v>13530700</v>
+        <v>13536800</v>
       </c>
       <c r="J62" s="3">
+        <v>13622800</v>
+      </c>
+      <c r="K62" s="3">
         <v>13403800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13526600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13729800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13614700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13016600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12820300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10694800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10566900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11144900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11048800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10354200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7139000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4589600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4043600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3657000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4636800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5335,8 +5483,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5427,8 +5578,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5519,100 +5673,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>107220200</v>
+        <v>112658500</v>
       </c>
       <c r="E66" s="3">
-        <v>105396500</v>
+        <v>107950100</v>
       </c>
       <c r="F66" s="3">
-        <v>105408500</v>
+        <v>106114000</v>
       </c>
       <c r="G66" s="3">
-        <v>109935200</v>
+        <v>106126100</v>
       </c>
       <c r="H66" s="3">
-        <v>105576900</v>
+        <v>110683600</v>
       </c>
       <c r="I66" s="3">
-        <v>102887300</v>
+        <v>106295700</v>
       </c>
       <c r="J66" s="3">
+        <v>103587700</v>
+      </c>
+      <c r="K66" s="3">
         <v>103156000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>106870400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106961600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105035900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103575200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>96014900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>83728500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>81439100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>85870200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>87396600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>85691900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>74973700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70887900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>65336800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>55593000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57452000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5645,8 +5805,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5737,8 +5898,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5829,8 +5993,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5856,73 +6023,76 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>1461600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1477500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1201100</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1207300</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1175300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1183700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1152400</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1425200</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1200300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1171000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1083400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1037300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1040600</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>839900</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>452700</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>430600</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>442100</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>133300</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>113200</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>435100</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>515800</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6013,100 +6183,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>89762900</v>
+        <v>87801700</v>
       </c>
       <c r="E72" s="3">
-        <v>87118000</v>
+        <v>90374000</v>
       </c>
       <c r="F72" s="3">
-        <v>84505700</v>
+        <v>87711100</v>
       </c>
       <c r="G72" s="3">
-        <v>82521300</v>
+        <v>85080900</v>
       </c>
       <c r="H72" s="3">
-        <v>76921900</v>
+        <v>83083100</v>
       </c>
       <c r="I72" s="3">
-        <v>79743300</v>
+        <v>77445500</v>
       </c>
       <c r="J72" s="3">
+        <v>80286100</v>
+      </c>
+      <c r="K72" s="3">
         <v>79174500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>81449200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>82138400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>86310300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>78268100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>79111700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>72029000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>67773800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>64563300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>63003500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>55694500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>43446200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39985800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34455500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29692900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27742100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6197,8 +6373,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6289,8 +6468,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6381,100 +6563,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>142924100</v>
+        <v>140492200</v>
       </c>
       <c r="E76" s="3">
-        <v>139944600</v>
+        <v>143897100</v>
       </c>
       <c r="F76" s="3">
-        <v>136651800</v>
+        <v>140897300</v>
       </c>
       <c r="G76" s="3">
-        <v>134759700</v>
+        <v>137582100</v>
       </c>
       <c r="H76" s="3">
-        <v>130891100</v>
+        <v>135677100</v>
       </c>
       <c r="I76" s="3">
-        <v>133004200</v>
+        <v>131782200</v>
       </c>
       <c r="J76" s="3">
+        <v>133909600</v>
+      </c>
+      <c r="K76" s="3">
         <v>130966000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>134238900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>136865400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>140101700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>130495800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130438900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126346900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>119170500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>118265600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>114579000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>94042700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>79603400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74882100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>66935500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>59001500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>56400400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6565,197 +6753,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3825600</v>
+        <v>2006500</v>
       </c>
       <c r="E81" s="3">
-        <v>4740600</v>
+        <v>3851700</v>
       </c>
       <c r="F81" s="3">
-        <v>3247100</v>
+        <v>4772800</v>
       </c>
       <c r="G81" s="3">
-        <v>6464200</v>
+        <v>3269200</v>
       </c>
       <c r="H81" s="3">
-        <v>-2839100</v>
+        <v>6508200</v>
       </c>
       <c r="I81" s="3">
-        <v>3139800</v>
+        <v>-2858400</v>
       </c>
       <c r="J81" s="3">
+        <v>3161200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2814700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>762900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6483200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-762700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11056200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7013000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>495000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8054500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11317000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3246900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3929300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4800100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2803800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1246100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6788,8 +6985,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6880,8 +7078,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6972,8 +7173,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7064,8 +7268,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7156,8 +7363,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7248,8 +7458,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7340,100 +7553,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6797800</v>
+        <v>8996800</v>
       </c>
       <c r="E89" s="3">
-        <v>6255900</v>
+        <v>6844100</v>
       </c>
       <c r="F89" s="3">
-        <v>4335900</v>
+        <v>6298400</v>
       </c>
       <c r="G89" s="3">
-        <v>12064000</v>
+        <v>4365400</v>
       </c>
       <c r="H89" s="3">
-        <v>6505200</v>
+        <v>12146200</v>
       </c>
       <c r="I89" s="3">
-        <v>4676600</v>
+        <v>6549500</v>
       </c>
       <c r="J89" s="3">
+        <v>4708500</v>
+      </c>
+      <c r="K89" s="3">
         <v>-972100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11072800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5093200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4826100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3366300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14366600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8001100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7382600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>338800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14859800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7383300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5288000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2822300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9425100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4395700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5182100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7466,100 +7685,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-20770000</v>
+        <v>-8857000</v>
       </c>
       <c r="E91" s="3">
-        <v>-4098000</v>
+        <v>-5150000</v>
       </c>
       <c r="F91" s="3">
-        <v>-15938000</v>
+        <v>-6927000</v>
       </c>
       <c r="G91" s="3">
-        <v>-12518000</v>
+        <v>-3500000</v>
       </c>
       <c r="H91" s="3">
-        <v>-4993000</v>
+        <v>-6897000</v>
       </c>
       <c r="I91" s="3">
-        <v>-5844000</v>
+        <v>-12112000</v>
       </c>
       <c r="J91" s="3">
-        <v>-18710000</v>
+        <v>-11843000</v>
       </c>
       <c r="K91" s="3">
         <v>-18710000</v>
       </c>
       <c r="L91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="M91" s="3" t="s">
+      <c r="N91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-453500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-813500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-281000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-975000</v>
       </c>
-      <c r="V91" s="3" t="s">
+      <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="Z91" s="3" t="s">
+      <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7650,8 +7873,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7742,100 +7968,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3280900</v>
+        <v>-4299200</v>
       </c>
       <c r="E94" s="3">
-        <v>1739100</v>
+        <v>-3303300</v>
       </c>
       <c r="F94" s="3">
-        <v>-3701600</v>
+        <v>1751000</v>
       </c>
       <c r="G94" s="3">
-        <v>-10072000</v>
+        <v>-3726800</v>
       </c>
       <c r="H94" s="3">
-        <v>-1125100</v>
+        <v>-10140500</v>
       </c>
       <c r="I94" s="3">
-        <v>-3812000</v>
+        <v>-1132700</v>
       </c>
       <c r="J94" s="3">
+        <v>-3837900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7868,8 +8100,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7960,8 +8193,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8052,8 +8288,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8144,8 +8383,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8236,280 +8478,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1709700</v>
+        <v>-2393100</v>
       </c>
       <c r="E100" s="3">
-        <v>-3401700</v>
+        <v>-1721300</v>
       </c>
       <c r="F100" s="3">
-        <v>-1286800</v>
+        <v>-3424900</v>
       </c>
       <c r="G100" s="3">
-        <v>-3287400</v>
+        <v>-1295500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1583800</v>
+        <v>-3309800</v>
       </c>
       <c r="I100" s="3">
-        <v>-2902700</v>
+        <v>-1594600</v>
       </c>
       <c r="J100" s="3">
+        <v>-2922500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4213600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-791400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1489200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-679200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>464500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9437000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>328600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>686400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>109400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-486600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>614200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>361000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>112300</v>
+        <v>-367400</v>
       </c>
       <c r="E101" s="3">
-        <v>596400</v>
+        <v>113000</v>
       </c>
       <c r="F101" s="3">
-        <v>-165800</v>
+        <v>600400</v>
       </c>
       <c r="G101" s="3">
-        <v>-280400</v>
+        <v>-167000</v>
       </c>
       <c r="H101" s="3">
-        <v>474400</v>
+        <v>-282300</v>
       </c>
       <c r="I101" s="3">
-        <v>459300</v>
+        <v>477700</v>
       </c>
       <c r="J101" s="3">
+        <v>462400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-126100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-816200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>27700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-314800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>159900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-575200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-567800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-51700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>363500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>367100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>210400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-173700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-9600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>233700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>399300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>253800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1919500</v>
+        <v>1937100</v>
       </c>
       <c r="E102" s="3">
-        <v>5189600</v>
+        <v>1932500</v>
       </c>
       <c r="F102" s="3">
-        <v>-818400</v>
+        <v>5224900</v>
       </c>
       <c r="G102" s="3">
-        <v>-1575800</v>
+        <v>-824000</v>
       </c>
       <c r="H102" s="3">
-        <v>4270800</v>
+        <v>-1586500</v>
       </c>
       <c r="I102" s="3">
-        <v>-1578800</v>
+        <v>4299900</v>
       </c>
       <c r="J102" s="3">
+        <v>-1589600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3025000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3883800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1904100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18978300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4747700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2955700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>209800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3610700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-277700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>494500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>291500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -656,411 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>36193600</v>
+        <v>30654100</v>
       </c>
       <c r="E8" s="3">
-        <v>31250300</v>
+        <v>35969700</v>
       </c>
       <c r="F8" s="3">
-        <v>32552400</v>
+        <v>31057000</v>
       </c>
       <c r="G8" s="3">
-        <v>28944000</v>
+        <v>32351000</v>
       </c>
       <c r="H8" s="3">
-        <v>34443000</v>
+        <v>28764900</v>
       </c>
       <c r="I8" s="3">
-        <v>28801600</v>
+        <v>34230000</v>
       </c>
       <c r="J8" s="3">
+        <v>28623400</v>
+      </c>
+      <c r="K8" s="3">
         <v>28576300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28175500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33422700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28528100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29548400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26085400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30774900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22849500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22656700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17897000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24861000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18567800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17558100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14222900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17032300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11917300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21716900</v>
+        <v>20461200</v>
       </c>
       <c r="E9" s="3">
-        <v>19416100</v>
+        <v>21582500</v>
       </c>
       <c r="F9" s="3">
-        <v>19789100</v>
+        <v>19296000</v>
       </c>
       <c r="G9" s="3">
-        <v>19299200</v>
+        <v>19666700</v>
       </c>
       <c r="H9" s="3">
-        <v>20853700</v>
+        <v>19179800</v>
       </c>
       <c r="I9" s="3">
-        <v>18240800</v>
+        <v>20724700</v>
       </c>
       <c r="J9" s="3">
+        <v>18128000</v>
+      </c>
+      <c r="K9" s="3">
         <v>18024900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19185500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20206500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18444000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17822800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17463200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16880500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13256500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12455300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11350900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12985400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10225800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9164800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8459400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8831900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6548200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>14476700</v>
+        <v>10192900</v>
       </c>
       <c r="E10" s="3">
-        <v>11834200</v>
+        <v>14387200</v>
       </c>
       <c r="F10" s="3">
-        <v>12763300</v>
+        <v>11761000</v>
       </c>
       <c r="G10" s="3">
-        <v>9644800</v>
+        <v>12684300</v>
       </c>
       <c r="H10" s="3">
-        <v>13589300</v>
+        <v>9585100</v>
       </c>
       <c r="I10" s="3">
-        <v>10560800</v>
+        <v>13505300</v>
       </c>
       <c r="J10" s="3">
+        <v>10495500</v>
+      </c>
+      <c r="K10" s="3">
         <v>10551300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8990000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13216100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10084100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11725600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8622200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13894400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9593000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10201400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6546100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11875600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8342000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8393300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5763500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8200400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5369100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,103 +1106,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1875100</v>
+        <v>1946000</v>
       </c>
       <c r="E12" s="3">
-        <v>1976600</v>
+        <v>1863500</v>
       </c>
       <c r="F12" s="3">
-        <v>1454800</v>
+        <v>1964400</v>
       </c>
       <c r="G12" s="3">
-        <v>1929600</v>
+        <v>1445800</v>
       </c>
       <c r="H12" s="3">
-        <v>1879700</v>
+        <v>1917700</v>
       </c>
       <c r="I12" s="3">
-        <v>2106200</v>
+        <v>1868100</v>
       </c>
       <c r="J12" s="3">
+        <v>2093100</v>
+      </c>
+      <c r="K12" s="3">
         <v>1973100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1511100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2163800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2174500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1941600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1851600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1894100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2835900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1633000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1657500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1705600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1706400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1600800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1317200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1292700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1170800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>959300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>933400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>754400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>696900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>657100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>642800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1284,198 +1300,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1180300</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1173000</v>
       </c>
       <c r="F14" s="3">
-        <v>282300</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>280600</v>
       </c>
       <c r="H14" s="3">
-        <v>377300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>375000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>89900</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3">
         <v>309000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2029800</v>
+        <v>287500</v>
       </c>
       <c r="E15" s="3">
-        <v>338000</v>
+        <v>2017300</v>
       </c>
       <c r="F15" s="3">
+        <v>335900</v>
+      </c>
+      <c r="G15" s="3">
+        <v>342500</v>
+      </c>
+      <c r="H15" s="3">
         <v>344600</v>
       </c>
-      <c r="G15" s="3">
-        <v>346700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>768800</v>
-      </c>
       <c r="I15" s="3">
-        <v>379400</v>
+        <v>764000</v>
       </c>
       <c r="J15" s="3">
+        <v>377000</v>
+      </c>
+      <c r="K15" s="3">
         <v>382400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>390900</v>
       </c>
       <c r="L15" s="3">
         <v>390900</v>
       </c>
       <c r="M15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="N15" s="3">
         <v>413100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>441300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>475400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>441500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>425600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>435000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>633100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>503800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>469000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>468400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>487200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>408000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>365400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>301900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>190700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>305300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>259400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>294700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>190900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>183400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1506,198 +1531,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>33064100</v>
+        <v>28614200</v>
       </c>
       <c r="E17" s="3">
-        <v>26581500</v>
+        <v>32859600</v>
       </c>
       <c r="F17" s="3">
-        <v>26645400</v>
+        <v>26417000</v>
       </c>
       <c r="G17" s="3">
-        <v>26825300</v>
+        <v>26480600</v>
       </c>
       <c r="H17" s="3">
-        <v>29573000</v>
+        <v>26659400</v>
       </c>
       <c r="I17" s="3">
-        <v>25307100</v>
+        <v>29390100</v>
       </c>
       <c r="J17" s="3">
+        <v>25150500</v>
+      </c>
+      <c r="K17" s="3">
         <v>25108700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25867200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32448800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26395000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25118100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27152100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23953800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20840400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17542600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16780600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18769500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15390900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13834100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12889600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13140400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10027700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3129500</v>
+        <v>2039900</v>
       </c>
       <c r="E18" s="3">
-        <v>4668800</v>
+        <v>3110100</v>
       </c>
       <c r="F18" s="3">
-        <v>5907000</v>
+        <v>4640000</v>
       </c>
       <c r="G18" s="3">
-        <v>2118700</v>
+        <v>5870400</v>
       </c>
       <c r="H18" s="3">
-        <v>4870000</v>
+        <v>2105600</v>
       </c>
       <c r="I18" s="3">
-        <v>3494500</v>
+        <v>4839900</v>
       </c>
       <c r="J18" s="3">
+        <v>3472900</v>
+      </c>
+      <c r="K18" s="3">
         <v>3467600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2308300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>973800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2133100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4430200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6821100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2009100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5114100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1116400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6091400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3177000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3724000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1333300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3891900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1889600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1731,177 +1763,181 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-425500</v>
+        <v>-378400</v>
       </c>
       <c r="E20" s="3">
-        <v>907400</v>
+        <v>-422900</v>
       </c>
       <c r="F20" s="3">
-        <v>-630300</v>
+        <v>901800</v>
       </c>
       <c r="G20" s="3">
-        <v>1641000</v>
+        <v>-626400</v>
       </c>
       <c r="H20" s="3">
-        <v>2360300</v>
+        <v>1630800</v>
       </c>
       <c r="I20" s="3">
-        <v>-5492400</v>
+        <v>2345700</v>
       </c>
       <c r="J20" s="3">
+        <v>-5458400</v>
+      </c>
+      <c r="K20" s="3">
         <v>761600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3230100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2335000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>309900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5966400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1717900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3482100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2790600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10377600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>349600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3059700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1735100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>714200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>405900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>767600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>498500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>560200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4442700</v>
+        <v>-53200</v>
       </c>
       <c r="E21" s="3">
-        <v>5529400</v>
+        <v>4415200</v>
       </c>
       <c r="F21" s="3">
-        <v>6550100</v>
+        <v>5495200</v>
       </c>
       <c r="G21" s="3">
-        <v>3299900</v>
+        <v>6509500</v>
       </c>
       <c r="H21" s="3">
-        <v>7615100</v>
+        <v>3279500</v>
       </c>
       <c r="I21" s="3">
-        <v>-1938100</v>
+        <v>7568000</v>
       </c>
       <c r="J21" s="3">
+        <v>-1926100</v>
+      </c>
+      <c r="K21" s="3">
         <v>5542300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4157900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>704500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8197100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>564900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12940900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3812200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9866300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1609300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8955000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13596400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5257300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4411900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5740800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2772500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>10</v>
@@ -1912,302 +1948,314 @@
       <c r="AD21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>296400</v>
+        <v>300800</v>
       </c>
       <c r="E22" s="3">
-        <v>257700</v>
+        <v>294600</v>
       </c>
       <c r="F22" s="3">
-        <v>248000</v>
+        <v>256100</v>
       </c>
       <c r="G22" s="3">
-        <v>241300</v>
+        <v>246500</v>
       </c>
       <c r="H22" s="3">
-        <v>215500</v>
+        <v>239800</v>
       </c>
       <c r="I22" s="3">
-        <v>193000</v>
+        <v>214100</v>
       </c>
       <c r="J22" s="3">
+        <v>191800</v>
+      </c>
+      <c r="K22" s="3">
         <v>172900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>164200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>163400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>180100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>182000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>161500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>152000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>162200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>165500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>182400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>201600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>212200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>205600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>198200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>193700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>187500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>174000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>168600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>125300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>110900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>118700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>98300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>101900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2407500</v>
+        <v>1360700</v>
       </c>
       <c r="E23" s="3">
-        <v>5318500</v>
+        <v>2392700</v>
       </c>
       <c r="F23" s="3">
-        <v>5028600</v>
+        <v>5285600</v>
       </c>
       <c r="G23" s="3">
-        <v>3518300</v>
+        <v>4997500</v>
       </c>
       <c r="H23" s="3">
-        <v>7014800</v>
+        <v>3496600</v>
       </c>
       <c r="I23" s="3">
-        <v>-2190800</v>
+        <v>6971400</v>
       </c>
       <c r="J23" s="3">
+        <v>-2177300</v>
+      </c>
+      <c r="K23" s="3">
         <v>4056200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4040500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>560900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6583300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-918300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12635500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3564800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8430800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-89100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8680500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13342400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3867900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4194900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5433200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2416300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>693400</v>
+        <v>790600</v>
       </c>
       <c r="E24" s="3">
-        <v>805900</v>
+        <v>689100</v>
       </c>
       <c r="F24" s="3">
-        <v>837200</v>
+        <v>800900</v>
       </c>
       <c r="G24" s="3">
-        <v>522400</v>
+        <v>832000</v>
       </c>
       <c r="H24" s="3">
-        <v>531100</v>
+        <v>519200</v>
       </c>
       <c r="I24" s="3">
-        <v>357600</v>
+        <v>527800</v>
       </c>
       <c r="J24" s="3">
+        <v>355300</v>
+      </c>
+      <c r="K24" s="3">
         <v>750600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>287100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1316200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>865300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1306400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>981200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1279800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>281600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1639200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>411400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1294500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>439200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1025500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>764400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>811300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>38800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>812800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>597500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>988900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>403500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>690600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>662100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>743100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2301,198 +2349,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1714100</v>
+        <v>570200</v>
       </c>
       <c r="E26" s="3">
-        <v>4512600</v>
+        <v>1703500</v>
       </c>
       <c r="F26" s="3">
-        <v>4191500</v>
+        <v>4484700</v>
       </c>
       <c r="G26" s="3">
-        <v>2995900</v>
+        <v>4165500</v>
       </c>
       <c r="H26" s="3">
-        <v>6483800</v>
+        <v>2977300</v>
       </c>
       <c r="I26" s="3">
-        <v>-2548400</v>
+        <v>6443600</v>
       </c>
       <c r="J26" s="3">
+        <v>-2532600</v>
+      </c>
+      <c r="K26" s="3">
         <v>3305600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2724300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-304300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5276900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11355700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3283200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6791500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7386000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12903300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2842500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3430500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4621900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2377500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>962900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2006500</v>
+        <v>451800</v>
       </c>
       <c r="E27" s="3">
-        <v>3851700</v>
+        <v>1994100</v>
       </c>
       <c r="F27" s="3">
-        <v>4772800</v>
+        <v>3827900</v>
       </c>
       <c r="G27" s="3">
-        <v>3269200</v>
+        <v>4743300</v>
       </c>
       <c r="H27" s="3">
-        <v>6508200</v>
+        <v>3249000</v>
       </c>
       <c r="I27" s="3">
-        <v>-2858400</v>
+        <v>6468000</v>
       </c>
       <c r="J27" s="3">
+        <v>-2840700</v>
+      </c>
+      <c r="K27" s="3">
         <v>3161200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2814700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>762900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6483200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-762700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11056200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4239400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7013000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>495000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8054500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11317000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3246900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3929300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2803800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2586,8 +2643,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2681,8 +2741,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2776,8 +2839,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2871,198 +2937,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>425500</v>
+        <v>378400</v>
       </c>
       <c r="E32" s="3">
-        <v>-907400</v>
+        <v>422900</v>
       </c>
       <c r="F32" s="3">
-        <v>630300</v>
+        <v>-901800</v>
       </c>
       <c r="G32" s="3">
-        <v>-1641000</v>
+        <v>626400</v>
       </c>
       <c r="H32" s="3">
-        <v>-2360300</v>
+        <v>-1630800</v>
       </c>
       <c r="I32" s="3">
-        <v>5492400</v>
+        <v>-2345700</v>
       </c>
       <c r="J32" s="3">
+        <v>5458400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-761600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4845000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1392100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-309900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1023100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-349600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-714200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2006500</v>
+        <v>451800</v>
       </c>
       <c r="E33" s="3">
-        <v>3851700</v>
+        <v>1994100</v>
       </c>
       <c r="F33" s="3">
-        <v>4772800</v>
+        <v>3827900</v>
       </c>
       <c r="G33" s="3">
-        <v>3269200</v>
+        <v>4743300</v>
       </c>
       <c r="H33" s="3">
-        <v>6508200</v>
+        <v>3249000</v>
       </c>
       <c r="I33" s="3">
-        <v>-2858400</v>
+        <v>6468000</v>
       </c>
       <c r="J33" s="3">
+        <v>-2840700</v>
+      </c>
+      <c r="K33" s="3">
         <v>3161200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2814700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>762900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6483200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-762700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11056200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4239400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7013000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>495000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8054500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11317000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3246900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3929300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4800100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2803800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3156,203 +3231,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2006500</v>
+        <v>451800</v>
       </c>
       <c r="E35" s="3">
-        <v>3851700</v>
+        <v>1994100</v>
       </c>
       <c r="F35" s="3">
-        <v>4772800</v>
+        <v>3827900</v>
       </c>
       <c r="G35" s="3">
-        <v>3269200</v>
+        <v>4743300</v>
       </c>
       <c r="H35" s="3">
-        <v>6508200</v>
+        <v>3249000</v>
       </c>
       <c r="I35" s="3">
-        <v>-2858400</v>
+        <v>6468000</v>
       </c>
       <c r="J35" s="3">
+        <v>-2840700</v>
+      </c>
+      <c r="K35" s="3">
         <v>3161200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2814700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>762900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6483200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-762700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11056200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4239400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7013000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>495000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8054500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11317000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3246900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3929300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4800100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2803800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3386,8 +3470,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3421,198 +3506,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>35422900</v>
+        <v>34281000</v>
       </c>
       <c r="E41" s="3">
-        <v>33881400</v>
+        <v>35203700</v>
       </c>
       <c r="F41" s="3">
-        <v>31474800</v>
+        <v>33671800</v>
       </c>
       <c r="G41" s="3">
-        <v>26842800</v>
+        <v>31280100</v>
       </c>
       <c r="H41" s="3">
-        <v>27143500</v>
+        <v>26676800</v>
       </c>
       <c r="I41" s="3">
-        <v>28737000</v>
+        <v>26975600</v>
       </c>
       <c r="J41" s="3">
+        <v>28559200</v>
+      </c>
+      <c r="K41" s="3">
         <v>24569300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26221100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40385100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38694100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41909600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44719700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43449500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44430400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45573600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>51743500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53981500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36534000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>32166100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28899100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27478100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>23005900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>49990900</v>
+        <v>44612400</v>
       </c>
       <c r="E42" s="3">
-        <v>45966100</v>
+        <v>49681600</v>
       </c>
       <c r="F42" s="3">
-        <v>44211700</v>
+        <v>45681800</v>
       </c>
       <c r="G42" s="3">
-        <v>46069000</v>
+        <v>43938200</v>
       </c>
       <c r="H42" s="3">
-        <v>45037500</v>
+        <v>45784000</v>
       </c>
       <c r="I42" s="3">
-        <v>38981100</v>
+        <v>44758900</v>
       </c>
       <c r="J42" s="3">
+        <v>38739900</v>
+      </c>
+      <c r="K42" s="3">
         <v>39836300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36617000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27806800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26581900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27509400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22575900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20883300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16090800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11389600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5121400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1021700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1066000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1540200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2006300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1653700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2402000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3706,8 +3798,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3801,483 +3896,501 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>26809000</v>
+        <v>25122300</v>
       </c>
       <c r="E45" s="3">
-        <v>25523500</v>
+        <v>26643200</v>
       </c>
       <c r="F45" s="3">
-        <v>25858600</v>
+        <v>25365600</v>
       </c>
       <c r="G45" s="3">
-        <v>24119400</v>
+        <v>25698600</v>
       </c>
       <c r="H45" s="3">
-        <v>29077800</v>
+        <v>23970200</v>
       </c>
       <c r="I45" s="3">
-        <v>26497100</v>
+        <v>28898000</v>
       </c>
       <c r="J45" s="3">
+        <v>26333200</v>
+      </c>
+      <c r="K45" s="3">
         <v>25257300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25330800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24828600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25422400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23522800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22260200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18870600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16538500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15436500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15610300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15742300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14770600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10696400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10208500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8872000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7886200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>112222800</v>
+        <v>104015700</v>
       </c>
       <c r="E46" s="3">
-        <v>105371000</v>
+        <v>111528600</v>
       </c>
       <c r="F46" s="3">
-        <v>101545100</v>
+        <v>104719200</v>
       </c>
       <c r="G46" s="3">
-        <v>97031200</v>
+        <v>100916900</v>
       </c>
       <c r="H46" s="3">
-        <v>101258800</v>
+        <v>96431000</v>
       </c>
       <c r="I46" s="3">
-        <v>94215100</v>
+        <v>100632400</v>
       </c>
       <c r="J46" s="3">
+        <v>93632300</v>
+      </c>
+      <c r="K46" s="3">
         <v>89662900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>88168900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>93020500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>90698400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>92941800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>89555700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>83203500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>77059700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>72399700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>72475200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>70745500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>52370500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>44402800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>41113900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>38003800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33294100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>59667900</v>
+        <v>58589900</v>
       </c>
       <c r="E47" s="3">
-        <v>63408300</v>
+        <v>59298800</v>
       </c>
       <c r="F47" s="3">
-        <v>62789800</v>
+        <v>63016000</v>
       </c>
       <c r="G47" s="3">
-        <v>62992300</v>
+        <v>62401300</v>
       </c>
       <c r="H47" s="3">
-        <v>60628400</v>
+        <v>62602600</v>
       </c>
       <c r="I47" s="3">
-        <v>58132700</v>
+        <v>60253400</v>
       </c>
       <c r="J47" s="3">
+        <v>57773100</v>
+      </c>
+      <c r="K47" s="3">
         <v>62111600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61204400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65630300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65584300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65281500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>60887500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>59266900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>58735200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>55079600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>54946500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55746500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>51631700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>38852700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>36743700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>33087900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>30691800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>25247100</v>
+        <v>25581800</v>
       </c>
       <c r="E48" s="3">
-        <v>24945200</v>
+        <v>25091000</v>
       </c>
       <c r="F48" s="3">
-        <v>24447900</v>
+        <v>24790900</v>
       </c>
       <c r="G48" s="3">
-        <v>24471800</v>
+        <v>24296700</v>
       </c>
       <c r="H48" s="3">
-        <v>24717200</v>
+        <v>24320400</v>
       </c>
       <c r="I48" s="3">
-        <v>24963400</v>
+        <v>24564300</v>
       </c>
       <c r="J48" s="3">
+        <v>24809000</v>
+      </c>
+      <c r="K48" s="3">
         <v>24719400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34500500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22741400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22326900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21917300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20519800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20473800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17393900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16424900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21612600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19466200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19627200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18193700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13999600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13188900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12180000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>40020700</v>
+        <v>39600700</v>
       </c>
       <c r="E49" s="3">
-        <v>42860600</v>
+        <v>39773100</v>
       </c>
       <c r="F49" s="3">
-        <v>43255200</v>
+        <v>42595400</v>
       </c>
       <c r="G49" s="3">
-        <v>43791900</v>
+        <v>42987700</v>
       </c>
       <c r="H49" s="3">
-        <v>44079500</v>
+        <v>43521000</v>
       </c>
       <c r="I49" s="3">
-        <v>45243900</v>
+        <v>43806800</v>
       </c>
       <c r="J49" s="3">
+        <v>44964000</v>
+      </c>
+      <c r="K49" s="3">
         <v>45496200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45402400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45628900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>51142200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>51691900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>50613700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>51132800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>49004600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>49288400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>52874900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>52626800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>53469800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>50862400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>50688100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45348800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>35607600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4371,8 +4484,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4466,103 +4582,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15992200</v>
+        <v>16040700</v>
       </c>
       <c r="E52" s="3">
-        <v>15262200</v>
+        <v>15893200</v>
       </c>
       <c r="F52" s="3">
-        <v>14973300</v>
+        <v>15167800</v>
       </c>
       <c r="G52" s="3">
-        <v>15420900</v>
+        <v>14880700</v>
       </c>
       <c r="H52" s="3">
-        <v>15676700</v>
+        <v>15325500</v>
       </c>
       <c r="I52" s="3">
-        <v>15522700</v>
+        <v>15579800</v>
       </c>
       <c r="J52" s="3">
+        <v>15426700</v>
+      </c>
+      <c r="K52" s="3">
         <v>15507100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4845800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15549900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15552800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14506300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13701700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13552100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9065700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8569300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3651800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4590900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3806500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3348900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4262100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3683500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3660800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4656,103 +4778,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>253150700</v>
+        <v>243828800</v>
       </c>
       <c r="E54" s="3">
-        <v>251847200</v>
+        <v>251584700</v>
       </c>
       <c r="F54" s="3">
-        <v>247011300</v>
+        <v>250289300</v>
       </c>
       <c r="G54" s="3">
-        <v>243708200</v>
+        <v>245483200</v>
       </c>
       <c r="H54" s="3">
-        <v>246360700</v>
+        <v>242200600</v>
       </c>
       <c r="I54" s="3">
-        <v>238077900</v>
+        <v>244836700</v>
       </c>
       <c r="J54" s="3">
+        <v>236605100</v>
+      </c>
+      <c r="K54" s="3">
         <v>237497300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>234122000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>242570900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>245304600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>246338700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>235278300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>227629000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>211259100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>201761900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>205560900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>203175800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>180905600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>155660500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>146807400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>133312900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>115434400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4786,8 +4914,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4821,62 +4950,63 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>43824900</v>
+        <v>41155500</v>
       </c>
       <c r="E57" s="3">
-        <v>39843700</v>
+        <v>43553800</v>
       </c>
       <c r="F57" s="3">
-        <v>38835400</v>
+        <v>39597200</v>
       </c>
       <c r="G57" s="3">
-        <v>38362600</v>
+        <v>38595100</v>
       </c>
       <c r="H57" s="3">
-        <v>40825400</v>
+        <v>38125300</v>
       </c>
       <c r="I57" s="3">
-        <v>37794400</v>
+        <v>40572900</v>
       </c>
       <c r="J57" s="3">
+        <v>37560600</v>
+      </c>
+      <c r="K57" s="3">
         <v>36918600</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="L57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38835600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37802900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35961600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36321300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>31307500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26279700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24271800</v>
       </c>
-      <c r="S57" s="3" t="s">
+      <c r="T57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
@@ -4916,483 +5046,501 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3663700</v>
+        <v>4006800</v>
       </c>
       <c r="E58" s="3">
-        <v>1138200</v>
+        <v>3641100</v>
       </c>
       <c r="F58" s="3">
-        <v>1145000</v>
+        <v>1131100</v>
       </c>
       <c r="G58" s="3">
-        <v>1705200</v>
+        <v>1137900</v>
       </c>
       <c r="H58" s="3">
-        <v>1607800</v>
+        <v>1694700</v>
       </c>
       <c r="I58" s="3">
-        <v>1612900</v>
+        <v>1597800</v>
       </c>
       <c r="J58" s="3">
+        <v>1602900</v>
+      </c>
+      <c r="K58" s="3">
         <v>1883600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1220800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1089300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2679000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2443400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1870400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2094500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>722500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>669500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>806900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>649000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3768400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3516800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3417500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3313000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1262700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>864900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>956800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14897100</v>
+        <v>13073100</v>
       </c>
       <c r="E59" s="3">
-        <v>13209500</v>
+        <v>14804900</v>
       </c>
       <c r="F59" s="3">
-        <v>12880500</v>
+        <v>13127800</v>
       </c>
       <c r="G59" s="3">
-        <v>13503700</v>
+        <v>12800800</v>
       </c>
       <c r="H59" s="3">
-        <v>15654200</v>
+        <v>13420200</v>
       </c>
       <c r="I59" s="3">
-        <v>13818000</v>
+        <v>15557400</v>
       </c>
       <c r="J59" s="3">
+        <v>13732600</v>
+      </c>
+      <c r="K59" s="3">
         <v>13411500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51772100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16634700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14652800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14475700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14336500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16453900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11744900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11617700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>37060600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>39764300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34290100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>28673900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>28173100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27007000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22264000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>62385800</v>
+        <v>58235400</v>
       </c>
       <c r="E60" s="3">
-        <v>54191400</v>
+        <v>61999900</v>
       </c>
       <c r="F60" s="3">
-        <v>52860800</v>
+        <v>53856100</v>
       </c>
       <c r="G60" s="3">
-        <v>53571500</v>
+        <v>52533800</v>
       </c>
       <c r="H60" s="3">
-        <v>58087400</v>
+        <v>53240100</v>
       </c>
       <c r="I60" s="3">
-        <v>53225300</v>
+        <v>57728100</v>
       </c>
       <c r="J60" s="3">
+        <v>52896100</v>
+      </c>
+      <c r="K60" s="3">
         <v>52213700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52992900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56559700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55134700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52880700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52528200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>49855900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38747100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36559000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>37867500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>40413300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38058500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32190700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31590600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30320000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23526700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19403300</v>
+        <v>19587600</v>
       </c>
       <c r="E61" s="3">
-        <v>22042600</v>
+        <v>19283300</v>
       </c>
       <c r="F61" s="3">
-        <v>21868800</v>
+        <v>21906200</v>
       </c>
       <c r="G61" s="3">
-        <v>20726200</v>
+        <v>21733500</v>
       </c>
       <c r="H61" s="3">
-        <v>20611100</v>
+        <v>20598000</v>
       </c>
       <c r="I61" s="3">
-        <v>20830500</v>
+        <v>20483600</v>
       </c>
       <c r="J61" s="3">
+        <v>20701600</v>
+      </c>
+      <c r="K61" s="3">
         <v>19249000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18296000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18149900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18892700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19187500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18891700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14289200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17224200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17814900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18830400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18196100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18958600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17779000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17012200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16446000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18082000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12541000</v>
+        <v>12289100</v>
       </c>
       <c r="E62" s="3">
-        <v>12953500</v>
+        <v>12463400</v>
       </c>
       <c r="F62" s="3">
-        <v>12820000</v>
+        <v>12873300</v>
       </c>
       <c r="G62" s="3">
-        <v>13302000</v>
+        <v>12740700</v>
       </c>
       <c r="H62" s="3">
-        <v>13380100</v>
+        <v>13219700</v>
       </c>
       <c r="I62" s="3">
-        <v>13536800</v>
+        <v>13297300</v>
       </c>
       <c r="J62" s="3">
+        <v>13453100</v>
+      </c>
+      <c r="K62" s="3">
         <v>13622800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13403800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13526600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13729800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13614700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13016600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12820300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10694800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10566900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11144900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11048800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10354200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7139000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4589600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4043600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3657000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5486,8 +5634,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5581,8 +5732,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5676,103 +5830,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>112658500</v>
+        <v>107527900</v>
       </c>
       <c r="E66" s="3">
-        <v>107950100</v>
+        <v>111961500</v>
       </c>
       <c r="F66" s="3">
-        <v>106114000</v>
+        <v>107282300</v>
       </c>
       <c r="G66" s="3">
-        <v>106126100</v>
+        <v>105457500</v>
       </c>
       <c r="H66" s="3">
-        <v>110683600</v>
+        <v>105469500</v>
       </c>
       <c r="I66" s="3">
-        <v>106295700</v>
+        <v>109998800</v>
       </c>
       <c r="J66" s="3">
+        <v>105638100</v>
+      </c>
+      <c r="K66" s="3">
         <v>103587700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103156000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>106870400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106961600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>105035900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103575200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>96014900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>83728500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>81439100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>85870200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>87396600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>85691900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>74973700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70887900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>65336800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55593000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5806,8 +5966,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5901,8 +6062,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5996,8 +6160,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6026,73 +6193,76 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>1461600</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1477500</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1201100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1207300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1175300</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1183700</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1152400</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1425200</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1200300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1171000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1083400</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1037300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1040600</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>839900</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>452700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>430600</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>442100</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>133300</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>113200</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>435100</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>515800</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6186,103 +6356,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>87801700</v>
+        <v>84641000</v>
       </c>
       <c r="E72" s="3">
-        <v>90374000</v>
+        <v>87258500</v>
       </c>
       <c r="F72" s="3">
-        <v>87711100</v>
+        <v>89814900</v>
       </c>
       <c r="G72" s="3">
-        <v>85080900</v>
+        <v>87168500</v>
       </c>
       <c r="H72" s="3">
-        <v>83083100</v>
+        <v>84554600</v>
       </c>
       <c r="I72" s="3">
-        <v>77445500</v>
+        <v>82569100</v>
       </c>
       <c r="J72" s="3">
+        <v>76966400</v>
+      </c>
+      <c r="K72" s="3">
         <v>80286100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>79174500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>81449200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>82138400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>86310300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>78268100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>79111700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>72029000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>67773800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>64563300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>63003500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>55694500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>43446200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39985800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34455500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>29692900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6376,8 +6552,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6471,8 +6650,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6566,103 +6748,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>140492200</v>
+        <v>136300900</v>
       </c>
       <c r="E76" s="3">
-        <v>143897100</v>
+        <v>139623100</v>
       </c>
       <c r="F76" s="3">
-        <v>140897300</v>
+        <v>143006900</v>
       </c>
       <c r="G76" s="3">
-        <v>137582100</v>
+        <v>140025700</v>
       </c>
       <c r="H76" s="3">
-        <v>135677100</v>
+        <v>136731000</v>
       </c>
       <c r="I76" s="3">
-        <v>131782200</v>
+        <v>134837800</v>
       </c>
       <c r="J76" s="3">
+        <v>130967000</v>
+      </c>
+      <c r="K76" s="3">
         <v>133909600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>130966000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>134238900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>136865400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>140101700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130495800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>130438900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>126346900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>119170500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>118265600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>114579000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>94042700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>79603400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>74882100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>66935500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59001500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6756,203 +6944,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2006500</v>
+        <v>451800</v>
       </c>
       <c r="E81" s="3">
-        <v>3851700</v>
+        <v>1994100</v>
       </c>
       <c r="F81" s="3">
-        <v>4772800</v>
+        <v>3827900</v>
       </c>
       <c r="G81" s="3">
-        <v>3269200</v>
+        <v>4743300</v>
       </c>
       <c r="H81" s="3">
-        <v>6508200</v>
+        <v>3249000</v>
       </c>
       <c r="I81" s="3">
-        <v>-2858400</v>
+        <v>6468000</v>
       </c>
       <c r="J81" s="3">
+        <v>-2840700</v>
+      </c>
+      <c r="K81" s="3">
         <v>3161200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2814700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>762900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6483200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-762700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11056200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4239400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7013000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>495000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8054500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11317000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3246900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3929300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4800100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2803800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6986,8 +7183,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7081,8 +7279,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7176,8 +7377,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7271,8 +7475,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7366,8 +7573,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7461,8 +7671,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7556,103 +7769,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8996800</v>
+        <v>3224700</v>
       </c>
       <c r="E89" s="3">
-        <v>6844100</v>
+        <v>8941200</v>
       </c>
       <c r="F89" s="3">
-        <v>6298400</v>
+        <v>6801800</v>
       </c>
       <c r="G89" s="3">
-        <v>4365400</v>
+        <v>6259500</v>
       </c>
       <c r="H89" s="3">
-        <v>12146200</v>
+        <v>4338400</v>
       </c>
       <c r="I89" s="3">
-        <v>6549500</v>
+        <v>12071000</v>
       </c>
       <c r="J89" s="3">
+        <v>6509000</v>
+      </c>
+      <c r="K89" s="3">
         <v>4708500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-972100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11072800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5093200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4826100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3366300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14366600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8001100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7382600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>338800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14859800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7383300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5288000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2822300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9425100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4395700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7686,103 +7905,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11995000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8857000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5150000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6927000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="L91" s="3">
         <v>-18710000</v>
       </c>
       <c r="M91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-453500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-813500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-281000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-975000</v>
       </c>
-      <c r="W91" s="3" t="s">
+      <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AA91" s="3" t="s">
+      <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7876,8 +8099,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7971,103 +8197,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4299200</v>
+        <v>2800100</v>
       </c>
       <c r="E94" s="3">
-        <v>-3303300</v>
+        <v>-4272600</v>
       </c>
       <c r="F94" s="3">
-        <v>1751000</v>
+        <v>-3282800</v>
       </c>
       <c r="G94" s="3">
-        <v>-3726800</v>
+        <v>1740100</v>
       </c>
       <c r="H94" s="3">
-        <v>-10140500</v>
+        <v>-3703800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1132700</v>
+        <v>-10077800</v>
       </c>
       <c r="J94" s="3">
+        <v>-1125700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8101,8 +8333,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8196,8 +8429,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8291,8 +8527,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8386,8 +8625,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8481,289 +8723,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2393100</v>
+        <v>-7462300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1721300</v>
+        <v>-2378300</v>
       </c>
       <c r="F100" s="3">
-        <v>-3424900</v>
+        <v>-1710700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1295500</v>
+        <v>-3403700</v>
       </c>
       <c r="H100" s="3">
-        <v>-3309800</v>
+        <v>-1287500</v>
       </c>
       <c r="I100" s="3">
-        <v>-1594600</v>
+        <v>-3289300</v>
       </c>
       <c r="J100" s="3">
+        <v>-1584700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4213600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-791400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1489200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-679200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>464500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9437000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>328600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>686400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>109400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-486600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>614200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>361000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-367400</v>
+        <v>262500</v>
       </c>
       <c r="E101" s="3">
-        <v>113000</v>
+        <v>-365200</v>
       </c>
       <c r="F101" s="3">
-        <v>600400</v>
+        <v>112300</v>
       </c>
       <c r="G101" s="3">
-        <v>-167000</v>
+        <v>596700</v>
       </c>
       <c r="H101" s="3">
-        <v>-282300</v>
+        <v>-165900</v>
       </c>
       <c r="I101" s="3">
-        <v>477700</v>
+        <v>-280600</v>
       </c>
       <c r="J101" s="3">
+        <v>474700</v>
+      </c>
+      <c r="K101" s="3">
         <v>462400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-126100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-816200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>27700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-314800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>159900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-575200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-567800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-51700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>363500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>367100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>210400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-173700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>233700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>399300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>253800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1937100</v>
+        <v>-1175100</v>
       </c>
       <c r="E102" s="3">
-        <v>1932500</v>
+        <v>1925100</v>
       </c>
       <c r="F102" s="3">
-        <v>5224900</v>
+        <v>1920600</v>
       </c>
       <c r="G102" s="3">
-        <v>-824000</v>
+        <v>5192600</v>
       </c>
       <c r="H102" s="3">
-        <v>-1586500</v>
+        <v>-818900</v>
       </c>
       <c r="I102" s="3">
-        <v>4299900</v>
+        <v>-1576700</v>
       </c>
       <c r="J102" s="3">
+        <v>4273300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3025000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3883800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1904100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18978300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4747700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2955700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>209800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3610700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-277700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>494500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>291500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,423 +656,435 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>30654100</v>
+        <v>34291400</v>
       </c>
       <c r="E8" s="3">
-        <v>35969700</v>
+        <v>31279800</v>
       </c>
       <c r="F8" s="3">
-        <v>31057000</v>
+        <v>36703900</v>
       </c>
       <c r="G8" s="3">
-        <v>32351000</v>
+        <v>31690900</v>
       </c>
       <c r="H8" s="3">
-        <v>28764900</v>
+        <v>33011300</v>
       </c>
       <c r="I8" s="3">
-        <v>34230000</v>
+        <v>29352000</v>
       </c>
       <c r="J8" s="3">
+        <v>34928600</v>
+      </c>
+      <c r="K8" s="3">
         <v>28623400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28576300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28175500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33422700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>28528100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29548400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26085400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30774900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22849500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22656700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17897000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24861000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18567800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17558100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14222900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17032300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20461200</v>
+        <v>20598000</v>
       </c>
       <c r="E9" s="3">
-        <v>21582500</v>
+        <v>20878900</v>
       </c>
       <c r="F9" s="3">
-        <v>19296000</v>
+        <v>22023000</v>
       </c>
       <c r="G9" s="3">
-        <v>19666700</v>
+        <v>19689800</v>
       </c>
       <c r="H9" s="3">
-        <v>19179800</v>
+        <v>20068100</v>
       </c>
       <c r="I9" s="3">
-        <v>20724700</v>
+        <v>19571300</v>
       </c>
       <c r="J9" s="3">
+        <v>21147700</v>
+      </c>
+      <c r="K9" s="3">
         <v>18128000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18024900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19185500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20206500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18444000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17822800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17463200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16880500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13256500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12455300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11350900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12985400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10225800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9164800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8459400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8831900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10192900</v>
+        <v>13693400</v>
       </c>
       <c r="E10" s="3">
-        <v>14387200</v>
+        <v>10400900</v>
       </c>
       <c r="F10" s="3">
-        <v>11761000</v>
+        <v>14680800</v>
       </c>
       <c r="G10" s="3">
-        <v>12684300</v>
+        <v>12001100</v>
       </c>
       <c r="H10" s="3">
-        <v>9585100</v>
+        <v>12943200</v>
       </c>
       <c r="I10" s="3">
-        <v>13505300</v>
+        <v>9780800</v>
       </c>
       <c r="J10" s="3">
+        <v>13780900</v>
+      </c>
+      <c r="K10" s="3">
         <v>10495500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10551300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8990000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13216100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10084100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11725600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8622200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13894400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9593000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10201400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6546100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11875600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8342000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8393300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5763500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8200400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1107,106 +1119,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1946000</v>
+        <v>1885300</v>
       </c>
       <c r="E12" s="3">
-        <v>1863500</v>
+        <v>1985700</v>
       </c>
       <c r="F12" s="3">
-        <v>1964400</v>
+        <v>1901500</v>
       </c>
       <c r="G12" s="3">
-        <v>1445800</v>
+        <v>2004500</v>
       </c>
       <c r="H12" s="3">
-        <v>1917700</v>
+        <v>1475400</v>
       </c>
       <c r="I12" s="3">
-        <v>1868100</v>
+        <v>1956800</v>
       </c>
       <c r="J12" s="3">
+        <v>1906200</v>
+      </c>
+      <c r="K12" s="3">
         <v>2093100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1973100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1511100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2163800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2174500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1941600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1851600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1894100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2835900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1633000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1657500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1705600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1706400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1600800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1317200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1292700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>959300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>933400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>754400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>696900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>657100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>642800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,204 +1319,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>1173000</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1196900</v>
       </c>
       <c r="G14" s="3">
-        <v>280600</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>286300</v>
       </c>
       <c r="I14" s="3">
-        <v>375000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>382600</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>89900</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
         <v>309000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>287500</v>
+        <v>252600</v>
       </c>
       <c r="E15" s="3">
-        <v>2017300</v>
+        <v>293400</v>
       </c>
       <c r="F15" s="3">
-        <v>335900</v>
+        <v>2058400</v>
       </c>
       <c r="G15" s="3">
-        <v>342500</v>
+        <v>342700</v>
       </c>
       <c r="H15" s="3">
-        <v>344600</v>
+        <v>349500</v>
       </c>
       <c r="I15" s="3">
-        <v>764000</v>
+        <v>351600</v>
       </c>
       <c r="J15" s="3">
+        <v>779600</v>
+      </c>
+      <c r="K15" s="3">
         <v>377000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>382400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>390900</v>
       </c>
       <c r="M15" s="3">
         <v>390900</v>
       </c>
       <c r="N15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="O15" s="3">
         <v>413100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>441300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>475400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>441500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>425600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>435000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>633100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>503800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>469000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>468400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>487200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>408000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>365400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>301900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>190700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>305300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>259400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>294700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>190900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>183400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1532,204 +1557,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>28614200</v>
+        <v>29217700</v>
       </c>
       <c r="E17" s="3">
-        <v>32859600</v>
+        <v>29198200</v>
       </c>
       <c r="F17" s="3">
-        <v>26417000</v>
+        <v>33530300</v>
       </c>
       <c r="G17" s="3">
-        <v>26480600</v>
+        <v>26956200</v>
       </c>
       <c r="H17" s="3">
-        <v>26659400</v>
+        <v>27021100</v>
       </c>
       <c r="I17" s="3">
-        <v>29390100</v>
+        <v>27203500</v>
       </c>
       <c r="J17" s="3">
+        <v>29990000</v>
+      </c>
+      <c r="K17" s="3">
         <v>25150500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25108700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25867200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32448800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26395000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25118100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27152100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23953800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20840400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17542600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16780600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18769500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15390900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13834100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12889600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13140400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2039900</v>
+        <v>5073700</v>
       </c>
       <c r="E18" s="3">
-        <v>3110100</v>
+        <v>2081600</v>
       </c>
       <c r="F18" s="3">
-        <v>4640000</v>
+        <v>3173600</v>
       </c>
       <c r="G18" s="3">
-        <v>5870400</v>
+        <v>4734700</v>
       </c>
       <c r="H18" s="3">
-        <v>2105600</v>
+        <v>5990200</v>
       </c>
       <c r="I18" s="3">
-        <v>4839900</v>
+        <v>2148500</v>
       </c>
       <c r="J18" s="3">
+        <v>4938700</v>
+      </c>
+      <c r="K18" s="3">
         <v>3472900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3467600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2308300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>973800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2133100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4430200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6821100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2009100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5114100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1116400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6091400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3177000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3724000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1333300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3891900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1764,183 +1796,187 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-378400</v>
+        <v>-172100</v>
       </c>
       <c r="E20" s="3">
-        <v>-422900</v>
+        <v>-386100</v>
       </c>
       <c r="F20" s="3">
-        <v>901800</v>
+        <v>-431500</v>
       </c>
       <c r="G20" s="3">
-        <v>-626400</v>
+        <v>920200</v>
       </c>
       <c r="H20" s="3">
-        <v>1630800</v>
+        <v>-639200</v>
       </c>
       <c r="I20" s="3">
-        <v>2345700</v>
+        <v>1664100</v>
       </c>
       <c r="J20" s="3">
+        <v>2393600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>761600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3230100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2335000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>309900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5966400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1717900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3482100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2790600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10377600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>349600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3059700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1735100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>714200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>405900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>767600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>498500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>560200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-53200</v>
+        <v>6017900</v>
       </c>
       <c r="E21" s="3">
-        <v>4415200</v>
+        <v>-54300</v>
       </c>
       <c r="F21" s="3">
-        <v>5495200</v>
+        <v>4505300</v>
       </c>
       <c r="G21" s="3">
-        <v>6509500</v>
+        <v>5607300</v>
       </c>
       <c r="H21" s="3">
-        <v>3279500</v>
+        <v>6642400</v>
       </c>
       <c r="I21" s="3">
-        <v>7568000</v>
+        <v>3346400</v>
       </c>
       <c r="J21" s="3">
+        <v>7722500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5542300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4157900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>704500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8197100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>564900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12940900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3812200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9866300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1609300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8955000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13596400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5257300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4411900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5740800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>10</v>
@@ -1951,311 +1987,323 @@
       <c r="AE21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>300800</v>
+        <v>308500</v>
       </c>
       <c r="E22" s="3">
-        <v>294600</v>
+        <v>306900</v>
       </c>
       <c r="F22" s="3">
-        <v>256100</v>
+        <v>300600</v>
       </c>
       <c r="G22" s="3">
-        <v>246500</v>
+        <v>261400</v>
       </c>
       <c r="H22" s="3">
-        <v>239800</v>
+        <v>251500</v>
       </c>
       <c r="I22" s="3">
-        <v>214100</v>
+        <v>244700</v>
       </c>
       <c r="J22" s="3">
+        <v>218500</v>
+      </c>
+      <c r="K22" s="3">
         <v>191800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>172900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>164200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>163400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>180100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>182000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>161500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>152000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>162200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>165500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>182400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>201600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>212200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>205600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>198200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>193700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>187500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>174000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>168600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>125300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>110900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>118700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>98300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>101900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1360700</v>
+        <v>4593100</v>
       </c>
       <c r="E23" s="3">
-        <v>2392700</v>
+        <v>1388500</v>
       </c>
       <c r="F23" s="3">
-        <v>5285600</v>
+        <v>2441500</v>
       </c>
       <c r="G23" s="3">
-        <v>4997500</v>
+        <v>5393500</v>
       </c>
       <c r="H23" s="3">
-        <v>3496600</v>
+        <v>5099500</v>
       </c>
       <c r="I23" s="3">
-        <v>6971400</v>
+        <v>3567900</v>
       </c>
       <c r="J23" s="3">
+        <v>7113700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4056200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4040500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>560900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6583300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-918300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12635500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3564800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8430800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-89100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8680500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13342400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3867900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4194900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5433200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>790600</v>
+        <v>1418700</v>
       </c>
       <c r="E24" s="3">
-        <v>689100</v>
+        <v>806700</v>
       </c>
       <c r="F24" s="3">
-        <v>800900</v>
+        <v>703200</v>
       </c>
       <c r="G24" s="3">
-        <v>832000</v>
+        <v>817300</v>
       </c>
       <c r="H24" s="3">
-        <v>519200</v>
+        <v>849000</v>
       </c>
       <c r="I24" s="3">
-        <v>527800</v>
+        <v>529800</v>
       </c>
       <c r="J24" s="3">
+        <v>538500</v>
+      </c>
+      <c r="K24" s="3">
         <v>355300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>750600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>287100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1316200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>865300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1306400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>981200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1279800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>281600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1639200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>411400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1294500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>439200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1025500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>764400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>811300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>812800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>597500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>988900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>403500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>690600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>662100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>743100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2352,204 +2400,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>570200</v>
+        <v>3174400</v>
       </c>
       <c r="E26" s="3">
-        <v>1703500</v>
+        <v>581800</v>
       </c>
       <c r="F26" s="3">
-        <v>4484700</v>
+        <v>1738300</v>
       </c>
       <c r="G26" s="3">
-        <v>4165500</v>
+        <v>4576200</v>
       </c>
       <c r="H26" s="3">
-        <v>2977300</v>
+        <v>4250500</v>
       </c>
       <c r="I26" s="3">
-        <v>6443600</v>
+        <v>3038100</v>
       </c>
       <c r="J26" s="3">
+        <v>6575200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3305600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2724300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-304300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5276900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11355700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3283200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6791500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7386000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12903300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2842500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3430500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4621900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>962900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>451800</v>
+        <v>3421400</v>
       </c>
       <c r="E27" s="3">
-        <v>1994100</v>
+        <v>461000</v>
       </c>
       <c r="F27" s="3">
-        <v>3827900</v>
+        <v>2034800</v>
       </c>
       <c r="G27" s="3">
-        <v>4743300</v>
+        <v>3906000</v>
       </c>
       <c r="H27" s="3">
-        <v>3249000</v>
+        <v>4840100</v>
       </c>
       <c r="I27" s="3">
-        <v>6468000</v>
+        <v>3315300</v>
       </c>
       <c r="J27" s="3">
+        <v>6600000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3161200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2814700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>762900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6483200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-762700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11056200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4239400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7013000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>495000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8054500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11317000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3246900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3929300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4800100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2646,8 +2703,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2744,8 +2804,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2842,8 +2905,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2940,204 +3006,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>378400</v>
+        <v>172100</v>
       </c>
       <c r="E32" s="3">
-        <v>422900</v>
+        <v>386100</v>
       </c>
       <c r="F32" s="3">
-        <v>-901800</v>
+        <v>431500</v>
       </c>
       <c r="G32" s="3">
-        <v>626400</v>
+        <v>-920200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1630800</v>
+        <v>639200</v>
       </c>
       <c r="I32" s="3">
-        <v>-2345700</v>
+        <v>-1664100</v>
       </c>
       <c r="J32" s="3">
+        <v>-2393600</v>
+      </c>
+      <c r="K32" s="3">
         <v>5458400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-761600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4845000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1392100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-309900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1023100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-349600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>451800</v>
+        <v>3421400</v>
       </c>
       <c r="E33" s="3">
-        <v>1994100</v>
+        <v>461000</v>
       </c>
       <c r="F33" s="3">
-        <v>3827900</v>
+        <v>2034800</v>
       </c>
       <c r="G33" s="3">
-        <v>4743300</v>
+        <v>3906000</v>
       </c>
       <c r="H33" s="3">
-        <v>3249000</v>
+        <v>4840100</v>
       </c>
       <c r="I33" s="3">
-        <v>6468000</v>
+        <v>3315300</v>
       </c>
       <c r="J33" s="3">
+        <v>6600000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3161200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2814700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>762900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6483200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-762700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11056200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4239400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7013000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>495000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8054500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11317000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3246900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3929300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4800100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3234,209 +3309,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>451800</v>
+        <v>3421400</v>
       </c>
       <c r="E35" s="3">
-        <v>1994100</v>
+        <v>461000</v>
       </c>
       <c r="F35" s="3">
-        <v>3827900</v>
+        <v>2034800</v>
       </c>
       <c r="G35" s="3">
-        <v>4743300</v>
+        <v>3906000</v>
       </c>
       <c r="H35" s="3">
-        <v>3249000</v>
+        <v>4840100</v>
       </c>
       <c r="I35" s="3">
-        <v>6468000</v>
+        <v>3315300</v>
       </c>
       <c r="J35" s="3">
+        <v>6600000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3161200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2814700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>762900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6483200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-762700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11056200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4239400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7013000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>495000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8054500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11317000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3246900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3929300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4800100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3471,8 +3555,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3507,204 +3592,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>34281000</v>
+        <v>30898200</v>
       </c>
       <c r="E41" s="3">
-        <v>35203700</v>
+        <v>34980700</v>
       </c>
       <c r="F41" s="3">
-        <v>33671800</v>
+        <v>35922300</v>
       </c>
       <c r="G41" s="3">
-        <v>31280100</v>
+        <v>34359100</v>
       </c>
       <c r="H41" s="3">
-        <v>26676800</v>
+        <v>31918600</v>
       </c>
       <c r="I41" s="3">
-        <v>26975600</v>
+        <v>27221300</v>
       </c>
       <c r="J41" s="3">
+        <v>27526200</v>
+      </c>
+      <c r="K41" s="3">
         <v>28559200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24569300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26221100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40385100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38694100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41909600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44719700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43449500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44430400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45573600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51743500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>53981500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36534000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>32166100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28899100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27478100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>44612400</v>
+        <v>32391100</v>
       </c>
       <c r="E42" s="3">
-        <v>49681600</v>
+        <v>45523000</v>
       </c>
       <c r="F42" s="3">
-        <v>45681800</v>
+        <v>50695700</v>
       </c>
       <c r="G42" s="3">
-        <v>43938200</v>
+        <v>46614200</v>
       </c>
       <c r="H42" s="3">
-        <v>45784000</v>
+        <v>44835000</v>
       </c>
       <c r="I42" s="3">
-        <v>44758900</v>
+        <v>46718500</v>
       </c>
       <c r="J42" s="3">
+        <v>45672400</v>
+      </c>
+      <c r="K42" s="3">
         <v>38739900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>39836300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36617000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27806800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26581900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>27509400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22575900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>20883300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16090800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11389600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5121400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1021700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1066000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1540200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2006300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1653700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3801,8 +3893,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3899,498 +3994,516 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25122300</v>
+        <v>28867900</v>
       </c>
       <c r="E45" s="3">
-        <v>26643200</v>
+        <v>25635100</v>
       </c>
       <c r="F45" s="3">
-        <v>25365600</v>
+        <v>27187000</v>
       </c>
       <c r="G45" s="3">
-        <v>25698600</v>
+        <v>25883400</v>
       </c>
       <c r="H45" s="3">
-        <v>23970200</v>
+        <v>26223100</v>
       </c>
       <c r="I45" s="3">
-        <v>28898000</v>
+        <v>24459500</v>
       </c>
       <c r="J45" s="3">
+        <v>29487800</v>
+      </c>
+      <c r="K45" s="3">
         <v>26333200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25257300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25330800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24828600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25422400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23522800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22260200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18870600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16538500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15436500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15610300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15742300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14770600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10696400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10208500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8872000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>104015700</v>
+        <v>92157200</v>
       </c>
       <c r="E46" s="3">
-        <v>111528600</v>
+        <v>106138800</v>
       </c>
       <c r="F46" s="3">
-        <v>104719200</v>
+        <v>113805000</v>
       </c>
       <c r="G46" s="3">
-        <v>100916900</v>
+        <v>106856600</v>
       </c>
       <c r="H46" s="3">
-        <v>96431000</v>
+        <v>102976700</v>
       </c>
       <c r="I46" s="3">
-        <v>100632400</v>
+        <v>98399200</v>
       </c>
       <c r="J46" s="3">
+        <v>102686400</v>
+      </c>
+      <c r="K46" s="3">
         <v>93632300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>89662900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>88168900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>93020500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>90698400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>92941800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>89555700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>83203500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>77059700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>72399700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>72475200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>70745500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52370500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>44402800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>41113900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>38003800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>58589900</v>
+        <v>75397200</v>
       </c>
       <c r="E47" s="3">
-        <v>59298800</v>
+        <v>59785800</v>
       </c>
       <c r="F47" s="3">
-        <v>63016000</v>
+        <v>60509200</v>
       </c>
       <c r="G47" s="3">
-        <v>62401300</v>
+        <v>64302200</v>
       </c>
       <c r="H47" s="3">
-        <v>62602600</v>
+        <v>63675000</v>
       </c>
       <c r="I47" s="3">
-        <v>60253400</v>
+        <v>63880400</v>
       </c>
       <c r="J47" s="3">
+        <v>61483200</v>
+      </c>
+      <c r="K47" s="3">
         <v>57773100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>62111600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61204400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65630300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65584300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>65281500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>60887500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>59266900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>58735200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>55079600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>54946500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>55746500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>51631700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>38852700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>36743700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>33087900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>25581800</v>
+        <v>27381400</v>
       </c>
       <c r="E48" s="3">
-        <v>25091000</v>
+        <v>26104000</v>
       </c>
       <c r="F48" s="3">
-        <v>24790900</v>
+        <v>25603100</v>
       </c>
       <c r="G48" s="3">
-        <v>24296700</v>
+        <v>25296900</v>
       </c>
       <c r="H48" s="3">
-        <v>24320400</v>
+        <v>24792600</v>
       </c>
       <c r="I48" s="3">
-        <v>24564300</v>
+        <v>24816900</v>
       </c>
       <c r="J48" s="3">
+        <v>25065700</v>
+      </c>
+      <c r="K48" s="3">
         <v>24809000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24719400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34500500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22741400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22326900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21917300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20519800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20473800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17393900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16424900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21612600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19466200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19627200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18193700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13999600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13188900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>39600700</v>
+        <v>40178500</v>
       </c>
       <c r="E49" s="3">
-        <v>39773100</v>
+        <v>40409000</v>
       </c>
       <c r="F49" s="3">
-        <v>42595400</v>
+        <v>40584900</v>
       </c>
       <c r="G49" s="3">
-        <v>42987700</v>
+        <v>43464800</v>
       </c>
       <c r="H49" s="3">
-        <v>43521000</v>
+        <v>43865100</v>
       </c>
       <c r="I49" s="3">
-        <v>43806800</v>
+        <v>44409300</v>
       </c>
       <c r="J49" s="3">
+        <v>44701000</v>
+      </c>
+      <c r="K49" s="3">
         <v>44964000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45496200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45402400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45628900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>51142200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>51691900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>50613700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>51132800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>49004600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>49288400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>52874900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>52626800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>53469800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>50862400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>50688100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>45348800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4487,8 +4600,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4585,106 +4701,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16040700</v>
+        <v>16542600</v>
       </c>
       <c r="E52" s="3">
-        <v>15893200</v>
+        <v>16368100</v>
       </c>
       <c r="F52" s="3">
-        <v>15167800</v>
+        <v>16217600</v>
       </c>
       <c r="G52" s="3">
-        <v>14880700</v>
+        <v>15477300</v>
       </c>
       <c r="H52" s="3">
-        <v>15325500</v>
+        <v>15184400</v>
       </c>
       <c r="I52" s="3">
-        <v>15579800</v>
+        <v>15638300</v>
       </c>
       <c r="J52" s="3">
+        <v>15897800</v>
+      </c>
+      <c r="K52" s="3">
         <v>15426700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15507100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4845800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15549900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15552800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14506300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13701700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13552100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9065700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8569300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3651800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4590900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3806500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3348900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4262100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3683500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4781,106 +4903,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>243828800</v>
+        <v>251656900</v>
       </c>
       <c r="E54" s="3">
-        <v>251584700</v>
+        <v>248805600</v>
       </c>
       <c r="F54" s="3">
-        <v>250289300</v>
+        <v>256719800</v>
       </c>
       <c r="G54" s="3">
-        <v>245483200</v>
+        <v>255398000</v>
       </c>
       <c r="H54" s="3">
-        <v>242200600</v>
+        <v>250493800</v>
       </c>
       <c r="I54" s="3">
-        <v>244836700</v>
+        <v>247144100</v>
       </c>
       <c r="J54" s="3">
+        <v>249834000</v>
+      </c>
+      <c r="K54" s="3">
         <v>236605100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>237497300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>234122000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>242570900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>245304600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>246338700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>235278300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>227629000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>211259100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>201761900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>205560900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>203175800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>180905600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>155660500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>146807400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>133312900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4915,8 +5043,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4951,65 +5080,66 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>41155500</v>
+        <v>47831600</v>
       </c>
       <c r="E57" s="3">
-        <v>43553800</v>
+        <v>41995500</v>
       </c>
       <c r="F57" s="3">
-        <v>39597200</v>
+        <v>44442800</v>
       </c>
       <c r="G57" s="3">
-        <v>38595100</v>
+        <v>40405400</v>
       </c>
       <c r="H57" s="3">
-        <v>38125300</v>
+        <v>39382900</v>
       </c>
       <c r="I57" s="3">
-        <v>40572900</v>
+        <v>38903400</v>
       </c>
       <c r="J57" s="3">
+        <v>41401000</v>
+      </c>
+      <c r="K57" s="3">
         <v>37560600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36918600</v>
       </c>
-      <c r="L57" s="3" t="s">
+      <c r="M57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38835600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37802900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35961600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36321300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31307500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26279700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24271800</v>
       </c>
-      <c r="T57" s="3" t="s">
+      <c r="U57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
@@ -5049,498 +5179,516 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4006800</v>
+        <v>4216700</v>
       </c>
       <c r="E58" s="3">
-        <v>3641100</v>
+        <v>4088600</v>
       </c>
       <c r="F58" s="3">
-        <v>1131100</v>
+        <v>3715400</v>
       </c>
       <c r="G58" s="3">
-        <v>1137900</v>
+        <v>1154200</v>
       </c>
       <c r="H58" s="3">
-        <v>1694700</v>
+        <v>1161100</v>
       </c>
       <c r="I58" s="3">
-        <v>1597800</v>
+        <v>1729300</v>
       </c>
       <c r="J58" s="3">
+        <v>1630400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1602900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1883600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1220800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1089300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2679000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2443400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1870400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2094500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>722500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>669500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>806900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>649000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3768400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3516800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3417500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3313000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>864900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>956800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13073100</v>
+        <v>13210000</v>
       </c>
       <c r="E59" s="3">
-        <v>14804900</v>
+        <v>13340000</v>
       </c>
       <c r="F59" s="3">
-        <v>13127800</v>
+        <v>15107100</v>
       </c>
       <c r="G59" s="3">
-        <v>12800800</v>
+        <v>13395800</v>
       </c>
       <c r="H59" s="3">
-        <v>13420200</v>
+        <v>13062100</v>
       </c>
       <c r="I59" s="3">
-        <v>15557400</v>
+        <v>13694100</v>
       </c>
       <c r="J59" s="3">
+        <v>15874900</v>
+      </c>
+      <c r="K59" s="3">
         <v>13732600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13411500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51772100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16634700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14652800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14475700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14336500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16453900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11744900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11617700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>37060600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>39764300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>34290100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>28673900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>28173100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27007000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>58235400</v>
+        <v>65258200</v>
       </c>
       <c r="E60" s="3">
-        <v>61999900</v>
+        <v>59424100</v>
       </c>
       <c r="F60" s="3">
-        <v>53856100</v>
+        <v>63265300</v>
       </c>
       <c r="G60" s="3">
-        <v>52533800</v>
+        <v>54955400</v>
       </c>
       <c r="H60" s="3">
-        <v>53240100</v>
+        <v>53606100</v>
       </c>
       <c r="I60" s="3">
-        <v>57728100</v>
+        <v>54326800</v>
       </c>
       <c r="J60" s="3">
+        <v>58906400</v>
+      </c>
+      <c r="K60" s="3">
         <v>52896100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52213700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52992900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56559700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55134700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52880700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52528200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49855900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38747100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36559000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>37867500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>40413300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38058500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32190700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31590600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30320000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19587600</v>
+        <v>25098200</v>
       </c>
       <c r="E61" s="3">
-        <v>19283300</v>
+        <v>19987400</v>
       </c>
       <c r="F61" s="3">
-        <v>21906200</v>
+        <v>19676900</v>
       </c>
       <c r="G61" s="3">
-        <v>21733500</v>
+        <v>22353400</v>
       </c>
       <c r="H61" s="3">
-        <v>20598000</v>
+        <v>22177100</v>
       </c>
       <c r="I61" s="3">
-        <v>20483600</v>
+        <v>21018400</v>
       </c>
       <c r="J61" s="3">
+        <v>20901700</v>
+      </c>
+      <c r="K61" s="3">
         <v>20701600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19249000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18296000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18149900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18892700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19187500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18891700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14289200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17224200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17814900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18830400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18196100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18958600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17779000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17012200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16446000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12289100</v>
+        <v>12797700</v>
       </c>
       <c r="E62" s="3">
-        <v>12463400</v>
+        <v>12539900</v>
       </c>
       <c r="F62" s="3">
-        <v>12873300</v>
+        <v>12717800</v>
       </c>
       <c r="G62" s="3">
-        <v>12740700</v>
+        <v>13136100</v>
       </c>
       <c r="H62" s="3">
-        <v>13219700</v>
+        <v>13000800</v>
       </c>
       <c r="I62" s="3">
-        <v>13297300</v>
+        <v>13489500</v>
       </c>
       <c r="J62" s="3">
+        <v>13568800</v>
+      </c>
+      <c r="K62" s="3">
         <v>13453100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13622800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13403800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13526600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13729800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13614700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13016600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12820300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10694800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10566900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11144900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11048800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10354200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7139000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4589600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4043600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5637,8 +5785,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5735,8 +5886,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5833,106 +5987,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>107527900</v>
+        <v>119414100</v>
       </c>
       <c r="E66" s="3">
-        <v>111961500</v>
+        <v>109722600</v>
       </c>
       <c r="F66" s="3">
-        <v>107282300</v>
+        <v>114246800</v>
       </c>
       <c r="G66" s="3">
-        <v>105457500</v>
+        <v>109472100</v>
       </c>
       <c r="H66" s="3">
-        <v>105469500</v>
+        <v>107610000</v>
       </c>
       <c r="I66" s="3">
-        <v>109998800</v>
+        <v>107622300</v>
       </c>
       <c r="J66" s="3">
+        <v>112244000</v>
+      </c>
+      <c r="K66" s="3">
         <v>105638100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103587700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103156000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106870400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106961600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>105035900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103575200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>96014900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>83728500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>81439100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>85870200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>87396600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>85691900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>74973700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70887900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>65336800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5967,8 +6127,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6065,8 +6226,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6163,8 +6327,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6196,73 +6363,76 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>1461600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1477500</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1201100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1207300</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1175300</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1183700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1152400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1425200</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1200300</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1171000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1083400</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1037300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1040600</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>839900</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>452700</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>430600</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>442100</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>133300</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>113200</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>435100</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>515800</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6359,106 +6529,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>84641000</v>
+        <v>81739600</v>
       </c>
       <c r="E72" s="3">
-        <v>87258500</v>
+        <v>86368600</v>
       </c>
       <c r="F72" s="3">
-        <v>89814900</v>
+        <v>89039600</v>
       </c>
       <c r="G72" s="3">
-        <v>87168500</v>
+        <v>91648100</v>
       </c>
       <c r="H72" s="3">
-        <v>84554600</v>
+        <v>88947700</v>
       </c>
       <c r="I72" s="3">
-        <v>82569100</v>
+        <v>86280500</v>
       </c>
       <c r="J72" s="3">
+        <v>84254400</v>
+      </c>
+      <c r="K72" s="3">
         <v>76966400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>80286100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>79174500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>81449200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>82138400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>86310300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78268100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>79111700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>72029000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>67773800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>64563300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>63003500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>55694500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>43446200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39985800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>34455500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6555,8 +6731,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6653,8 +6832,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6751,106 +6933,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>136300900</v>
+        <v>132242800</v>
       </c>
       <c r="E76" s="3">
-        <v>139623100</v>
+        <v>139083000</v>
       </c>
       <c r="F76" s="3">
-        <v>143006900</v>
+        <v>142473000</v>
       </c>
       <c r="G76" s="3">
-        <v>140025700</v>
+        <v>145925900</v>
       </c>
       <c r="H76" s="3">
-        <v>136731000</v>
+        <v>142883800</v>
       </c>
       <c r="I76" s="3">
-        <v>134837800</v>
+        <v>139521800</v>
       </c>
       <c r="J76" s="3">
+        <v>137590000</v>
+      </c>
+      <c r="K76" s="3">
         <v>130967000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>133909600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>130966000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>134238900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>136865400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>140101700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>130495800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130438900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>126346900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>119170500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>118265600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>114579000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>94042700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>79603400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74882100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>66935500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6947,209 +7135,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>451800</v>
+        <v>3421400</v>
       </c>
       <c r="E81" s="3">
-        <v>1994100</v>
+        <v>461000</v>
       </c>
       <c r="F81" s="3">
-        <v>3827900</v>
+        <v>2034800</v>
       </c>
       <c r="G81" s="3">
-        <v>4743300</v>
+        <v>3906000</v>
       </c>
       <c r="H81" s="3">
-        <v>3249000</v>
+        <v>4840100</v>
       </c>
       <c r="I81" s="3">
-        <v>6468000</v>
+        <v>3315300</v>
       </c>
       <c r="J81" s="3">
+        <v>6600000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3161200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2814700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>762900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6483200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-762700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11056200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4239400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7013000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>495000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8054500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11317000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3246900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3929300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4800100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7184,8 +7381,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7282,8 +7480,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7380,8 +7581,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7478,8 +7682,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7576,8 +7783,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7674,8 +7884,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7772,106 +7985,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3224700</v>
+        <v>4742000</v>
       </c>
       <c r="E89" s="3">
-        <v>8941200</v>
+        <v>3290500</v>
       </c>
       <c r="F89" s="3">
-        <v>6801800</v>
+        <v>9123700</v>
       </c>
       <c r="G89" s="3">
-        <v>6259500</v>
+        <v>6940600</v>
       </c>
       <c r="H89" s="3">
-        <v>4338400</v>
+        <v>6387200</v>
       </c>
       <c r="I89" s="3">
-        <v>12071000</v>
+        <v>4426900</v>
       </c>
       <c r="J89" s="3">
+        <v>12317400</v>
+      </c>
+      <c r="K89" s="3">
         <v>6509000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4708500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-972100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11072800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5093200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4826100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3366300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14366600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8001100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7382600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>338800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14859800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7383300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5288000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2822300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9425100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7906,106 +8125,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12094000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11995000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8857000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5150000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6927000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="M91" s="3">
         <v>-18710000</v>
       </c>
       <c r="N91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-453500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-813500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-281000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-975000</v>
       </c>
-      <c r="X91" s="3" t="s">
+      <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AB91" s="3" t="s">
+      <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8102,8 +8325,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8200,106 +8426,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>2800100</v>
+        <v>-5051200</v>
       </c>
       <c r="E94" s="3">
-        <v>-4272600</v>
+        <v>2857200</v>
       </c>
       <c r="F94" s="3">
-        <v>-3282800</v>
+        <v>-4359800</v>
       </c>
       <c r="G94" s="3">
-        <v>1740100</v>
+        <v>-3349800</v>
       </c>
       <c r="H94" s="3">
-        <v>-3703800</v>
+        <v>1775600</v>
       </c>
       <c r="I94" s="3">
-        <v>-10077800</v>
+        <v>-3779400</v>
       </c>
       <c r="J94" s="3">
+        <v>-10283500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8334,8 +8566,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8432,8 +8665,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8530,8 +8766,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8628,8 +8867,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8726,298 +8968,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-7462300</v>
+        <v>-2760700</v>
       </c>
       <c r="E100" s="3">
-        <v>-2378300</v>
+        <v>-7614600</v>
       </c>
       <c r="F100" s="3">
-        <v>-1710700</v>
+        <v>-2426800</v>
       </c>
       <c r="G100" s="3">
-        <v>-3403700</v>
+        <v>-1745600</v>
       </c>
       <c r="H100" s="3">
-        <v>-1287500</v>
+        <v>-3473200</v>
       </c>
       <c r="I100" s="3">
-        <v>-3289300</v>
+        <v>-1313800</v>
       </c>
       <c r="J100" s="3">
+        <v>-3356500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4213600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-791400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1489200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-679200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>464500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9437000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>328600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>686400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>109400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>614200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>361000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>262500</v>
+        <v>92900</v>
       </c>
       <c r="E101" s="3">
-        <v>-365200</v>
+        <v>267900</v>
       </c>
       <c r="F101" s="3">
-        <v>112300</v>
+        <v>-372600</v>
       </c>
       <c r="G101" s="3">
-        <v>596700</v>
+        <v>114600</v>
       </c>
       <c r="H101" s="3">
-        <v>-165900</v>
+        <v>608900</v>
       </c>
       <c r="I101" s="3">
-        <v>-280600</v>
+        <v>-169300</v>
       </c>
       <c r="J101" s="3">
+        <v>-286300</v>
+      </c>
+      <c r="K101" s="3">
         <v>474700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>462400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-126100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-816200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>27700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-314800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>159900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-575200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-567800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-51700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>363500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>367100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>210400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-173700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>233700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>399300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>253800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1175100</v>
+        <v>-2976900</v>
       </c>
       <c r="E102" s="3">
-        <v>1925100</v>
+        <v>-1199000</v>
       </c>
       <c r="F102" s="3">
-        <v>1920600</v>
+        <v>1964400</v>
       </c>
       <c r="G102" s="3">
-        <v>5192600</v>
+        <v>1959800</v>
       </c>
       <c r="H102" s="3">
-        <v>-818900</v>
+        <v>5298600</v>
       </c>
       <c r="I102" s="3">
-        <v>-1576700</v>
+        <v>-835600</v>
       </c>
       <c r="J102" s="3">
+        <v>-1608900</v>
+      </c>
+      <c r="K102" s="3">
         <v>4273300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3025000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3883800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1904100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18978300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4747700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2955700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>209800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3610700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>494500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>291500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,435 +656,447 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34291400</v>
+        <v>33716300</v>
       </c>
       <c r="E8" s="3">
-        <v>31279800</v>
+        <v>33471800</v>
       </c>
       <c r="F8" s="3">
-        <v>36703900</v>
+        <v>30728300</v>
       </c>
       <c r="G8" s="3">
-        <v>31690900</v>
+        <v>36715800</v>
       </c>
       <c r="H8" s="3">
-        <v>33011300</v>
+        <v>30807500</v>
       </c>
       <c r="I8" s="3">
-        <v>29352000</v>
+        <v>32287100</v>
       </c>
       <c r="J8" s="3">
+        <v>30309200</v>
+      </c>
+      <c r="K8" s="3">
         <v>34928600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28623400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28576300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28175500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33422700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>28528100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29548400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26085400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30774900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22849500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22656700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17897000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24861000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18567800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17558100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14222900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20598000</v>
+        <v>20533000</v>
       </c>
       <c r="E9" s="3">
-        <v>20878900</v>
+        <v>20105700</v>
       </c>
       <c r="F9" s="3">
-        <v>22023000</v>
+        <v>20510800</v>
       </c>
       <c r="G9" s="3">
-        <v>19689800</v>
+        <v>22030200</v>
       </c>
       <c r="H9" s="3">
-        <v>20068100</v>
+        <v>19141000</v>
       </c>
       <c r="I9" s="3">
-        <v>19571300</v>
+        <v>19627800</v>
       </c>
       <c r="J9" s="3">
+        <v>20044500</v>
+      </c>
+      <c r="K9" s="3">
         <v>21147700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18128000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18024900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19185500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20206500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18444000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17822800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17463200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16880500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13256500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12455300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11350900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12985400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10225800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9164800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8459400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13693400</v>
+        <v>13183300</v>
       </c>
       <c r="E10" s="3">
-        <v>10400900</v>
+        <v>13366100</v>
       </c>
       <c r="F10" s="3">
-        <v>14680800</v>
+        <v>10217600</v>
       </c>
       <c r="G10" s="3">
-        <v>12001100</v>
+        <v>14685600</v>
       </c>
       <c r="H10" s="3">
-        <v>12943200</v>
+        <v>11666500</v>
       </c>
       <c r="I10" s="3">
-        <v>9780800</v>
+        <v>12659300</v>
       </c>
       <c r="J10" s="3">
+        <v>10264700</v>
+      </c>
+      <c r="K10" s="3">
         <v>13780900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10495500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10551300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8990000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13216100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10084100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11725600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8622200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13894400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9593000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10201400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6546100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11875600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8342000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8393300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5763500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,109 +1132,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1885300</v>
+        <v>2021800</v>
       </c>
       <c r="E12" s="3">
-        <v>1985700</v>
+        <v>1840300</v>
       </c>
       <c r="F12" s="3">
-        <v>1901500</v>
+        <v>1950700</v>
       </c>
       <c r="G12" s="3">
-        <v>2004500</v>
+        <v>1902200</v>
       </c>
       <c r="H12" s="3">
-        <v>1475400</v>
+        <v>1948600</v>
       </c>
       <c r="I12" s="3">
-        <v>1956800</v>
+        <v>1443000</v>
       </c>
       <c r="J12" s="3">
+        <v>2020600</v>
+      </c>
+      <c r="K12" s="3">
         <v>1906200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2093100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1973100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1511100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2163800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2174500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1941600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1851600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1894100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2835900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1633000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1657500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1705600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1706400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1600800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1317200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>959300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>933400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>754400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>696900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>657100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>642800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1331,201 +1350,207 @@
         <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>636200</v>
       </c>
       <c r="F14" s="3">
-        <v>1196900</v>
+        <v>2845900</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>286300</v>
+        <v>1690900</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>1093300</v>
       </c>
       <c r="J14" s="3">
+        <v>-953800</v>
+      </c>
+      <c r="K14" s="3">
         <v>382600</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>89900</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>309000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>252600</v>
+        <v>235100</v>
       </c>
       <c r="E15" s="3">
-        <v>293400</v>
+        <v>246600</v>
       </c>
       <c r="F15" s="3">
-        <v>2058400</v>
+        <v>-1768000</v>
       </c>
       <c r="G15" s="3">
-        <v>342700</v>
+        <v>2059100</v>
       </c>
       <c r="H15" s="3">
-        <v>349500</v>
+        <v>333200</v>
       </c>
       <c r="I15" s="3">
-        <v>351600</v>
+        <v>341800</v>
       </c>
       <c r="J15" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="K15" s="3">
         <v>779600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>377000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>382400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>390900</v>
       </c>
       <c r="N15" s="3">
         <v>390900</v>
       </c>
       <c r="O15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="P15" s="3">
         <v>413100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>441300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>475400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>441500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>425600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>435000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>633100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>503800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>469000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>468400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>487200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>408000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>365400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>301900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>190700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>305300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>259400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>294700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>190900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>183400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1558,210 +1583,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>29217700</v>
+        <v>28691600</v>
       </c>
       <c r="E17" s="3">
-        <v>29198200</v>
+        <v>28086500</v>
       </c>
       <c r="F17" s="3">
-        <v>33530300</v>
+        <v>26627200</v>
       </c>
       <c r="G17" s="3">
-        <v>26956200</v>
+        <v>32343800</v>
       </c>
       <c r="H17" s="3">
-        <v>27021100</v>
+        <v>26204800</v>
       </c>
       <c r="I17" s="3">
-        <v>27203500</v>
+        <v>26148300</v>
       </c>
       <c r="J17" s="3">
+        <v>27516500</v>
+      </c>
+      <c r="K17" s="3">
         <v>29990000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25150500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25108700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25867200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32448800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26395000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25118100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27152100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23953800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20840400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17542600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16780600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18769500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15390900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13834100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12889600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5073700</v>
+        <v>5024700</v>
       </c>
       <c r="E18" s="3">
-        <v>2081600</v>
+        <v>5385200</v>
       </c>
       <c r="F18" s="3">
-        <v>3173600</v>
+        <v>4101100</v>
       </c>
       <c r="G18" s="3">
-        <v>4734700</v>
+        <v>4371900</v>
       </c>
       <c r="H18" s="3">
-        <v>5990200</v>
+        <v>4602700</v>
       </c>
       <c r="I18" s="3">
-        <v>2148500</v>
+        <v>6138900</v>
       </c>
       <c r="J18" s="3">
+        <v>2792800</v>
+      </c>
+      <c r="K18" s="3">
         <v>4938700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3472900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3467600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2308300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>973800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2133100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4430200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6821100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2009100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5114100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1116400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6091400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3177000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3724000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1333300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1797,189 +1829,193 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-172100</v>
+        <v>71300</v>
       </c>
       <c r="E20" s="3">
-        <v>-386100</v>
+        <v>-242500</v>
       </c>
       <c r="F20" s="3">
-        <v>-431500</v>
+        <v>33900</v>
       </c>
       <c r="G20" s="3">
-        <v>920200</v>
+        <v>165600</v>
       </c>
       <c r="H20" s="3">
-        <v>-639200</v>
+        <v>599300</v>
       </c>
       <c r="I20" s="3">
-        <v>1664100</v>
+        <v>-581100</v>
       </c>
       <c r="J20" s="3">
+        <v>-255300</v>
+      </c>
+      <c r="K20" s="3">
         <v>2393600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>761600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3230100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2335000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>309900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5966400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1717900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3482100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2790600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10377600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>349600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3059700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>714200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>405900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>767600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>498500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>560200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6017900</v>
+        <v>5188500</v>
       </c>
       <c r="E21" s="3">
-        <v>-54300</v>
+        <v>5874300</v>
       </c>
       <c r="F21" s="3">
-        <v>4505300</v>
+        <v>2299100</v>
       </c>
       <c r="G21" s="3">
-        <v>5607300</v>
+        <v>6265500</v>
       </c>
       <c r="H21" s="3">
-        <v>6642400</v>
+        <v>4336500</v>
       </c>
       <c r="I21" s="3">
-        <v>3346400</v>
+        <v>7061800</v>
       </c>
       <c r="J21" s="3">
+        <v>3002000</v>
+      </c>
+      <c r="K21" s="3">
         <v>7722500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5542300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4157900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>704500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8197100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>564900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12940900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3812200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9866300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1609300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8955000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13596400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5257300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4411900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>10</v>
@@ -1990,320 +2026,332 @@
       <c r="AF21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>308500</v>
+        <v>346000</v>
       </c>
       <c r="E22" s="3">
-        <v>306900</v>
+        <v>301100</v>
       </c>
       <c r="F22" s="3">
-        <v>300600</v>
+        <v>301500</v>
       </c>
       <c r="G22" s="3">
-        <v>261400</v>
+        <v>300700</v>
       </c>
       <c r="H22" s="3">
-        <v>251500</v>
+        <v>254100</v>
       </c>
       <c r="I22" s="3">
-        <v>244700</v>
+        <v>246000</v>
       </c>
       <c r="J22" s="3">
+        <v>252700</v>
+      </c>
+      <c r="K22" s="3">
         <v>218500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>191800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>172900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>164200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>163400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>180100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>182000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>161500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>152000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>162200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>165500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>182400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>201600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>212200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>205600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>198200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>193700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>187500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>174000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>168600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>125300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>110900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>118700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>98300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>101900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4593100</v>
+        <v>7260100</v>
       </c>
       <c r="E23" s="3">
-        <v>1388500</v>
+        <v>4690400</v>
       </c>
       <c r="F23" s="3">
-        <v>2441500</v>
+        <v>919700</v>
       </c>
       <c r="G23" s="3">
-        <v>5393500</v>
+        <v>2214800</v>
       </c>
       <c r="H23" s="3">
-        <v>5099500</v>
+        <v>4453200</v>
       </c>
       <c r="I23" s="3">
-        <v>3567900</v>
+        <v>5380600</v>
       </c>
       <c r="J23" s="3">
+        <v>3749200</v>
+      </c>
+      <c r="K23" s="3">
         <v>7113700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4056200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4040500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>560900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6583300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-918300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12635500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3564800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8430800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-89100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8680500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13342400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3867900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4194900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1418700</v>
+        <v>1052000</v>
       </c>
       <c r="E24" s="3">
-        <v>806700</v>
+        <v>1384800</v>
       </c>
       <c r="F24" s="3">
-        <v>703200</v>
+        <v>792500</v>
       </c>
       <c r="G24" s="3">
-        <v>817300</v>
+        <v>703400</v>
       </c>
       <c r="H24" s="3">
-        <v>849000</v>
+        <v>794500</v>
       </c>
       <c r="I24" s="3">
-        <v>529800</v>
+        <v>830400</v>
       </c>
       <c r="J24" s="3">
+        <v>547100</v>
+      </c>
+      <c r="K24" s="3">
         <v>538500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>355300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>750600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>287100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1316200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>865300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1306400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>981200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1279800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>281600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1639200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>411400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1294500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>439200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1025500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>764400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>811300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>38800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>812800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>597500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>988900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>403500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>690600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>662100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>743100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2403,210 +2451,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3174400</v>
+        <v>6208100</v>
       </c>
       <c r="E26" s="3">
-        <v>581800</v>
+        <v>3305700</v>
       </c>
       <c r="F26" s="3">
-        <v>1738300</v>
+        <v>127300</v>
       </c>
       <c r="G26" s="3">
-        <v>4576200</v>
+        <v>1511400</v>
       </c>
       <c r="H26" s="3">
-        <v>4250500</v>
+        <v>3658700</v>
       </c>
       <c r="I26" s="3">
-        <v>3038100</v>
+        <v>4550300</v>
       </c>
       <c r="J26" s="3">
+        <v>3202100</v>
+      </c>
+      <c r="K26" s="3">
         <v>6575200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3305600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2724300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-304300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5276900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11355700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3283200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6791500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7386000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12903300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2842500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3430500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>962900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3421400</v>
+        <v>6254800</v>
       </c>
       <c r="E27" s="3">
-        <v>461000</v>
+        <v>3339700</v>
       </c>
       <c r="F27" s="3">
-        <v>2034800</v>
+        <v>452900</v>
       </c>
       <c r="G27" s="3">
-        <v>3906000</v>
+        <v>2035400</v>
       </c>
       <c r="H27" s="3">
-        <v>4840100</v>
+        <v>3797100</v>
       </c>
       <c r="I27" s="3">
-        <v>3315300</v>
+        <v>4733900</v>
       </c>
       <c r="J27" s="3">
+        <v>3423400</v>
+      </c>
+      <c r="K27" s="3">
         <v>6600000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3161200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2814700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>762900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6483200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-762700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11056200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4239400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7013000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>495000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8054500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11317000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3246900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3929300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2706,8 +2763,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2807,8 +2867,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2908,8 +2971,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3009,210 +3075,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>172100</v>
+        <v>-71300</v>
       </c>
       <c r="E32" s="3">
-        <v>386100</v>
+        <v>242500</v>
       </c>
       <c r="F32" s="3">
-        <v>431500</v>
+        <v>-33900</v>
       </c>
       <c r="G32" s="3">
-        <v>-920200</v>
+        <v>-165600</v>
       </c>
       <c r="H32" s="3">
-        <v>639200</v>
+        <v>-599300</v>
       </c>
       <c r="I32" s="3">
-        <v>-1664100</v>
+        <v>581100</v>
       </c>
       <c r="J32" s="3">
+        <v>255300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5458400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-761600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4845000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1392100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-309900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1023100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-349600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3421400</v>
+        <v>6277400</v>
       </c>
       <c r="E33" s="3">
-        <v>461000</v>
+        <v>3356300</v>
       </c>
       <c r="F33" s="3">
-        <v>2034800</v>
+        <v>466000</v>
       </c>
       <c r="G33" s="3">
-        <v>3906000</v>
+        <v>2052600</v>
       </c>
       <c r="H33" s="3">
-        <v>4840100</v>
+        <v>3816400</v>
       </c>
       <c r="I33" s="3">
-        <v>3315300</v>
+        <v>4721500</v>
       </c>
       <c r="J33" s="3">
+        <v>3442000</v>
+      </c>
+      <c r="K33" s="3">
         <v>6600000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3161200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2814700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>762900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6483200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-762700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11056200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4239400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7013000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>495000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8054500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11317000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3246900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3929300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3312,215 +3387,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3421400</v>
+        <v>6277400</v>
       </c>
       <c r="E35" s="3">
-        <v>461000</v>
+        <v>3356300</v>
       </c>
       <c r="F35" s="3">
-        <v>2034800</v>
+        <v>466000</v>
       </c>
       <c r="G35" s="3">
-        <v>3906000</v>
+        <v>2052600</v>
       </c>
       <c r="H35" s="3">
-        <v>4840100</v>
+        <v>3816400</v>
       </c>
       <c r="I35" s="3">
-        <v>3315300</v>
+        <v>4721500</v>
       </c>
       <c r="J35" s="3">
+        <v>3442000</v>
+      </c>
+      <c r="K35" s="3">
         <v>6600000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3161200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2814700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>762900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6483200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-762700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11056200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4239400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7013000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>495000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8054500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11317000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3246900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3929300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3556,8 +3640,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3593,233 +3678,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>30898200</v>
+        <v>26087700</v>
       </c>
       <c r="E41" s="3">
-        <v>34980700</v>
+        <v>30159600</v>
       </c>
       <c r="F41" s="3">
-        <v>35922300</v>
+        <v>34364000</v>
       </c>
       <c r="G41" s="3">
-        <v>34359100</v>
+        <v>35933900</v>
       </c>
       <c r="H41" s="3">
-        <v>31918600</v>
+        <v>33401300</v>
       </c>
       <c r="I41" s="3">
-        <v>27221300</v>
+        <v>31218400</v>
       </c>
       <c r="J41" s="3">
+        <v>28109000</v>
+      </c>
+      <c r="K41" s="3">
         <v>27526200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28559200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24569300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26221100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40385100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38694100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41909600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44719700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43449500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44430400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45573600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51743500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53981500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>36534000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32166100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28899100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>32391100</v>
+        <v>29338700</v>
       </c>
       <c r="E42" s="3">
-        <v>45523000</v>
+        <v>31616900</v>
       </c>
       <c r="F42" s="3">
-        <v>50695700</v>
+        <v>44720400</v>
       </c>
       <c r="G42" s="3">
-        <v>46614200</v>
+        <v>50712200</v>
       </c>
       <c r="H42" s="3">
-        <v>44835000</v>
+        <v>45314800</v>
       </c>
       <c r="I42" s="3">
-        <v>46718500</v>
+        <v>43851500</v>
       </c>
       <c r="J42" s="3">
+        <v>48242000</v>
+      </c>
+      <c r="K42" s="3">
         <v>45672400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38739900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39836300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36617000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27806800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26581900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27509400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22575900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20883300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16090800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11389600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5121400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1021700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1066000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1540200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2006300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+        <v>9542600</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>9337900</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3896,31 +3988,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+        <v>3526100</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>4155800</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3997,513 +4092,531 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28867900</v>
+        <v>31408400</v>
       </c>
       <c r="E45" s="3">
-        <v>25635100</v>
+        <v>28177900</v>
       </c>
       <c r="F45" s="3">
-        <v>27187000</v>
+        <v>9651500</v>
       </c>
       <c r="G45" s="3">
-        <v>25883400</v>
+        <v>27195800</v>
       </c>
       <c r="H45" s="3">
-        <v>26223100</v>
+        <v>25161900</v>
       </c>
       <c r="I45" s="3">
-        <v>24459500</v>
+        <v>25647900</v>
       </c>
       <c r="J45" s="3">
+        <v>9318600</v>
+      </c>
+      <c r="K45" s="3">
         <v>29487800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26333200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25257300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25330800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24828600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25422400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23522800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22260200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>18870600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16538500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15436500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15610300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15742300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14770600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10696400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10208500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>92157200</v>
+        <v>86834700</v>
       </c>
       <c r="E46" s="3">
-        <v>106138800</v>
+        <v>89954500</v>
       </c>
       <c r="F46" s="3">
-        <v>113805000</v>
+        <v>104267600</v>
       </c>
       <c r="G46" s="3">
-        <v>106856600</v>
+        <v>113842000</v>
       </c>
       <c r="H46" s="3">
-        <v>102976700</v>
+        <v>103878000</v>
       </c>
       <c r="I46" s="3">
-        <v>98399200</v>
+        <v>100717700</v>
       </c>
       <c r="J46" s="3">
+        <v>101608000</v>
+      </c>
+      <c r="K46" s="3">
         <v>102686400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>93632300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>89662900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>88168900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>93020500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>90698400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>92941800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>89555700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>83203500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>77059700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>72399700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>72475200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>70745500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>52370500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>44402800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>41113900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>75397200</v>
+        <v>78010700</v>
       </c>
       <c r="E47" s="3">
-        <v>59785800</v>
+        <v>73595100</v>
       </c>
       <c r="F47" s="3">
-        <v>60509200</v>
+        <v>58731800</v>
       </c>
       <c r="G47" s="3">
-        <v>64302200</v>
+        <v>60528800</v>
       </c>
       <c r="H47" s="3">
-        <v>63675000</v>
+        <v>62509800</v>
       </c>
       <c r="I47" s="3">
-        <v>63880400</v>
+        <v>62278200</v>
       </c>
       <c r="J47" s="3">
+        <v>65963600</v>
+      </c>
+      <c r="K47" s="3">
         <v>61483200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>57773100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>62111600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61204400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65630300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>65584300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>65281500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>60887500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>59266900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>58735200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55079600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54946500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>55746500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>51631700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>38852700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>36743700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>27381400</v>
+        <v>29641000</v>
       </c>
       <c r="E48" s="3">
-        <v>26104000</v>
+        <v>26726900</v>
       </c>
       <c r="F48" s="3">
-        <v>25603100</v>
+        <v>36297800</v>
       </c>
       <c r="G48" s="3">
-        <v>25296900</v>
+        <v>25611400</v>
       </c>
       <c r="H48" s="3">
-        <v>24792600</v>
+        <v>24591700</v>
       </c>
       <c r="I48" s="3">
-        <v>24816900</v>
+        <v>24248700</v>
       </c>
       <c r="J48" s="3">
+        <v>36897900</v>
+      </c>
+      <c r="K48" s="3">
         <v>25065700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24809000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24719400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34500500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22741400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22326900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21917300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20519800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20473800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17393900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16424900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21612600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19466200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19627200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18193700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13999600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>40178500</v>
+        <v>40277600</v>
       </c>
       <c r="E49" s="3">
-        <v>40409000</v>
+        <v>39218100</v>
       </c>
       <c r="F49" s="3">
-        <v>40584900</v>
+        <v>39696600</v>
       </c>
       <c r="G49" s="3">
-        <v>43464800</v>
+        <v>40598100</v>
       </c>
       <c r="H49" s="3">
-        <v>43865100</v>
+        <v>42253200</v>
       </c>
       <c r="I49" s="3">
-        <v>44409300</v>
+        <v>42902800</v>
       </c>
       <c r="J49" s="3">
+        <v>45857500</v>
+      </c>
+      <c r="K49" s="3">
         <v>44701000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>44964000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45496200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45402400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45628900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>51142200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>51691900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>50613700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>51132800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>49004600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>49288400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>52874900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>52626800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>53469800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>50862400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>50688100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,8 +4716,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4704,109 +4820,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16542600</v>
+        <v>16531500</v>
       </c>
       <c r="E52" s="3">
-        <v>16368100</v>
+        <v>16147200</v>
       </c>
       <c r="F52" s="3">
-        <v>16217600</v>
+        <v>3852100</v>
       </c>
       <c r="G52" s="3">
-        <v>15477300</v>
+        <v>16222900</v>
       </c>
       <c r="H52" s="3">
-        <v>15184400</v>
+        <v>15045900</v>
       </c>
       <c r="I52" s="3">
-        <v>15638300</v>
+        <v>14851300</v>
       </c>
       <c r="J52" s="3">
+        <v>2621000</v>
+      </c>
+      <c r="K52" s="3">
         <v>15897800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15426700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15507100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4845800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15549900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15552800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14506300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13701700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13552100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9065700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8569300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3651800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4590900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3806500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3348900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4262100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4906,109 +5028,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>251656900</v>
+        <v>251295500</v>
       </c>
       <c r="E54" s="3">
-        <v>248805600</v>
+        <v>245641700</v>
       </c>
       <c r="F54" s="3">
-        <v>256719800</v>
+        <v>244419200</v>
       </c>
       <c r="G54" s="3">
-        <v>255398000</v>
+        <v>256803200</v>
       </c>
       <c r="H54" s="3">
-        <v>250493800</v>
+        <v>248278700</v>
       </c>
       <c r="I54" s="3">
-        <v>247144100</v>
+        <v>244998700</v>
       </c>
       <c r="J54" s="3">
+        <v>255203500</v>
+      </c>
+      <c r="K54" s="3">
         <v>249834000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>236605100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>237497300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>234122000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>242570900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>245304600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>246338700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>235278300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>227629000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>211259100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>201761900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>205560900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>203175800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>180905600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>155660500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>146807400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5044,8 +5172,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5081,68 +5210,69 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>47831600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>41995500</v>
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F57" s="3">
-        <v>44442800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>40405400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>39382900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>38903400</v>
+        <v>17666400</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J57" s="3">
+        <v>16559700</v>
+      </c>
+      <c r="K57" s="3">
         <v>41401000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37560600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36918600</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="N57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38835600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37802900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35961600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36321300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31307500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26279700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24271800</v>
       </c>
-      <c r="U57" s="3" t="s">
+      <c r="V57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
@@ -5182,513 +5312,531 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4216700</v>
+        <v>4665200</v>
       </c>
       <c r="E58" s="3">
-        <v>4088600</v>
+        <v>4115900</v>
       </c>
       <c r="F58" s="3">
-        <v>3715400</v>
+        <v>4829600</v>
       </c>
       <c r="G58" s="3">
-        <v>1154200</v>
+        <v>3716600</v>
       </c>
       <c r="H58" s="3">
-        <v>1161100</v>
+        <v>1122000</v>
       </c>
       <c r="I58" s="3">
-        <v>1729300</v>
+        <v>1135600</v>
       </c>
       <c r="J58" s="3">
+        <v>2610600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1630400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1602900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1883600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1220800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1089300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2679000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2443400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1870400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2094500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>722500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>669500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>806900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>649000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3768400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3516800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3417500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>864900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>956800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13210000</v>
+        <v>12745200</v>
       </c>
       <c r="E59" s="3">
-        <v>13340000</v>
+        <v>12894200</v>
       </c>
       <c r="F59" s="3">
-        <v>15107100</v>
+        <v>30677900</v>
       </c>
       <c r="G59" s="3">
-        <v>13395800</v>
+        <v>15112000</v>
       </c>
       <c r="H59" s="3">
-        <v>13062100</v>
+        <v>13022400</v>
       </c>
       <c r="I59" s="3">
-        <v>13694100</v>
+        <v>12775500</v>
       </c>
       <c r="J59" s="3">
+        <v>31687700</v>
+      </c>
+      <c r="K59" s="3">
         <v>15874900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13732600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13411500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51772100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16634700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14652800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14475700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14336500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16453900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11744900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11617700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>37060600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39764300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34290100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>28673900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>28173100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>65258200</v>
+        <v>63421200</v>
       </c>
       <c r="E60" s="3">
-        <v>59424100</v>
+        <v>63698400</v>
       </c>
       <c r="F60" s="3">
-        <v>63265300</v>
+        <v>58376400</v>
       </c>
       <c r="G60" s="3">
-        <v>54955400</v>
+        <v>63285900</v>
       </c>
       <c r="H60" s="3">
-        <v>53606100</v>
+        <v>53423500</v>
       </c>
       <c r="I60" s="3">
-        <v>54326800</v>
+        <v>52430100</v>
       </c>
       <c r="J60" s="3">
+        <v>56098400</v>
+      </c>
+      <c r="K60" s="3">
         <v>58906400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52896100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52213700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52992900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56559700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>55134700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52880700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52528200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>49855900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38747100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>36559000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>37867500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>40413300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38058500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32190700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31590600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25098200</v>
+        <v>28640800</v>
       </c>
       <c r="E61" s="3">
-        <v>19987400</v>
+        <v>28927300</v>
       </c>
       <c r="F61" s="3">
-        <v>19676900</v>
+        <v>23646800</v>
       </c>
       <c r="G61" s="3">
-        <v>22353400</v>
+        <v>24277700</v>
       </c>
       <c r="H61" s="3">
-        <v>22177100</v>
+        <v>26076700</v>
       </c>
       <c r="I61" s="3">
-        <v>21018400</v>
+        <v>25934500</v>
       </c>
       <c r="J61" s="3">
+        <v>25859800</v>
+      </c>
+      <c r="K61" s="3">
         <v>20901700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20701600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19249000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18296000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18149900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18892700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19187500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18891700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14289200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17224200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17814900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18830400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18196100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18958600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17779000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17012200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>12797700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>12539900</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F62" s="3">
-        <v>12717800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>13136100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>13000800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>13489500</v>
+        <v>401600</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J62" s="3">
+        <v>266600</v>
+      </c>
+      <c r="K62" s="3">
         <v>13568800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13453100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13622800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13403800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13526600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13729800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13614700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13016600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12820300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10694800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10566900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11144900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11048800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10354200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7139000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4589600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5788,8 +5936,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5889,8 +6040,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5990,109 +6144,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>119414100</v>
+        <v>100482400</v>
       </c>
       <c r="E66" s="3">
-        <v>109722600</v>
+        <v>100688600</v>
       </c>
       <c r="F66" s="3">
-        <v>114246800</v>
+        <v>90330300</v>
       </c>
       <c r="G66" s="3">
-        <v>109472100</v>
+        <v>95691100</v>
       </c>
       <c r="H66" s="3">
-        <v>107610000</v>
+        <v>87923700</v>
       </c>
       <c r="I66" s="3">
-        <v>107622300</v>
+        <v>86836300</v>
       </c>
       <c r="J66" s="3">
+        <v>91731600</v>
+      </c>
+      <c r="K66" s="3">
         <v>112244000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105638100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103587700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103156000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106870400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106961600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105035900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>103575200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>96014900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>83728500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>81439100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>85870200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87396600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>85691900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>74973700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>70887900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6128,8 +6288,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6229,8 +6390,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6330,8 +6494,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6366,73 +6533,76 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>1461600</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1477500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1201100</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1207300</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1175300</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1183700</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1152400</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1425200</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1200300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1171000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1083400</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1037300</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>839900</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>452700</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>430600</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>442100</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>133300</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>113200</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>435100</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>515800</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6532,109 +6702,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>81739600</v>
+        <v>86891000</v>
       </c>
       <c r="E72" s="3">
-        <v>86368600</v>
+        <v>79785900</v>
       </c>
       <c r="F72" s="3">
-        <v>89039600</v>
+        <v>84845900</v>
       </c>
       <c r="G72" s="3">
-        <v>91648100</v>
+        <v>89068500</v>
       </c>
       <c r="H72" s="3">
-        <v>88947700</v>
+        <v>89093400</v>
       </c>
       <c r="I72" s="3">
-        <v>86280500</v>
+        <v>86996400</v>
       </c>
       <c r="J72" s="3">
+        <v>89094100</v>
+      </c>
+      <c r="K72" s="3">
         <v>84254400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>76966400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>80286100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>79174500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>81449200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>82138400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>86310300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>78268100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>79111700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>72029000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>67773800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>64563300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>63003500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55694500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>43446200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39985800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6734,8 +6910,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6835,8 +7014,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6936,109 +7118,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>132242800</v>
+        <v>135993300</v>
       </c>
       <c r="E76" s="3">
-        <v>139083000</v>
+        <v>129081900</v>
       </c>
       <c r="F76" s="3">
-        <v>142473000</v>
+        <v>136631000</v>
       </c>
       <c r="G76" s="3">
-        <v>145925900</v>
+        <v>142519300</v>
       </c>
       <c r="H76" s="3">
-        <v>142883800</v>
+        <v>141858100</v>
       </c>
       <c r="I76" s="3">
-        <v>139521800</v>
+        <v>139749300</v>
       </c>
       <c r="J76" s="3">
+        <v>144071700</v>
+      </c>
+      <c r="K76" s="3">
         <v>137590000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>130967000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>133909600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>130966000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>134238900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>136865400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>140101700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130495800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130438900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>126346900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>119170500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>118265600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>114579000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>94042700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>79603400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74882100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7138,215 +7326,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3421400</v>
+        <v>6277400</v>
       </c>
       <c r="E81" s="3">
-        <v>461000</v>
+        <v>3356300</v>
       </c>
       <c r="F81" s="3">
-        <v>2034800</v>
+        <v>466000</v>
       </c>
       <c r="G81" s="3">
-        <v>3906000</v>
+        <v>2052600</v>
       </c>
       <c r="H81" s="3">
-        <v>4840100</v>
+        <v>3816400</v>
       </c>
       <c r="I81" s="3">
-        <v>3315300</v>
+        <v>4721500</v>
       </c>
       <c r="J81" s="3">
+        <v>3442000</v>
+      </c>
+      <c r="K81" s="3">
         <v>6600000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3161200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2814700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>762900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6483200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-762700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11056200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4239400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7013000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>495000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8054500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11317000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3246900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3929300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7382,31 +7579,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>876000</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>921200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>996200</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>1031400</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>1004600</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>999400</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1192800</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7483,8 +7681,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7584,8 +7785,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7685,8 +7889,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7786,8 +7993,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7887,8 +8097,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7988,109 +8201,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4742000</v>
+        <v>4481900</v>
       </c>
       <c r="E89" s="3">
-        <v>3290500</v>
+        <v>4628700</v>
       </c>
       <c r="F89" s="3">
-        <v>9123700</v>
+        <v>3232500</v>
       </c>
       <c r="G89" s="3">
-        <v>6940600</v>
+        <v>9126600</v>
       </c>
       <c r="H89" s="3">
-        <v>6387200</v>
+        <v>6747100</v>
       </c>
       <c r="I89" s="3">
-        <v>4426900</v>
+        <v>6247100</v>
       </c>
       <c r="J89" s="3">
+        <v>4571300</v>
+      </c>
+      <c r="K89" s="3">
         <v>12317400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6509000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4708500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-972100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11072800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5093200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4826100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3366300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14366600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8001100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7382600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>338800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14859800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7383300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5288000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2822300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8126,109 +8345,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12094000</v>
+        <v>-2493500</v>
       </c>
       <c r="E91" s="3">
-        <v>-11995000</v>
+        <v>-1664300</v>
       </c>
       <c r="F91" s="3">
-        <v>-8857000</v>
+        <v>-4443900</v>
       </c>
       <c r="G91" s="3">
-        <v>-5150000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-6927000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3500000</v>
+        <v>-1249100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J91" s="3">
+        <v>-4997700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="N91" s="3">
         <v>-18710000</v>
       </c>
       <c r="O91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="P91" s="3" t="s">
+      <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-453500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-813500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-281000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-975000</v>
       </c>
-      <c r="Y91" s="3" t="s">
+      <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AC91" s="3" t="s">
+      <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8328,8 +8551,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8429,109 +8655,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5051200</v>
+        <v>137400</v>
       </c>
       <c r="E94" s="3">
-        <v>2857200</v>
+        <v>-4930400</v>
       </c>
       <c r="F94" s="3">
-        <v>-4359800</v>
+        <v>2806900</v>
       </c>
       <c r="G94" s="3">
-        <v>-3349800</v>
+        <v>-4361200</v>
       </c>
       <c r="H94" s="3">
-        <v>1775600</v>
+        <v>-3256400</v>
       </c>
       <c r="I94" s="3">
-        <v>-3779400</v>
+        <v>1736700</v>
       </c>
       <c r="J94" s="3">
+        <v>-3902600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8567,31 +8799,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+        <v>4115800</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>2485400</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8668,8 +8901,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8769,8 +9005,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8870,8 +9109,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8971,307 +9213,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2760700</v>
+        <v>-9520600</v>
       </c>
       <c r="E100" s="3">
-        <v>-7614600</v>
+        <v>-2694700</v>
       </c>
       <c r="F100" s="3">
-        <v>-2426800</v>
+        <v>-7480400</v>
       </c>
       <c r="G100" s="3">
-        <v>-1745600</v>
+        <v>-2427600</v>
       </c>
       <c r="H100" s="3">
-        <v>-3473200</v>
+        <v>-1697000</v>
       </c>
       <c r="I100" s="3">
-        <v>-1313800</v>
+        <v>-3397000</v>
       </c>
       <c r="J100" s="3">
+        <v>-1356600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4213600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-791400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1489200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-679200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>464500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9437000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>328600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>686400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>109400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>614200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>361000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>92900</v>
+        <v>111400</v>
       </c>
       <c r="E101" s="3">
-        <v>267900</v>
+        <v>595500</v>
       </c>
       <c r="F101" s="3">
-        <v>-372600</v>
+        <v>-174800</v>
       </c>
       <c r="G101" s="3">
-        <v>114600</v>
+        <v>-294600</v>
       </c>
       <c r="H101" s="3">
-        <v>608900</v>
+        <v>483100</v>
       </c>
       <c r="I101" s="3">
-        <v>-169300</v>
+        <v>496500</v>
       </c>
       <c r="J101" s="3">
+        <v>-144000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-286300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>474700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>462400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-126100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-816200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>27700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-314800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>159900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-575200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-567800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-51700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>363500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>367100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>210400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-173700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>233700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>399300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>253800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2976900</v>
+        <v>-5251400</v>
       </c>
       <c r="E102" s="3">
-        <v>-1199000</v>
+        <v>-2905800</v>
       </c>
       <c r="F102" s="3">
-        <v>1964400</v>
+        <v>-1177900</v>
       </c>
       <c r="G102" s="3">
-        <v>1959800</v>
+        <v>1965100</v>
       </c>
       <c r="H102" s="3">
-        <v>5298600</v>
+        <v>1905100</v>
       </c>
       <c r="I102" s="3">
-        <v>-835600</v>
+        <v>5182400</v>
       </c>
       <c r="J102" s="3">
+        <v>-862800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4273300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3025000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3883800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1904100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18978300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4747700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2955700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>209800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>494500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>291500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,447 +656,459 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38382000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33716300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33471800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30728300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36715800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30807500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32287100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30309200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34928600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28623400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28576300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>28175500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33422700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28528100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29548400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26085400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30774900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22849500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22656700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17897000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24861000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18567800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17558100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14222900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22266300</v>
+      </c>
+      <c r="E9" s="3">
         <v>20533000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20105700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20510800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22030200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19141000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19627800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20044500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21147700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18128000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18024900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19185500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20206500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18444000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17822800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17463200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16880500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13256500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12455300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11350900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12985400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10225800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9164800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8459400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16115700</v>
+      </c>
+      <c r="E10" s="3">
         <v>13183300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13366100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10217600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14685600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11666500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12659300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10264700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13780900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10495500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10551300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8990000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13216100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10084100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11725600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8622200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13894400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9593000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10201400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6546100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11875600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8342000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8393300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5763500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1133,112 +1145,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2008700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2021800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1840300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1950700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1902200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1948600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1443000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2020600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1906200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2093100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1973100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1511100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2163800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2174500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1941600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1851600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1894100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2835900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1633000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1657500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1705600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1706400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1600800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1317200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>959300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>933400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>754400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>696900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>657100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>642800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,216 +1357,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>931200</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>636200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2845900</v>
       </c>
-      <c r="G14" s="3">
-        <v>1690900</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>3395100</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1093300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-953800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>382600</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>89900</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="3">
         <v>309000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E15" s="3">
         <v>235100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>246600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-1768000</v>
       </c>
-      <c r="G15" s="3">
-        <v>2059100</v>
-      </c>
       <c r="H15" s="3">
+        <v>355000</v>
+      </c>
+      <c r="I15" s="3">
         <v>333200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>341800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-46100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>779600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>377000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>382400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>390900</v>
       </c>
       <c r="O15" s="3">
         <v>390900</v>
       </c>
       <c r="P15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>413100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>441300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>475400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>441500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>425600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>435000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>633100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>503800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>469000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>468400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>487200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>408000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>365400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>301900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>190700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>305300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>259400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>294700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>190900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>183400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1584,216 +1609,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31805600</v>
+      </c>
+      <c r="E17" s="3">
         <v>28691600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28086500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26627200</v>
       </c>
-      <c r="G17" s="3">
-        <v>32343800</v>
-      </c>
       <c r="H17" s="3">
+        <v>30639700</v>
+      </c>
+      <c r="I17" s="3">
         <v>26204800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26148300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27516500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29990000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25150500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25108700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25867200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32448800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26395000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25118100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27152100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23953800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20840400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17542600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16780600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18769500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15390900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13834100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12889600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6576400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5024700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5385200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4101100</v>
       </c>
-      <c r="G18" s="3">
-        <v>4371900</v>
-      </c>
       <c r="H18" s="3">
+        <v>6076100</v>
+      </c>
+      <c r="I18" s="3">
         <v>4602700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6138900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2792800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4938700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3472900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3467600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2308300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>973800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2133100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4430200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6821100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2009100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5114100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1116400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6091400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3177000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3724000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1333300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1830,195 +1862,199 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1057300</v>
+      </c>
+      <c r="E20" s="3">
         <v>71300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-242500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>165600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>599300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-581100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-255300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2393600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>761600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3230100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2335000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>309900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5966400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1717900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3482100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2790600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>10377600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>349600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3059700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>714200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>405900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>767600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>498500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>560200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7830400</v>
+      </c>
+      <c r="E21" s="3">
         <v>5188500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5874300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2299100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6265500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4336500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7061800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3002000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7722500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5542300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4157900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>704500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8197100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>564900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12940900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3812200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9866300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1609300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8955000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13596400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5257300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4411900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>10</v>
@@ -2029,329 +2065,341 @@
       <c r="AG21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>340500</v>
+      </c>
+      <c r="E22" s="3">
         <v>346000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>301100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>301500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>254100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>246000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>252700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>218500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>191800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>172900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>164200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>163400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>180100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>182000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>161500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>152000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>162200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>165500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>182400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>201600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>212200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>205600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>198200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>193700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>187500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>174000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>168600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>125300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>110900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>118700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>98300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>101900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7889100</v>
+      </c>
+      <c r="E23" s="3">
         <v>7260100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4690400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>919700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2214800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4453200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5380600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3749200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7113700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4056200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4040500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>560900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6583300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-918300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12635500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3564800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8430800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-89100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8680500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13342400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3867900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4194900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1527400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1052000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1384800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>792500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>703400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>794500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>830400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>547100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>538500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>355300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>750600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>287100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1316200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>865300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1306400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>981200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1279800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>281600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1639200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>411400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1294500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>439200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1025500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>764400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>811300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>38800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>812800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>597500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>988900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>403500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>690600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>662100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>743100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2454,216 +2502,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6361600</v>
+      </c>
+      <c r="E26" s="3">
         <v>6208100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3305700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>127300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1511400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3658700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4550300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3202100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6575200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3305600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2724300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-304300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5276900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11355700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3283200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6791500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7386000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12903300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2842500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3430500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>962900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6705600</v>
+      </c>
+      <c r="E27" s="3">
         <v>6254800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3339700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>452900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2035400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3797100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4733900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3423400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6600000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3161200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2814700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>762900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6483200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-762700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11056200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4239400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7013000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>495000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8054500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11317000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3246900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3929300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2766,8 +2823,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2870,8 +2930,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2974,8 +3037,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3078,216 +3144,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1057300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-71300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>242500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-165600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-599300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>581100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>255300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5458400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-761600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4845000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1392100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-309900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1023100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-349600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6730600</v>
+      </c>
+      <c r="E33" s="3">
         <v>6277400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3356300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>466000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2052600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3816400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4721500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3442000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6600000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3161200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2814700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>762900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6483200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-762700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11056200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4239400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7013000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>495000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8054500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11317000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3246900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3929300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3390,221 +3465,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6730600</v>
+      </c>
+      <c r="E35" s="3">
         <v>6277400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3356300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>466000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2052600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3816400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4721500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3442000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6600000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3161200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2814700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>762900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6483200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-762700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11056200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4239400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7013000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>495000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8054500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11317000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3246900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3929300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3641,8 +3725,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3679,216 +3764,223 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22301900</v>
+      </c>
+      <c r="E41" s="3">
         <v>26087700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30159600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34364000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35933900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33401300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31218400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28109000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27526200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28559200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24569300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26221100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40385100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>38694100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41909600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44719700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43449500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44430400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45573600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51743500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>53981500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36534000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32166100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28899100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39798600</v>
+      </c>
+      <c r="E42" s="3">
         <v>29338700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31616900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>44720400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50712200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>45314800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>43851500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48242000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45672400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38739900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>39836300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36617000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>27806800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>26581900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>27509400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>22575900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20883300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16090800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11389600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5121400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1021700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1066000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1540200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2006300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3898,11 +3990,11 @@
       <c r="E43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="3">
         <v>9542600</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>10</v>
@@ -3910,12 +4002,12 @@
       <c r="I43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K43" s="3">
         <v>9337900</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3991,8 +4083,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4002,11 +4097,11 @@
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3">
         <v>3526100</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -4014,12 +4109,12 @@
       <c r="I44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K44" s="3">
         <v>4155800</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -4095,528 +4190,546 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30766000</v>
+      </c>
+      <c r="E45" s="3">
         <v>31408400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28177900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9651500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27195800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25161900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25647900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9318600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29487800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26333200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25257300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25330800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24828600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25422400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23522800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22260200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18870600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16538500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15436500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15610300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15742300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14770600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10696400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10208500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92866500</v>
+      </c>
+      <c r="E46" s="3">
         <v>86834700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>89954500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>104267600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>113842000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>103878000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>100717700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>101608000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>102686400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>93632300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>89662900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>88168900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93020500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>90698400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>92941800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>89555700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>83203500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>77059700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>72399700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>72475200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>70745500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>52370500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>44402800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>41113900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76295000</v>
+      </c>
+      <c r="E47" s="3">
         <v>78010700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>73595100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>58731800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>60528800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>62509800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>62278200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>65963600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61483200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57773100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>62111600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61204400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>65630300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>65584300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>65281500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>60887500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>59266900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>58735200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>55079600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>54946500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>55746500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>51631700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>38852700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>36743700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31076600</v>
+      </c>
+      <c r="E48" s="3">
         <v>29641000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26726900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36297800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25611400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24591700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24248700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36897900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25065700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24809000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24719400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34500500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22741400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22326900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21917300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20519800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20473800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17393900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16424900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21612600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19466200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19627200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18193700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13999600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37896700</v>
+      </c>
+      <c r="E49" s="3">
         <v>40277600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39218100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39696600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40598100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42253200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42902800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>45857500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>44701000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44964000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45496200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45402400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45628900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>51142200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>51691900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>50613700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>51132800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>49004600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>49288400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>52874900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>52626800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>53469800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>50862400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>50688100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4719,8 +4832,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4823,112 +4939,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16001200</v>
+      </c>
+      <c r="E52" s="3">
         <v>16531500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16147200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3852100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16222900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15045900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14851300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2621000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15897800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15426700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15507100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4845800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15549900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15552800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14506300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13701700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13552100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9065700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8569300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3651800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4590900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3806500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3348900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4262100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5031,112 +5153,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>254136000</v>
+      </c>
+      <c r="E54" s="3">
         <v>251295500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>245641700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>244419200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>256803200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>248278700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244998700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>255203500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>249834000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>236605100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>237497300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>234122000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>242570900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>245304600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>246338700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>235278300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>227629000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>211259100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>201761900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>205560900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>203175800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>180905600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>155660500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>146807400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5173,8 +5301,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5211,8 +5340,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5222,11 +5352,11 @@
       <c r="E57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="3">
         <v>17666400</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>10</v>
@@ -5234,48 +5364,48 @@
       <c r="I57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K57" s="3">
         <v>16559700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41401000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37560600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36918600</v>
       </c>
-      <c r="N57" s="3" t="s">
+      <c r="O57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38835600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37802900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35961600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36321300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31307500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26279700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24271800</v>
       </c>
-      <c r="V57" s="3" t="s">
+      <c r="W57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
@@ -5315,424 +5445,439 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2939100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4665200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4115900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4829600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3716600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1122000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1135600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2610600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1630400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1602900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1883600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1220800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1089300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2679000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2443400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1870400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2094500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>722500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>669500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>806900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>649000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3768400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3516800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3417500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>864900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>956800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13093100</v>
+      </c>
+      <c r="E59" s="3">
         <v>12745200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12894200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30677900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15112000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13022400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12775500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31687700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15874900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13732600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13411500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>51772100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16634700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14652800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14475700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14336500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16453900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11744900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11617700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>37060600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>39764300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34290100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>28673900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>28173100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>62659600</v>
+      </c>
+      <c r="E60" s="3">
         <v>63421200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63698400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58376400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63285900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53423500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52430100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56098400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58906400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52896100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52213700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52992900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56559700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>55134700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52880700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52528200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>49855900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38747100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>36559000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>37867500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>40413300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>38058500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32190700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>31590600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33271000</v>
+      </c>
+      <c r="E61" s="3">
         <v>28640800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28927300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23646800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24277700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26076700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25934500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25859800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20901700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20701600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19249000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18296000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18149900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18892700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19187500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18891700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14289200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17224200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17814900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18830400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18196100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18958600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17779000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17012200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5742,11 +5887,11 @@
       <c r="E62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3">
         <v>401600</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>10</v>
@@ -5754,89 +5899,92 @@
       <c r="I62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="3">
         <v>266600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13568800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13453100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13622800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13403800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13526600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13729800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13614700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13016600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12820300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10694800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10566900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11144900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11048800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10354200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7139000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4589600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5939,8 +6087,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6043,8 +6194,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6147,112 +6301,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>104145600</v>
+      </c>
+      <c r="E66" s="3">
         <v>100482400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100688600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>90330300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>95691100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87923700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86836300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91731600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112244000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105638100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103587700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103156000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106870400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106961600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105035900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>103575200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>96014900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>83728500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>81439100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>85870200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87396600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>85691900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>74973700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>70887900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6289,8 +6449,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6393,8 +6554,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6497,8 +6661,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6536,73 +6703,76 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1461600</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1477500</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1201100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1207300</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1175300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1183700</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1152400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1425200</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1200300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1171000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1083400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1037300</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>839900</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>452700</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>430600</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>442100</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>133300</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>113200</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>435100</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>515800</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6705,112 +6875,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>89370200</v>
+      </c>
+      <c r="E72" s="3">
         <v>86891000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>79785900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>84845900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>89068500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>89093400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>86996400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>89094100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>84254400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76966400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>80286100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>79174500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>81449200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>82138400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>86310300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>78268100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>79111700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>72029000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>67773800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>64563300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>63003500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>55694500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>43446200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39985800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6913,8 +7089,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7017,8 +7196,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7121,112 +7303,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>137157900</v>
+      </c>
+      <c r="E76" s="3">
         <v>135993300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>129081900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>136631000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>142519300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>141858100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>139749300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>144071700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>137590000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>130967000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>133909600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>130966000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>134238900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>136865400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>140101700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130495800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>130438900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>126346900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>119170500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>118265600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>114579000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>94042700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>79603400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>74882100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7329,221 +7517,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6730600</v>
+      </c>
+      <c r="E81" s="3">
         <v>6277400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3356300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>466000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2052600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3816400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4721500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3442000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6600000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3161200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2814700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>762900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6483200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-762700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11056200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4239400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7013000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>495000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8054500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11317000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3246900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3929300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7580,35 +7777,36 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>949000</v>
+      </c>
+      <c r="E83" s="3">
         <v>876000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>921200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>996200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1031400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1004600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>999400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1192800</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7684,8 +7882,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7788,8 +7989,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7892,8 +8096,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7996,8 +8203,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8100,8 +8310,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8204,112 +8417,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9715600</v>
+      </c>
+      <c r="E89" s="3">
         <v>4481900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4628700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3232500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9126600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6747100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6247100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4571300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12317400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6509000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4708500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-972100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11072800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5093200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4826100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3366300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14366600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8001100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7382600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>338800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14859800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7383300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5288000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2822300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8346,22 +8565,23 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4353300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2493500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1664300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4443900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1249100</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>10</v>
@@ -8369,89 +8589,92 @@
       <c r="I91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4997700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="O91" s="3">
         <v>-18710000</v>
       </c>
       <c r="P91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="Q91" s="3" t="s">
+      <c r="R91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-453500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-813500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-281000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z91" s="3" t="s">
+      <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AD91" s="3" t="s">
+      <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8554,8 +8777,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8658,112 +8884,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15207800</v>
+      </c>
+      <c r="E94" s="3">
         <v>137400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4930400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2806900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4361200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3256400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1736700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3902600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8800,22 +9032,23 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
         <v>4115800</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2485400</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>10</v>
@@ -8826,8 +9059,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8904,8 +9137,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9008,8 +9244,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9112,8 +9351,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9216,316 +9458,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1952400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9520600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2694700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7480400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2427600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1697000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1356600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4213600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-791400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1489200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-679200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>464500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9437000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>328600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>686400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>109400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>614200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>361000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-372700</v>
+      </c>
+      <c r="E101" s="3">
         <v>111400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>595500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-174800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-294600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>483100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>496500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-144000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-286300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>474700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>462400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-126100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-816200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>27700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-314800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>159900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-575200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-567800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-51700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>363500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>367100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>210400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-173700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>233700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>399300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>253800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3083400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5251400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2905800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1177900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1965100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1905100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5182400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-862800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4273300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3025000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3883800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1904100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18978300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4747700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2955700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>209800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>494500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>291500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,459 +656,471 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32585100</v>
+      </c>
+      <c r="E8" s="3">
         <v>38382000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33716300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33471800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30728300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>36715800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30807500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32287100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30309200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34928600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28623400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>28576300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>28175500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33422700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28528100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29548400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26085400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30774900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22849500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22656700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17897000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24861000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18567800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17558100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14222900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20068400</v>
+      </c>
+      <c r="E9" s="3">
         <v>22266300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20533000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20105700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20510800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22030200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19141000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19627800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20044500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21147700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18128000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18024900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19185500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20206500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18444000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17822800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17463200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16880500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13256500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12455300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11350900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12985400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10225800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9164800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8459400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12516800</v>
+      </c>
+      <c r="E10" s="3">
         <v>16115700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13183300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13366100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10217600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14685600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11666500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12659300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10264700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13780900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10495500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10551300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8990000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13216100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10084100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11725600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8622200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13894400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9593000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10201400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6546100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11875600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8342000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8393300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5763500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1146,115 +1158,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2058000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2008700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2021800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1840300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1950700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1902200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1948600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1443000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2020600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1906200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2093100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1973100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1511100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2163800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2174500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1941600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1851600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1894100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2835900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1633000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1657500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1705600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1706400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1600800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1317200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>959300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>933400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>754400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>696900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>657100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>642800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1360,222 +1376,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1035800</v>
+      </c>
+      <c r="E14" s="3">
         <v>931200</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>636200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2845900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3395100</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1093300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-953800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>382600</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>89900</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>309000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E15" s="3">
         <v>196700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>235100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>246600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-1768000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>355000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>333200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>341800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-46100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>779600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>377000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>382400</v>
-      </c>
-      <c r="O15" s="3">
-        <v>390900</v>
       </c>
       <c r="P15" s="3">
         <v>390900</v>
       </c>
       <c r="Q15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="R15" s="3">
         <v>413100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>441300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>475400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>441500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>425600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>435000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>633100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>503800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>469000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>468400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>487200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>408000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>365400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>301900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>190700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>305300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>259400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>294700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>190900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>183400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1610,222 +1635,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28662400</v>
+      </c>
+      <c r="E17" s="3">
         <v>31805600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28691600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28086500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26627200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30639700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26204800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26148300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27516500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29990000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25150500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25108700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25867200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32448800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26395000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25118100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27152100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23953800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20840400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17542600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16780600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18769500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15390900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13834100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12889600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3922700</v>
+      </c>
+      <c r="E18" s="3">
         <v>6576400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5024700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5385200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4101100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6076100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4602700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6138900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2792800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4938700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3472900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3467600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2308300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>973800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2133100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4430200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6821100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2009100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5114100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1116400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6091400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3177000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3724000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1333300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1863,201 +1895,205 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1057300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>71300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-242500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>165600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>599300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-581100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-255300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2393600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>761600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3230100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2335000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>309900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5966400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1717900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3482100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2790600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>10377600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>349600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3059700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>714200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>405900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>767600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>498500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>560200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4089000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7830400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5188500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5874300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2299100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6265500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4336500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7061800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3002000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7722500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5542300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4157900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>704500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8197100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>564900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12940900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3812200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9866300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1609300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8955000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13596400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5257300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4411900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>10</v>
@@ -2068,338 +2104,350 @@
       <c r="AH21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E22" s="3">
         <v>340500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>346000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>301100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>301500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>254100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>246000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>252700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>218500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>191800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>172900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>164200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>163400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>180100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>182000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>161500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>152000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>162200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>165500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>182400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>201600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>212200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>205600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>198200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>193700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>187500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>174000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>168600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>125300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>110900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>118700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>98300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>101900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2594500</v>
+      </c>
+      <c r="E23" s="3">
         <v>7889100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7260100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4690400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>919700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2214800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4453200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5380600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3749200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7113700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4056200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4040500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>560900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6583300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-918300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12635500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3564800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8430800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-89100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8680500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13342400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3867900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4194900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>944500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1527400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1052000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1384800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>792500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>703400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>794500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>830400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>547100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>538500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>355300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>750600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>287100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1316200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>865300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1306400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>981200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1279800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>281600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1639200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>411400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1294500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>439200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1025500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>764400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>811300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>38800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>812800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>597500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>988900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>403500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>690600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>662100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>743100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2505,222 +2553,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1650000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6361600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6208100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3305700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>127300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1511400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3658700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4550300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3202100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6575200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3305600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2724300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-304300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5276900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11355700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3283200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6791500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7386000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12903300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2842500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3430500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>962900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1706300</v>
+      </c>
+      <c r="E27" s="3">
         <v>6705600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6254800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3339700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>452900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2035400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3797100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4733900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3423400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6600000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3161200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2814700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>762900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6483200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-762700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11056200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4239400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7013000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>495000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8054500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11317000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3246900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3929300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2826,8 +2883,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2933,8 +2993,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3040,8 +3103,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3147,222 +3213,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1057300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-71300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>242500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-165600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-599300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>581100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>255300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5458400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-761600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4845000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1392100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-309900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1023100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-349600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1730700</v>
+      </c>
+      <c r="E33" s="3">
         <v>6730600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6277400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3356300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>466000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2052600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3816400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4721500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3442000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6600000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3161200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2814700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>762900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6483200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-762700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11056200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4239400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7013000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>495000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8054500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11317000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3246900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3929300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3468,227 +3543,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1730700</v>
+      </c>
+      <c r="E35" s="3">
         <v>6730600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6277400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3356300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>466000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2052600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3816400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4721500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3442000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6600000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3161200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2814700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>762900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6483200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-762700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11056200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4239400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7013000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>495000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8054500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11317000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3246900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3929300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3726,8 +3810,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3765,222 +3850,229 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20049200</v>
+      </c>
+      <c r="E41" s="3">
         <v>22301900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26087700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30159600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34364000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35933900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33401300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31218400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28109000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27526200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28559200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24569300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26221100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40385100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>38694100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41909600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44719700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43449500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44430400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>45573600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51743500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>53981500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36534000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32166100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28899100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>38945200</v>
+      </c>
+      <c r="E42" s="3">
         <v>39798600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29338700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31616900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44720400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50712200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>45314800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>43851500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48242000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>45672400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38739900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39836300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>36617000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27806800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26581900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>27509400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>22575900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20883300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16090800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11389600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5121400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1021700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1066000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1540200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2006300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3993,11 +4085,11 @@
       <c r="F43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="3">
         <v>9542600</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>10</v>
@@ -4005,12 +4097,12 @@
       <c r="J43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" s="3">
         <v>9337900</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4086,8 +4178,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4100,11 +4195,11 @@
       <c r="F44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3">
         <v>3526100</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>10</v>
@@ -4112,12 +4207,12 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" s="3">
         <v>4155800</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -4193,543 +4288,561 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33894600</v>
+      </c>
+      <c r="E45" s="3">
         <v>30766000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31408400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28177900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9651500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27195800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25161900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25647900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9318600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29487800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26333200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25257300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25330800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24828600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25422400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23522800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22260200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18870600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16538500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15436500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15610300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15742300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14770600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10696400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10208500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92889000</v>
+      </c>
+      <c r="E46" s="3">
         <v>92866500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>86834700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>89954500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>104267600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>113842000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103878000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>100717700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>101608000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>102686400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>93632300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>89662900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>88168900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>93020500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>90698400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>92941800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>89555700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>83203500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>77059700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>72399700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>72475200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>70745500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>52370500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>44402800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41113900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>78135100</v>
+      </c>
+      <c r="E47" s="3">
         <v>76295000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>78010700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>73595100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>58731800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>60528800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>62509800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>62278200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>65963600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61483200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>57773100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>62111600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61204400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>65630300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>65584300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65281500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>60887500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>59266900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58735200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>55079600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>54946500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55746500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>51631700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>38852700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>36743700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28022900</v>
+      </c>
+      <c r="E48" s="3">
         <v>31076600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29641000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26726900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36297800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25611400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24591700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24248700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36897900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25065700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24809000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24719400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34500500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22741400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22326900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21917300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20519800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20473800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17393900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16424900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21612600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19466200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19627200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18193700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13999600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38091600</v>
+      </c>
+      <c r="E49" s="3">
         <v>37896700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40277600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39218100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39696600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>40598100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42253200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>42902800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45857500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44701000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44964000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45496200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45402400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>45628900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>51142200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>51691900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>50613700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>51132800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>49004600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>49288400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>52874900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>52626800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>53469800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>50862400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>50688100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4835,8 +4948,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4942,115 +5058,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11497400</v>
+      </c>
+      <c r="E52" s="3">
         <v>16001200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16531500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16147200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3852100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16222900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15045900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14851300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2621000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15897800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15426700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15507100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4845800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15549900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15552800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14506300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13701700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13552100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9065700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8569300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3651800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4590900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3806500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3348900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4262100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5156,115 +5278,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>248636000</v>
+      </c>
+      <c r="E54" s="3">
         <v>254136000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>251295500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>245641700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>244419200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>256803200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>248278700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>244998700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>255203500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>249834000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>236605100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>237497300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>234122000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>242570900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>245304600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>246338700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>235278300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>227629000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>211259100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>201761900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>205560900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>203175800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>180905600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>155660500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>146807400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5302,8 +5430,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5341,8 +5470,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5355,11 +5485,11 @@
       <c r="F57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="3">
         <v>17666400</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>10</v>
@@ -5367,48 +5497,48 @@
       <c r="J57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="3">
         <v>16559700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41401000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37560600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36918600</v>
       </c>
-      <c r="O57" s="3" t="s">
+      <c r="P57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38835600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>37802900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35961600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36321300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>31307500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26279700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24271800</v>
       </c>
-      <c r="W57" s="3" t="s">
+      <c r="X57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
@@ -5448,436 +5578,451 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3109200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2939100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4665200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4115900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4829600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3716600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1122000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1135600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2610600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1630400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1602900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1883600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1220800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1089300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2679000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2443400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1870400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2094500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>722500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>669500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>806900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>649000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3768400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3516800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3417500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>864900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>956800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11058600</v>
+      </c>
+      <c r="E59" s="3">
         <v>13093100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12745200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12894200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30677900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15112000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13022400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12775500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31687700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15874900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13732600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13411500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51772100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16634700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14652800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14475700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14336500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16453900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11744900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11617700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37060600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>39764300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>34290100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>28673900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>28173100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59993900</v>
+      </c>
+      <c r="E60" s="3">
         <v>62659600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63421200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>63698400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58376400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>63285900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53423500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52430100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56098400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58906400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>52896100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52213700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52992900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56559700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>55134700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52880700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>52528200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>49855900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38747100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36559000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>37867500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>40413300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>38058500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32190700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31590600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31114900</v>
+      </c>
+      <c r="E61" s="3">
         <v>33271000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28640800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28927300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23646800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24277700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26076700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25934500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25859800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20901700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20701600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19249000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18296000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18149900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18892700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19187500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18891700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14289200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17224200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17814900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18830400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18196100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18958600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17779000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17012200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5890,11 +6035,11 @@
       <c r="F62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3">
         <v>401600</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>10</v>
@@ -5902,89 +6047,92 @@
       <c r="J62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="3">
         <v>266600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13568800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13453100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13622800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13403800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13526600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13729800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13614700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13016600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12820300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10694800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10566900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11144900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11048800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10354200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7139000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4589600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6090,8 +6238,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6197,8 +6348,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6304,115 +6458,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>98411200</v>
+      </c>
+      <c r="E66" s="3">
         <v>104145600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100482400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100688600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>90330300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>95691100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>87923700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>86836300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91731600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112244000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105638100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103587700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103156000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106870400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106961600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>105035900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>103575200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>96014900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>83728500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>81439100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>85870200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>87396600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>85691900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>74973700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>70887900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6450,8 +6610,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6557,8 +6718,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6664,8 +6828,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6706,73 +6873,76 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1461600</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1477500</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1201100</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1207300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1175300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1183700</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1152400</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1425200</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1200300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1171000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1083400</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>1037300</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>839900</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>452700</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>430600</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>442100</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>133300</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>113200</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>435100</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>515800</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6878,115 +7048,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>91147800</v>
+      </c>
+      <c r="E72" s="3">
         <v>89370200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>86891000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>79785900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>84845900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>89068500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>89093400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86996400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>89094100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>84254400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>76966400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>80286100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>79174500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>81449200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>82138400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>86310300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>78268100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>79111700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>72029000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>67773800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>64563300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>63003500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55694500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>43446200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39985800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7092,8 +7268,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7199,8 +7378,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7306,115 +7488,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>139166000</v>
+      </c>
+      <c r="E76" s="3">
         <v>137157900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>135993300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>129081900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>136631000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>142519300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>141858100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>139749300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>144071700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>137590000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>130967000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>133909600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130966000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>134238900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>136865400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>140101700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>130495800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>130438900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>126346900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>119170500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>118265600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>114579000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>94042700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>79603400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>74882100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7520,227 +7708,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1730700</v>
+      </c>
+      <c r="E81" s="3">
         <v>6730600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6277400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3356300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>466000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2052600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3816400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4721500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3442000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6600000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3161200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2814700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>762900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6483200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-762700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11056200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4239400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7013000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>495000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8054500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11317000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3246900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3929300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7778,38 +7975,39 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>718900</v>
+      </c>
+      <c r="E83" s="3">
         <v>949000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>876000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>921200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>996200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1031400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1004600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>999400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1192800</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7885,8 +8083,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7992,8 +8193,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8099,8 +8303,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8206,8 +8413,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8313,8 +8523,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8420,115 +8633,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3792500</v>
+      </c>
+      <c r="E89" s="3">
         <v>9715600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4481900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4628700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3232500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9126600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6747100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6247100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4571300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12317400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6509000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4708500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-972100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11072800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5093200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4826100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3366300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14366600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8001100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7382600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>338800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14859800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7383300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5288000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2822300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8566,25 +8785,26 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11847600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4353300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2493500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1664300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4443900</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>10</v>
@@ -8592,89 +8812,92 @@
       <c r="J91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L91" s="3">
         <v>-4997700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="P91" s="3">
         <v>-18710000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="R91" s="3" t="s">
+      <c r="S91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-453500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-813500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-281000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-975000</v>
       </c>
-      <c r="AA91" s="3" t="s">
+      <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AE91" s="3" t="s">
+      <c r="AF91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8780,8 +9003,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8887,115 +9113,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5449900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15207800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>137400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4930400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2806900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4361200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3256400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1736700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3902600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9033,25 +9265,26 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4115800</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2485400</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>10</v>
@@ -9062,8 +9295,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9140,8 +9373,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9247,8 +9483,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9354,8 +9593,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9461,325 +9703,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-565300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1952400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9520600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2694700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7480400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2427600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1697000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1356600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4213600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-791400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1489200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-679200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>464500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9437000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>328600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>686400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>109400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>614200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>361000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-372700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>111400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>595500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-174800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-294600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>483100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>496500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-144000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-286300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>474700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>462400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-126100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-816200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>27700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-314800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>159900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-575200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-567800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-51700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>363500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>367100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>210400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-173700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>233700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>399300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>253800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2301100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3083400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5251400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2905800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1177900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1965100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1905100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5182400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-862800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4273300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3025000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3883800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1904100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18978300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4747700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2955700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>209800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>494500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>291500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -1385,7 +1385,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1035800</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>931200</v>
@@ -1397,7 +1397,7 @@
         <v>636200</v>
       </c>
       <c r="H14" s="3">
-        <v>2845900</v>
+        <v>877500</v>
       </c>
       <c r="I14" s="3">
         <v>3395100</v>
@@ -1507,7 +1507,7 @@
         <v>246600</v>
       </c>
       <c r="H15" s="3">
-        <v>-1768000</v>
+        <v>200400</v>
       </c>
       <c r="I15" s="3">
         <v>355000</v>
@@ -1654,7 +1654,7 @@
         <v>28086500</v>
       </c>
       <c r="H17" s="3">
-        <v>26627200</v>
+        <v>28595700</v>
       </c>
       <c r="I17" s="3">
         <v>30639700</v>
@@ -1764,7 +1764,7 @@
         <v>5385200</v>
       </c>
       <c r="H18" s="3">
-        <v>4101100</v>
+        <v>2132700</v>
       </c>
       <c r="I18" s="3">
         <v>6076100</v>
@@ -4076,8 +4076,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
+      <c r="D43" s="3">
+        <v>10487000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>10</v>
@@ -4186,8 +4186,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
+      <c r="D44" s="3">
+        <v>2602800</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>10</v>
@@ -4297,7 +4297,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33894600</v>
+        <v>17972000</v>
       </c>
       <c r="E45" s="3">
         <v>30766000</v>
@@ -4627,7 +4627,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>28022900</v>
+        <v>33425200</v>
       </c>
       <c r="E48" s="3">
         <v>31076600</v>
@@ -5067,7 +5067,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11497400</v>
+        <v>4281400</v>
       </c>
       <c r="E52" s="3">
         <v>16001200</v>
@@ -5476,8 +5476,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>10</v>
+      <c r="D57" s="3">
+        <v>16401400</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>10</v>
@@ -5587,7 +5587,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3109200</v>
+        <v>3652700</v>
       </c>
       <c r="E58" s="3">
         <v>2939100</v>
@@ -5697,7 +5697,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11058600</v>
+        <v>34517600</v>
       </c>
       <c r="E59" s="3">
         <v>13093100</v>
@@ -5917,7 +5917,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>31114900</v>
+        <v>30538700</v>
       </c>
       <c r="E61" s="3">
         <v>33271000</v>
@@ -6026,8 +6026,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>10</v>
+      <c r="D62" s="3">
+        <v>576200</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>10</v>
@@ -7982,7 +7982,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>718900</v>
+        <v>947000</v>
       </c>
       <c r="E83" s="3">
         <v>949000</v>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,483 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34806600</v>
+      </c>
+      <c r="E8" s="3">
         <v>34569900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32585100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38382000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33716300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33471800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30728300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36715800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30807500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32287100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30309200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34928600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>28623400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28576300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28175500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33422700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28528100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29548400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26085400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30774900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22849500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22656700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17897000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24861000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18567800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17558100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14222900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21179500</v>
+      </c>
+      <c r="E9" s="3">
         <v>19044200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20068400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22266300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20533000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20105700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20510800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22030200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19141000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19627800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20044500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21147700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18128000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18024900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19185500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20206500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18444000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17822800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17463200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16880500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13256500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12455300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11350900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12985400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10225800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9164800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8459400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13627100</v>
+      </c>
+      <c r="E10" s="3">
         <v>15525700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12516800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16115700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13183300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13366100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10217600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14685600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11666500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12659300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10264700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13780900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10495500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10551300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8990000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13216100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10084100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11725600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8622200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13894400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9593000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10201400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6546100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11875600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8342000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8393300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5763500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1172,121 +1184,125 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2401300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2094000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2058000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2008700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2021800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1840300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1950700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1902200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1948600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1443000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2020600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1906200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2093100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1973100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1511100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2163800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2174500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1941600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1851600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1894100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2835900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1633000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1657500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1705600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1706400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1600800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1317200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>959300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>933400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>754400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>696900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>657100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>642800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1398,234 +1414,243 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>635400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>931200</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>636200</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2845900</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3395100</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
-        <v>636200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2845900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3395100</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1093300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-953800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>382600</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>89900</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
         <v>309000</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E15" s="3">
         <v>112600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-520600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>196700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>235100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>246600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-1768000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>355000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>333200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>341800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-46100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>779600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>377000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>382400</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>390900</v>
       </c>
       <c r="R15" s="3">
         <v>390900</v>
       </c>
       <c r="S15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="T15" s="3">
         <v>413100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>441300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>475400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>441500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>425600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>435000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>633100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>503800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>469000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>468400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>487200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>408000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>365400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>301900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>190700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>305300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>259400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>294700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>190900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>183400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1662,234 +1687,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34053000</v>
+      </c>
+      <c r="E17" s="3">
         <v>29685900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28027000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31805600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28691600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28086500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26627200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30639700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26204800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26148300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27516500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29990000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25150500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25108700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25867200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32448800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26395000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25118100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27152100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23953800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20840400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17542600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16780600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18769500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>15390900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13834100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12889600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>753600</v>
+      </c>
+      <c r="E18" s="3">
         <v>4884000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4558100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6576400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5024700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5385200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4101100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6076100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4602700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6138900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2792800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4938700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3472900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3467600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2308300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>973800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2133100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4430200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6821100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2009100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5114100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1116400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6091400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3177000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3724000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1333300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1929,213 +1961,217 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-452600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-190000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-51500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1057300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>71300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-242500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>33900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>165600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>599300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-581100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-255300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2393600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>761600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3230100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2335000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>309900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5966400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1717900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3482100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2790600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10377600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>349600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3059700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>714200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>405900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>767600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>498500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>560200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1322200</v>
+      </c>
+      <c r="E21" s="3">
         <v>5186600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4089000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7830400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5188500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5874300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2299100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6265500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4336500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7061800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3002000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7722500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5542300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4157900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>704500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8197100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>564900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12940900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3812200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9866300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1609300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8955000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13596400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5257300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4411900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>10</v>
@@ -2146,356 +2182,368 @@
       <c r="AJ21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>353600</v>
+      </c>
+      <c r="E22" s="3">
         <v>345900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>344000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>340500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>346000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>301100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>301500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>254100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>246000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>252700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>218500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>191800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>172900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>164200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>163400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>180100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>182000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>161500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>152000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>162200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>165500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>182400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>201600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>212200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>205600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>198200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>193700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>187500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>174000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>168600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>125300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>110900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>118700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>98300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>101900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3674900</v>
+      </c>
+      <c r="E23" s="3">
         <v>7153600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2594500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7889100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7260100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4690400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>919700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2214800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4453200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5380600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3749200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7113700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4056200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4040500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>560900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6583300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-918300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12635500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3564800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8430800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-89100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8680500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>13342400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3867900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4194900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>779600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1237500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>944500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1527400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1052000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1384800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>792500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>703400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>794500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>830400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>547100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>538500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>355300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>750600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>287100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1316200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>865300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1306400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>981200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1279800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>281600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1639200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>411400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1294500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>439200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1025500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>764400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>811300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>38800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>812800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>597500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>988900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>403500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>690600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>662100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>743100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2607,234 +2655,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2895300</v>
+      </c>
+      <c r="E26" s="3">
         <v>5916100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1650000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6361600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6208100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3305700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>127300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1511400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3658700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4550300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3202100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6575200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3305600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2724300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-304300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5276900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11355700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3283200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6791500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7386000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12903300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2842500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3430500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>962900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2948400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6018600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1706300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6705600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6254800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3339700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>452900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2035400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3797100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4733900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3423400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6600000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3161200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2814700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>762900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6483200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-762700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11056200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4239400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7013000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>495000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8054500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11317000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3246900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3929300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2946,8 +3003,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3059,8 +3119,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3172,8 +3235,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3285,234 +3351,243 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>452600</v>
+      </c>
+      <c r="E32" s="3">
         <v>190000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>51500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1057300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-71300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>242500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-33900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-165600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-599300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>581100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>255300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5458400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-761600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4845000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1392100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-309900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1023100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-349600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2952400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5674200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1730700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6730600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6277400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3356300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>466000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2052600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3816400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4721500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3442000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6600000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3161200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2814700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>762900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6483200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-762700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11056200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4239400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7013000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>495000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8054500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11317000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3246900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3929300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3624,239 +3699,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2952400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5674200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1730700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6730600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6277400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3356300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>466000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2052600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3816400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4721500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3442000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6600000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3161200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2814700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>762900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6483200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-762700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11056200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4239400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7013000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>495000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8054500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11317000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3246900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3929300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3896,8 +3980,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3937,245 +4022,252 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18972500</v>
+      </c>
+      <c r="E41" s="3">
         <v>25561900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20049200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22301900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26087700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30159600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34364000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35933900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33401300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31218400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28109000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27526200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28559200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24569300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26221100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40385100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38694100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>41909600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44719700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43449500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>44430400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>45573600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>51743500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>53981500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36534000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32166100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28899100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>33501400</v>
+      </c>
+      <c r="E42" s="3">
         <v>32565800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38945200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>39798600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29338700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31616900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>44720400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>50712200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45314800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43851500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>48242000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45672400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>38739900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39836300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>36617000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>27806800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>26581900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>27509400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>22575900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>20883300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>16090800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11389600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5121400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1021700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1066000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1540200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2006300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3">
         <v>10487000</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -4183,11 +4275,11 @@
       <c r="H43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="3">
         <v>9542600</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>10</v>
@@ -4195,12 +4287,12 @@
       <c r="L43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N43" s="3">
         <v>9337900</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
@@ -4276,19 +4368,22 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3">
         <v>2602800</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -4296,11 +4391,11 @@
       <c r="H44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3">
         <v>3526100</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>10</v>
@@ -4308,12 +4403,12 @@
       <c r="L44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N44" s="3">
         <v>4155800</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
@@ -4389,573 +4484,591 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5671100</v>
+      </c>
+      <c r="E45" s="3">
         <v>5787300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17972000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30766000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6483700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28177900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9651500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27195800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25161900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25647900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9318600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29487800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26333200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25257300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25330800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24828600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25422400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23522800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22260200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>18870600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16538500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15436500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15610300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15742300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14770600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10696400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10208500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>90827500</v>
+      </c>
+      <c r="E46" s="3">
         <v>95769100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>92889000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92866500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86834700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>89954500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>104267600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>113842000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>103878000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>100717700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101608000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>102686400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93632300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>89662900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>88168900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>93020500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>90698400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>92941800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>89555700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>83203500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>77059700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>72399700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>72475200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>70745500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>52370500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>44402800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>41113900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86922000</v>
+      </c>
+      <c r="E47" s="3">
         <v>79733100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>78135100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>76295000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>78010700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>73595100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58731800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>60528800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>62509800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>62278200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65963600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61483200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>57773100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>62111600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61204400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65630300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>65584300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>65281500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>60887500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>59266900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>58735200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55079600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>54946500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>55746500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>51631700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>38852700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>36743700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34630200</v>
+      </c>
+      <c r="E48" s="3">
         <v>30826500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33425200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31076600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29641000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26726900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36297800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25611400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24591700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24248700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36897900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25065700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24809000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24719400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34500500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22741400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22326900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21917300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20519800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20473800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17393900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16424900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21612600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19466200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19627200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18193700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13999600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38625100</v>
+      </c>
+      <c r="E49" s="3">
         <v>38485600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>38091600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>37896700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40277600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39218100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>39696600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40598100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>42253200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>42902800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45857500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>44701000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>44964000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>45496200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>45402400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>45628900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>51142200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>51691900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>50613700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>51132800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>49004600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>49288400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>52874900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>52626800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>53469800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>50862400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>50688100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5067,8 +5180,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5180,121 +5296,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13614900</v>
+      </c>
+      <c r="E52" s="3">
         <v>13021600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4281400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16001200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16531500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16147200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3852100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16222900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15045900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14851300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2621000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15897800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15426700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15507100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4845800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15549900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15552800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14506300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13701700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13552100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9065700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8569300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3651800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4590900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3806500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3348900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4262100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5406,121 +5528,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>264619600</v>
+      </c>
+      <c r="E54" s="3">
         <v>257835900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>248636000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>254136000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>251295500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>245641700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244419200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256803200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>248278700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>244998700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>255203500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>249834000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>236605100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>237497300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>234122000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>242570900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>245304600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>246338700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>235278300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>227629000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>211259100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>201761900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>205560900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>203175800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>180905600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>155660500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>146807400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5560,8 +5688,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5601,19 +5730,20 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="3">
         <v>16401400</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -5621,11 +5751,11 @@
       <c r="H57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="3">
         <v>17666400</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>10</v>
@@ -5633,48 +5763,48 @@
       <c r="L57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N57" s="3">
         <v>16559700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41401000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37560600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36918600</v>
       </c>
-      <c r="Q57" s="3" t="s">
+      <c r="R57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>38835600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37802900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35961600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36321300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>31307500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26279700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24271800</v>
       </c>
-      <c r="Y57" s="3" t="s">
+      <c r="Z57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
@@ -5714,471 +5844,486 @@
       <c r="AM57" s="3">
         <v>0</v>
       </c>
+      <c r="AN57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3692500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3431700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3652700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2939100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4665200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4115900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4829600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3716600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1122000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1135600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2610600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1630400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1602900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1883600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1220800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1089300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2679000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2443400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1870400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2094500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>722500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>669500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>806900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>649000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3768400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3516800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3417500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>864900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>956800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10827100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10807000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34517600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13093100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12745200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12894200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30677900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15112000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13022400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12775500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31687700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15874900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13732600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13411500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51772100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16634700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14652800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14475700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14336500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16453900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11744900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11617700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>37060600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>39764300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>34290100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>28673900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>28173100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>62385800</v>
+      </c>
+      <c r="E60" s="3">
         <v>66113900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59993900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62659600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63421200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>63698400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58376400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>63285900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53423500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52430100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56098400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>58906400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52896100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52213700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52992900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56559700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>55134700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>52880700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>52528200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>49855900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38747100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36559000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>37867500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>40413300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38058500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>32190700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>31590600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38861100</v>
+      </c>
+      <c r="E61" s="3">
         <v>31921900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30538700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33271000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28640800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28927300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23646800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24277700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26076700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25934500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25859800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20901700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20701600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19249000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18296000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18149900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18892700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19187500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18891700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14289200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17224200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17814900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18830400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>18196100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18958600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17779000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17012200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3">
         <v>576200</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
@@ -6186,11 +6331,11 @@
       <c r="H62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="3">
         <v>401600</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>10</v>
@@ -6198,89 +6343,92 @@
       <c r="L62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N62" s="3">
         <v>266600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13568800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13453100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13622800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13403800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13526600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13729800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13614700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13016600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12820300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10694800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10566900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11144900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11048800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10354200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7139000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4589600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6392,8 +6540,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6505,8 +6656,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6618,121 +6772,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>108452500</v>
+      </c>
+      <c r="E66" s="3">
         <v>105218700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98411200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>104145600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100482400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100688600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90330300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>95691100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87923700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>86836300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>91731600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112244000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>105638100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103587700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>103156000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106870400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>106961600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>105035900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>103575200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>96014900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>83728500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>81439100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>85870200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87396600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>85691900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>74973700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>70887900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6772,8 +6932,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6885,8 +7046,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6998,8 +7162,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7046,73 +7213,76 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>1461600</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1477500</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1201100</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1207300</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1175300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1183700</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1152400</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1425200</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1200300</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>1171000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>1083400</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>1037300</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>839900</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>452700</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>430600</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>442100</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>133300</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>113200</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>435100</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>515800</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7224,121 +7394,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>95947600</v>
+      </c>
+      <c r="E72" s="3">
         <v>92618300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>91147800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>89370200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>86891000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>79785900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>84845900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>89068500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>89093400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>86996400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>89094100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>84254400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76966400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>80286100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>79174500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>81449200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>82138400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>86310300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>78268100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>79111700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>72029000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>67773800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>64563300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>63003500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55694500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>43446200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>39985800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7450,8 +7626,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7563,8 +7742,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7676,121 +7858,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>145029600</v>
+      </c>
+      <c r="E76" s="3">
         <v>141499200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>139166000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>137157900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>135993300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>129081900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>136631000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>142519300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>141858100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>139749300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>144071700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>137590000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130967000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>133909600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130966000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>134238900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>136865400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>140101700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>130495800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>130438900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>126346900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>119170500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>118265600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>114579000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>94042700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>79603400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>74882100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7902,239 +8090,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2952400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5674200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1730700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6730600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6277400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3356300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>466000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2052600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3816400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4721500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3442000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6600000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3161200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2814700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>762900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6483200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-762700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11056200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4239400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7013000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>495000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8054500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11317000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3246900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3929300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8174,44 +8371,45 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>964600</v>
+      </c>
+      <c r="E83" s="3">
         <v>843000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>947000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>949000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>876000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>921200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>996200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1031400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1004600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>999400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1192800</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -8287,8 +8485,11 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8400,8 +8601,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8513,8 +8717,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8626,8 +8833,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8739,8 +8949,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8852,121 +9065,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1418600</v>
+      </c>
+      <c r="E89" s="3">
         <v>2885600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3792500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9715600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4481900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4628700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3232500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9126600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6747100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6247100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4571300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12317400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6509000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4708500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-972100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11072800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5093200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4826100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3366300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14366600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8001100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7382600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>338800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14859800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7383300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5288000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2822300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9006,31 +9225,32 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4424800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5398800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11847600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4353300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-2493500</v>
-      </c>
-      <c r="H91" s="3" t="s">
+      <c r="H91" s="3">
+        <v>-4217700</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4443900</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>10</v>
@@ -9038,89 +9258,92 @@
       <c r="L91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N91" s="3">
         <v>-4997700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="R91" s="3">
         <v>-18710000</v>
       </c>
       <c r="S91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="T91" s="3" t="s">
+      <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-453500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-813500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-281000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-975000</v>
       </c>
-      <c r="AC91" s="3" t="s">
+      <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AG91" s="3" t="s">
+      <c r="AH91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
-      </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9232,8 +9455,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9345,121 +9571,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9783700</v>
+      </c>
+      <c r="E94" s="3">
         <v>2558400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5449900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15207800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>137400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4930400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2806900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4361200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3256400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1736700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3902600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9499,31 +9731,32 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>4722600</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2800</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3">
-        <v>4115800</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>4137400</v>
+      </c>
+      <c r="I96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2485400</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>10</v>
@@ -9534,8 +9767,8 @@
       <c r="M96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -9612,8 +9845,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9725,8 +9961,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9838,8 +10077,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9951,343 +10193,355 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1531400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-381200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-565300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1952400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9520600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2694700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7480400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2427600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1697000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1356600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4213600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-791400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1489200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-679200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>464500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9437000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>328600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>686400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>109400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>614200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>361000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="E101" s="3">
         <v>90700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>263100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-372700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>111400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>595500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-174800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-294600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>483100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>496500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-144000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-286300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>474700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>462400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-126100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-816200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>27700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-314800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>159900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-575200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-567800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-51700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>363500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>367100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>210400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-173700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>233700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>399300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>253800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6901900</v>
+      </c>
+      <c r="E102" s="3">
         <v>4929100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2301100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3083400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5251400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2905800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1177900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1965100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1905100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5182400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-862800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4273300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3025000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3883800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1904100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18978300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4747700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2955700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>209800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>494500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>291500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>3117700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,495 +656,519 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35285800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>40724400</v>
+      </c>
+      <c r="F8" s="3">
         <v>34806600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>34569900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>32585100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>38382000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>33716300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>33471800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>30728300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>36715800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>30807500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>32287100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>30309200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>34928600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>28623400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>28576300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>28175500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>33422700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>28528100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>29548400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>26085400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>30774900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>22849500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>22656700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>17897000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>24861000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>18567800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>17558100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>14222900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>23109000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>24238500</v>
+      </c>
+      <c r="F9" s="3">
         <v>21179500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>19044200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>20068400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>22266300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>20533000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>20105700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>20510800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>22030200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>19141000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>19627800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>20044500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>21147700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>18128000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>18024900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>19185500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>20206500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>18444000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>17822800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>17463200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>16880500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>13256500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>12455300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11350900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>12985400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>10225800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>9164800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8459400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12176800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16485900</v>
+      </c>
+      <c r="F10" s="3">
         <v>13627100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>15525700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>12516800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>16115700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13183300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>13366100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>10217600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>14685600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>11666500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>12659300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>10264700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>13780900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>10495500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>10551300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8990000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>13216100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>10084100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>11725600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>8622200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>13894400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>9593000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>10201400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>6546100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>11875600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>8342000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>8393300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>5763500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1185,124 +1209,132 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2748400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2213200</v>
+      </c>
+      <c r="F12" s="3">
         <v>2401300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2094000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2058000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2008700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2021800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1840300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1950700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1902200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1948600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1443000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2020600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1906200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2093100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1973100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1511100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2163800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2174500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1941600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1851600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1894100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2835900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1633000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1657500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1705600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1706400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1600800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1317200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>959300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>933400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>754400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>696900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>657100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>642800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1417,240 +1449,258 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>481100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1360400</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>635400</v>
       </c>
-      <c r="G14" s="3">
-        <v>931200</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>845400</v>
+      </c>
+      <c r="J14" s="3">
         <v>-210700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>636200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2845900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>3395100</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1093300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-953800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>382600</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>3463900</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>89900</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>73300</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>309000</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>120200</v>
+      </c>
+      <c r="F15" s="3">
         <v>116000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>112600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>-520600</v>
       </c>
-      <c r="G15" s="3">
-        <v>196700</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>282500</v>
+      </c>
+      <c r="J15" s="3">
         <v>235100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>246600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>-1768000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>355000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>333200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>341800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-46100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>779600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>377000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>382400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>390900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>390900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>413100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>441300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>475400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>441500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>425600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>435000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>633100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>503800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>469000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>468400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>487200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>408000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>365400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>301900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>190700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>305300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>259400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>294700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>190900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>183400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1688,240 +1738,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34927700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>37842100</v>
+      </c>
+      <c r="F17" s="3">
         <v>34053000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>29685900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>28027000</v>
       </c>
-      <c r="G17" s="3">
-        <v>31805600</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>31891300</v>
+      </c>
+      <c r="J17" s="3">
         <v>28691600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>28086500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>26627200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>30639700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>26204800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>26148300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>27516500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>29990000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>25150500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>25108700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>25867200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>32448800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>26395000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>25118100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>27152100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>23953800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>20840400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>17542600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>16780600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>18769500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>15390900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>13834100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>12889600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>358100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2882300</v>
+      </c>
+      <c r="F18" s="3">
         <v>753600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4884000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>4558100</v>
       </c>
-      <c r="G18" s="3">
-        <v>6576400</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>6490700</v>
+      </c>
+      <c r="J18" s="3">
         <v>5024700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5385200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4101100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6076100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4602700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6138900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2792800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4938700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3472900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3467600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2308300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>973800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2133100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4430200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>6821100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2009100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>5114100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1116400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>6091400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>3177000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>3724000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1333300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1962,222 +2026,230 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>31200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-452600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-190000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-51500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1057300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>71300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-242500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>33900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>165600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>599300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-581100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-255300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2393600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>761600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>3230100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2335000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>309900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>5966400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1717900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>3482100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2790600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>10377600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>349600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3059700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>714200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>405900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>767600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>498500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>560200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2971400</v>
+      </c>
+      <c r="F21" s="3">
         <v>1322200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5186600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>4089000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>7830400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5188500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5874300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2299100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6265500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4336500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>7061800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3002000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>7722500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5542300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4157900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>704500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>8197100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>564900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>12940900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3812200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>9866300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1609300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>8955000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>13596400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>5257300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>4411900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>10</v>
@@ -2185,365 +2257,389 @@
       <c r="AK21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>324900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>365600</v>
+      </c>
+      <c r="F22" s="3">
         <v>353600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>345900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>344000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>340500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>346000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>301100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>301500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>300700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>254100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>246000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>252700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>218500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>191800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>172900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>164200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>163400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>180100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>182000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>161500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>152000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>162200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>165500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>182400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>201600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>212200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>205600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>198200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>193700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>187500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>174000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>168600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>125300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>110900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>118700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>98300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>101900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4446900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3444300</v>
+      </c>
+      <c r="F23" s="3">
         <v>3674900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>7153600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2594500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>7889100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7260100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4690400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>919700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2214800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4453200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5380600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3749200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>7113700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4056200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4040500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>560900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>6583300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-918300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>12635500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3564800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>8430800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-89100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>8680500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>13342400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3867900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>4194900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1039500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1209500</v>
+      </c>
+      <c r="F24" s="3">
         <v>779600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1237500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>944500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1527400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1052000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1384800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>792500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>703400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>794500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>830400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>547100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>538500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>355300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>750600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>287100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1316200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>865300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1306400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>981200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1279800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>281600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1639200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>411400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1294500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>439200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>1025500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>764400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>811300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>38800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>812800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>597500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>988900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>403500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>690600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>662100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>743100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,240 +2754,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3407400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2234800</v>
+      </c>
+      <c r="F26" s="3">
         <v>2895300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>5916100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1650000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>6361600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6208100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3305700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>127300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1511400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3658700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4550300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3202100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>6575200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3305600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2724300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-304300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>5276900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>11355700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3283200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>6791500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-500500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>7386000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>12903300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2842500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>3430500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>962900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3693600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2333600</v>
+      </c>
+      <c r="F27" s="3">
         <v>2948400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>6018600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1706300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>6705600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>6254800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3339700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>452900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2035400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3797100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4733900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3423400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>6600000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3161200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2814700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>762900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>6483200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-762700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>11056200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>495000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>8054500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>11317000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3246900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>3929300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3006,8 +3120,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3122,8 +3242,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3238,8 +3364,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3354,240 +3486,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F32" s="3">
         <v>452600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>190000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>51500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1057300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-71300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>242500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-33900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-165600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-599300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>581100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>255300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5458400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-761600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4845000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1392100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-309900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1023100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-349600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3703000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2342300</v>
+      </c>
+      <c r="F33" s="3">
         <v>2952400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>5674200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1730700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>6730600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>6277400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3356300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>466000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2052600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3816400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4721500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3442000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>6600000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3161200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2814700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>762900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>6483200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-762700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>11056200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>495000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>8054500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>11317000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3246900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>3929300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3702,245 +3852,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3703000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2342300</v>
+      </c>
+      <c r="F35" s="3">
         <v>2952400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>5674200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1730700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>6730600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>6277400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3356300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>466000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2052600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3816400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4721500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3442000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>6600000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3161200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2814700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>762900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>6483200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-762700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>11056200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>495000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>8054500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>11317000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3246900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>3929300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3981,8 +4149,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4023,282 +4193,296 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19069500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18325200</v>
+      </c>
+      <c r="F41" s="3">
         <v>18972500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>25561900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>20049200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22301900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>26087700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>30159600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>34364000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>35933900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>33401300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>31218400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>28109000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>27526200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>28559200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>24569300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>26221100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>40385100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>38694100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>41909600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>44719700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>43449500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>44430400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>45573600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>51743500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>53981500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>36534000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>32166100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>28899100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26863700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>30014900</v>
+      </c>
+      <c r="F42" s="3">
         <v>33501400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>32565800</v>
       </c>
-      <c r="F42" s="3">
-        <v>38945200</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>38854700</v>
+      </c>
+      <c r="I42" s="3">
         <v>39798600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>29338700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>31616900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>44720400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>50712200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>45314800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>43851500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>48242000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>45672400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>38739900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>39836300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>36617000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>27806800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>26581900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>27509400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>22575900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>20883300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>16090800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>11389600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>5121400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1021700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1066000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1540200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>2006300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
+      <c r="D43" s="3">
+        <v>13644000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="3">
-        <v>10487000</v>
+      <c r="F43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>10</v>
+      <c r="H43" s="3">
+        <v>10487000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="3">
-        <v>9542600</v>
+      <c r="J43" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>10</v>
+      <c r="L43" s="3">
+        <v>9542600</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P43" s="3">
         <v>9337900</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4371,50 +4555,56 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
+      <c r="D44" s="3">
+        <v>2741500</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="3">
-        <v>2602800</v>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>10</v>
+      <c r="H44" s="3">
+        <v>2602800</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="3">
-        <v>3526100</v>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>10</v>
+      <c r="L44" s="3">
+        <v>3526100</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="3">
         <v>4155800</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -4487,588 +4677,624 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22961700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6054100</v>
+      </c>
+      <c r="F45" s="3">
         <v>5671100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5787300</v>
       </c>
-      <c r="F45" s="3">
-        <v>17972000</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>18062600</v>
+      </c>
+      <c r="I45" s="3">
         <v>30766000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>6483700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>28177900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9651500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27195800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>25161900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>25647900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9318600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>29487800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>26333200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>25257300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>25330800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>24828600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>25422400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>23522800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>22260200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>18870600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>16538500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>15436500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>15610300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>15742300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>14770600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>10696400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>10208500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>88550600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>87529500</v>
+      </c>
+      <c r="F46" s="3">
         <v>90827500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>95769100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>92889000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>92866500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>86834700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>89954500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>104267600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>113842000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>103878000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>100717700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>101608000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>102686400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>93632300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>89662900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>88168900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>93020500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>90698400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>92941800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>89555700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>83203500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>77059700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>72399700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>72475200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>70745500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>52370500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>44402800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>41113900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>95216300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>92819400</v>
+      </c>
+      <c r="F47" s="3">
         <v>86922000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>79733100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>78135100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>76295000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>78010700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>73595100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>58731800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>60528800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>62509800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>62278200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>65963600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>61483200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>57773100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>62111600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>61204400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>65630300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>65584300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>65281500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>60887500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>59266900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>58735200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>55079600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>54946500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>55746500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>51631700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>38852700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>36743700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47586500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>36383100</v>
+      </c>
+      <c r="F48" s="3">
         <v>34630200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>30826500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>33425200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>31076600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>29641000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>26726900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>36297800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>25611400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>24591700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>24248700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>36897900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>25065700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>24809000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>24719400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>34500500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>22741400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>22326900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>21917300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>20519800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>20473800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>17393900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>16424900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>21612600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19466200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>19627200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>18193700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>13999600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38327600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>37753100</v>
+      </c>
+      <c r="F49" s="3">
         <v>38625100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>38485600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>38091600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>37896700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>40277600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>39218100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>39696600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>40598100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>42253200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>42902800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>45857500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>44701000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>44964000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>45496200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>45402400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>45628900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>51142200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>51691900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>50613700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>51132800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>49004600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>49288400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>52874900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>52626800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>53469800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>50862400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>50688100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5183,8 +5409,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5299,124 +5531,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5149000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>14058200</v>
+      </c>
+      <c r="F52" s="3">
         <v>13614900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>13021600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4281400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16001200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>16531500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>16147200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3852100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>16222900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>15045900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>14851300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2621000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>15897800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>15426700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>15507100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4845800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>15549900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>15552800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>14506300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>13701700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>13552100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>9065700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>8569300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3651800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4590900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3806500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3348900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4262100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5531,124 +5775,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>276853600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>268543300</v>
+      </c>
+      <c r="F54" s="3">
         <v>264619600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>257835900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>248636000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>254136000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>251295500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>245641700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>244419200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>256803200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>248278700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>244998700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>255203500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>249834000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>236605100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>237497300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>234122000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>242570900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>245304600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>246338700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>235278300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>227629000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>211259100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>201761900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>205560900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>203175800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>180905600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>155660500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>146807400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5689,8 +5945,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5731,86 +5989,88 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>10</v>
+      <c r="D57" s="3">
+        <v>20107600</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F57" s="3">
-        <v>16401400</v>
+      <c r="F57" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>10</v>
+      <c r="H57" s="3">
+        <v>16401400</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J57" s="3">
-        <v>17666400</v>
+      <c r="J57" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>10</v>
+      <c r="L57" s="3">
+        <v>17666400</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P57" s="3">
         <v>16559700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>41401000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>37560600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>36918600</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="T57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>38835600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>37802900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>35961600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>36321300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>31307500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>26279700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>24271800</v>
       </c>
-      <c r="Z57" s="3" t="s">
+      <c r="AB57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
@@ -5847,588 +6107,624 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4718000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3525000</v>
+      </c>
+      <c r="F58" s="3">
         <v>3692500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3431700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3652700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2939100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4665200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4115900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4829600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3716600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1122000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1135600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2610600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1630400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1602900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1883600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1220800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1089300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2679000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2443400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1870400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2094500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>722500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>669500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>806900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>649000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3768400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3516800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3417500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>864900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>956800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38532500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11990000</v>
+      </c>
+      <c r="F59" s="3">
         <v>10827100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10807000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>34517600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>13093100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12745200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12894200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>30677900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15112000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13022400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12775500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>31687700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15874900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13732600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>13411500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>51772100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>16634700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>14652800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>14475700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>14336500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>16453900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11744900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>11617700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>37060600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>39764300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>34290100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>28673900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>28173100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69069200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>65739900</v>
+      </c>
+      <c r="F60" s="3">
         <v>62385800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>66113900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>59993900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>62659600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>63421200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>63698400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>58376400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>63285900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>53423500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>52430100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>56098400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>58906400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>52896100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>52213700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>52992900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>56559700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>55134700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>52880700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>52528200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>49855900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>38747100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>36559000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>37867500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>40413300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>38058500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>32190700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>31590600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36126700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>37440500</v>
+      </c>
+      <c r="F61" s="3">
         <v>38861100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>31921900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>30538700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>33271000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>28640800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>28927300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>23646800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>24277700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>26076700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>25934500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>25859800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>20901700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>20701600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>19249000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>18296000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>18149900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>18892700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>19187500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>18891700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>14289200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>17224200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>17814900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>18830400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>18196100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>18958600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>17779000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>17012200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>10</v>
+      <c r="D62" s="3">
+        <v>982500</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="3">
-        <v>576200</v>
+      <c r="F62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>10</v>
+      <c r="H62" s="3">
+        <v>576200</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="3">
-        <v>401600</v>
+      <c r="J62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>10</v>
+      <c r="L62" s="3">
+        <v>401600</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="3">
         <v>266600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>13568800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13453100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>13622800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>13403800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>13526600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>13729800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>13614700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>13016600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>12820300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>10694800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>10566900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11144900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>11048800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>10354200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>7139000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>4589600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6543,8 +6839,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6659,8 +6961,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6775,124 +7083,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>113564500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>110427100</v>
+      </c>
+      <c r="F66" s="3">
         <v>108452500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>105218700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>98411200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>104145600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>100482400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>100688600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>90330300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>95691100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>87923700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>86836300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>91731600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>112244000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>105638100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>103587700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>103156000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>106870400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>106961600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>105035900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>103575200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>96014900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>83728500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>81439100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>85870200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>87396600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>85691900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>74973700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>70887900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6933,8 +7253,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7049,8 +7371,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7165,8 +7493,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7216,73 +7550,79 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1461600</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>1477500</v>
       </c>
-      <c r="U70" s="3">
+      <c r="W70" s="3">
         <v>1201100</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>1207300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>1175300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>1183700</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>1152400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>1425200</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>1200300</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>1171000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>1083400</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>1037300</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AG70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AH70" s="3">
         <v>839900</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>452700</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>430600</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AK70" s="3">
         <v>442100</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AL70" s="3">
         <v>133300</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AM70" s="3">
         <v>113200</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AN70" s="3">
         <v>435100</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AO70" s="3">
         <v>515800</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AP70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7397,124 +7737,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>105113500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>100002600</v>
+      </c>
+      <c r="F72" s="3">
         <v>95947600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>92618300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>91147800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>89370200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>86891000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>79785900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>84845900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>89068500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>89093400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>86996400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>89094100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>84254400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>76966400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>80286100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>79174500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>81449200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>82138400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>86310300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>78268100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>79111700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>72029000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>67773800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>64563300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>63003500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>55694500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>43446200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>39985800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7629,8 +7981,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7745,8 +8103,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7861,124 +8225,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>153809600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>148641100</v>
+      </c>
+      <c r="F76" s="3">
         <v>145029600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>141499200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>139166000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>137157900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>135993300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>129081900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>136631000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>142519300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>141858100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>139749300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>144071700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>137590000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>130967000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>133909600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>130966000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>134238900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>136865400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>140101700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>130495800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>130438900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>126346900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>119170500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>118265600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>114579000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>94042700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>79603400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>74882100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8093,245 +8469,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3703000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2342300</v>
+      </c>
+      <c r="F81" s="3">
         <v>2952400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>5674200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1730700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>6730600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>6277400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3356300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>466000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2052600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3816400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4721500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3442000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>6600000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3161200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2814700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>762900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>6483200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-762700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>11056200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>495000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>8054500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>11317000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3246900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>3929300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8372,50 +8766,52 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1263300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>986600</v>
+      </c>
+      <c r="F83" s="3">
         <v>964600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>843000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>947000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>949000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>876000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>921200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>996200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1031400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1004600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>999400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1192800</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -8488,8 +8884,14 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8604,8 +9006,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8720,8 +9128,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8836,8 +9250,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8952,8 +9372,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9068,124 +9494,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1364300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5151500</v>
+      </c>
+      <c r="F89" s="3">
         <v>1418600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2885600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3792500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>9715600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4481900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4628700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3232500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>9126600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6747100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>6247100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4571300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>12317400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>6509000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4708500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-972100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>11072800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>5093200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>4826100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3366300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>14366600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>8001100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>7382600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>338800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>14859800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>7383300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>5288000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>2822300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9226,124 +9664,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18276900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4146000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4424800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5398800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-11847600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4353300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-4217700</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J91" s="3">
-        <v>-4443900</v>
+        <v>-4217700</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>10</v>
+      <c r="L91" s="3">
+        <v>-4443900</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P91" s="3">
         <v>-4997700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11843000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-18710000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-18710000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="U91" s="3" t="s">
+      <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-453500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-813500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-281000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-975000</v>
       </c>
-      <c r="AD91" s="3" t="s">
+      <c r="AF91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AH91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AL91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>0</v>
-      </c>
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9458,8 +9904,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9574,124 +10026,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1406900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3676700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-9783700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>2558400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5449900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-15207800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>137400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4930400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2806900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4361200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3256400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1736700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3902600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9732,37 +10196,39 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4722600</v>
+        <v>6100</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="3">
-        <v>2800</v>
+        <v>4722600</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H96" s="3">
-        <v>4137400</v>
+        <v>4007000</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J96" s="3">
-        <v>2485400</v>
+        <v>4137400</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
+      <c r="L96" s="3">
+        <v>2485400</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>10</v>
@@ -9770,11 +10236,11 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9848,8 +10314,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9964,8 +10436,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10080,8 +10558,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10196,352 +10680,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2175000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1964700</v>
+      </c>
+      <c r="F100" s="3">
         <v>1531400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-381200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-565300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1952400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-9520600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2694700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-7480400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2427600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1697000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1356600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>4213600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-791400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1489200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-679200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>464500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>9437000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>328600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>686400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>109400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>614200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>361000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-78400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>456400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-350100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>90700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>263100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-372700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>111400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>595500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-174800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-294600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>483100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>496500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-144000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-286300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>474700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>462400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-126100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-816200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>27700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-314800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>159900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-575200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-567800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-51700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>363500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-300600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>367100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>210400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-173700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>233700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>399300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>253800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-704000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6901900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4929100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2301100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3083400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5251400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2905800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1177900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1965100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1905100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>5182400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-862800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>4273300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3025000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>3883800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1904100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>18978300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4747700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2955700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>209800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>494500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>291500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>3117700</v>
       </c>
     </row>
